--- a/content/notes/travel/travel.xlsx
+++ b/content/notes/travel/travel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ravi/programs/rk1165.github.io/content/notes/travel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CF5706-066B-E647-835D-FC33BE3C714E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B21D2B3-E048-8147-BAFC-B2BB616DE917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="3" xr2:uid="{FBDD8960-5B88-4843-A147-F58767FB427D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="542">
   <si>
     <t>Check In</t>
   </si>
@@ -606,9 +606,6 @@
     <t>Estonian War Museum</t>
   </si>
   <si>
-    <t>0630-0739</t>
-  </si>
-  <si>
     <t>Trakai</t>
   </si>
   <si>
@@ -726,12 +723,6 @@
     <t>Cycle</t>
   </si>
   <si>
-    <t>0700-0705</t>
-  </si>
-  <si>
-    <t>0710-0808</t>
-  </si>
-  <si>
     <t>MC</t>
   </si>
   <si>
@@ -741,33 +732,18 @@
     <t>5-day Ticket</t>
   </si>
   <si>
-    <t>Ühiskaart</t>
-  </si>
-  <si>
     <t>Audio Guide 3€</t>
   </si>
   <si>
     <t>Dome Cathedral</t>
   </si>
   <si>
-    <t>1805-1906</t>
-  </si>
-  <si>
-    <t>0630-0821</t>
-  </si>
-  <si>
-    <t>1726-1906</t>
-  </si>
-  <si>
     <t>Turaida Museum</t>
   </si>
   <si>
     <t>Castle Complex</t>
   </si>
   <si>
-    <t>1925-2310</t>
-  </si>
-  <si>
     <t>0705-1104</t>
   </si>
   <si>
@@ -1170,9 +1146,6 @@
     <t>Estonian History Museum</t>
   </si>
   <si>
-    <t>TV Tower</t>
-  </si>
-  <si>
     <t>Fotografiska</t>
   </si>
   <si>
@@ -1569,9 +1542,6 @@
     <t>Helsinki Cathedral</t>
   </si>
   <si>
-    <t>Uspenskin Cathedral</t>
-  </si>
-  <si>
     <t>Evening Cruise</t>
   </si>
   <si>
@@ -1671,9 +1641,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Tallinn 72h Card</t>
-  </si>
-  <si>
     <t>7 remaining</t>
   </si>
   <si>
@@ -1687,6 +1654,18 @@
   </si>
   <si>
     <t>3€ Funicular Up and Down, VP</t>
+  </si>
+  <si>
+    <t>Uspenski Cathedral</t>
+  </si>
+  <si>
+    <t>Tallinn 56h Card</t>
+  </si>
+  <si>
+    <t>Summer Guided Tour</t>
+  </si>
+  <si>
+    <t>TB</t>
   </si>
 </sst>
 </file>
@@ -2067,9 +2046,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2082,18 +2064,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4480,7 +4459,7 @@
       <c r="O2" s="64"/>
       <c r="P2" s="65"/>
       <c r="R2" s="38" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:20" ht="19" x14ac:dyDescent="0.25">
@@ -4497,7 +4476,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>53</v>
@@ -4535,7 +4514,7 @@
         <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F4" s="1">
         <v>29714</v>
@@ -4570,7 +4549,7 @@
         <v>79</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F5" s="1">
         <v>10060</v>
@@ -4605,7 +4584,7 @@
         <v>90</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F6" s="1">
         <v>2970</v>
@@ -4640,7 +4619,7 @@
         <v>95</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="F7" s="1">
         <v>6300</v>
@@ -4676,7 +4655,7 @@
         <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F8" s="1">
         <v>10132</v>
@@ -4760,7 +4739,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>53</v>
@@ -4807,7 +4786,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -4819,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>53</v>
@@ -4831,7 +4810,7 @@
       <c r="K13" s="80"/>
       <c r="L13" s="81"/>
       <c r="N13" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O13" s="41">
         <v>1640</v>
@@ -4858,7 +4837,7 @@
       <c r="K14" s="78"/>
       <c r="L14" s="78"/>
       <c r="N14" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="O14" s="41">
         <v>3000</v>
@@ -4877,10 +4856,10 @@
         <v>45794</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>89</v>
@@ -4899,7 +4878,7 @@
       <c r="K15" s="78"/>
       <c r="L15" s="78"/>
       <c r="N15" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O15" s="41">
         <v>3000</v>
@@ -4918,10 +4897,10 @@
         <v>45795</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>84</v>
@@ -4938,7 +4917,7 @@
       <c r="K16" s="71"/>
       <c r="L16" s="72"/>
       <c r="N16" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="O16" s="41">
         <v>17000</v>
@@ -4957,13 +4936,13 @@
         <v>45795</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>83</v>
@@ -4977,7 +4956,7 @@
       <c r="K17" s="71"/>
       <c r="L17" s="72"/>
       <c r="N17" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4">
@@ -4994,14 +4973,14 @@
         <v>45795</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G18" s="40">
         <v>1100</v>
@@ -5033,16 +5012,16 @@
         <v>45796</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G19" s="1">
         <v>400</v>
@@ -5066,16 +5045,16 @@
         <v>45796</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G20" s="1">
         <v>300</v>
@@ -5099,16 +5078,16 @@
         <v>45796</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G21" s="40">
         <v>1600</v>
@@ -5136,13 +5115,13 @@
         <v>45797</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>77</v>
@@ -5177,10 +5156,10 @@
         <v>45797</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>91</v>
@@ -5214,13 +5193,13 @@
         <v>45797</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>77</v>
@@ -5230,7 +5209,7 @@
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="78" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="J24" s="78"/>
       <c r="K24" s="78"/>
@@ -5253,10 +5232,10 @@
         <v>45797</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>82</v>
@@ -5291,13 +5270,13 @@
         <v>45798</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>77</v>
@@ -5326,13 +5305,13 @@
         <v>45799</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>77</v>
@@ -5360,13 +5339,13 @@
         <v>45800</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>77</v>
@@ -5376,7 +5355,7 @@
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="78" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="J28" s="78"/>
       <c r="K28" s="78"/>
@@ -5397,14 +5376,14 @@
         <v>45800</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="G29" s="40">
         <v>900</v>
@@ -5417,7 +5396,7 @@
       <c r="K29" s="78"/>
       <c r="L29" s="78"/>
       <c r="N29" s="6" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>80</v>
@@ -5429,7 +5408,7 @@
         <v>37</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="T29">
         <v>362.54</v>
@@ -5440,13 +5419,13 @@
         <v>45801</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>79</v>
@@ -5483,13 +5462,13 @@
         <v>45801</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>79</v>
@@ -5511,13 +5490,13 @@
         <v>45802</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>79</v>
@@ -5539,13 +5518,13 @@
         <v>45802</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>79</v>
@@ -5571,11 +5550,11 @@
         <v>45802</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>79</v>
@@ -5603,11 +5582,11 @@
         <v>45802</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>79</v>
@@ -5637,13 +5616,13 @@
         <v>45803</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>79</v>
@@ -5665,13 +5644,13 @@
         <v>45803</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>79</v>
@@ -5693,14 +5672,14 @@
         <v>45803</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G38" s="1">
         <v>500</v>
@@ -5719,16 +5698,16 @@
         <v>45804</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G39" s="1">
         <v>500</v>
@@ -5747,23 +5726,23 @@
         <v>45804</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G40" s="1">
         <v>700</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="78" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="J40" s="78"/>
       <c r="K40" s="78"/>
@@ -5777,10 +5756,10 @@
         <v>45805</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>88</v>
@@ -5795,7 +5774,7 @@
         <v>623.46</v>
       </c>
       <c r="I41" s="78" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="J41" s="78"/>
       <c r="K41" s="78"/>
@@ -5809,11 +5788,11 @@
         <v>45805</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>90</v>
@@ -5835,13 +5814,13 @@
         <v>45806</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>96</v>
@@ -5863,13 +5842,13 @@
         <v>45806</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>96</v>
@@ -5879,7 +5858,7 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="78" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="J44" s="78"/>
       <c r="K44" s="78"/>
@@ -5893,13 +5872,13 @@
         <v>45806</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>96</v>
@@ -5909,7 +5888,7 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="78" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="J45" s="78"/>
       <c r="K45" s="78"/>
@@ -5923,10 +5902,10 @@
         <v>45807</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>97</v>
@@ -5953,13 +5932,13 @@
         <v>45808</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>85</v>
@@ -5981,13 +5960,13 @@
         <v>45808</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>85</v>
@@ -6009,13 +5988,13 @@
         <v>45808</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>78</v>
@@ -6025,7 +6004,7 @@
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="78" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J49" s="78"/>
       <c r="K49" s="78"/>
@@ -6034,7 +6013,7 @@
         <v>3982.12</v>
       </c>
       <c r="U49" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.2">
@@ -6042,11 +6021,11 @@
         <v>45808</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>78</v>
@@ -6056,7 +6035,7 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="78" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J50" s="78"/>
       <c r="K50" s="78"/>
@@ -6070,13 +6049,13 @@
         <v>45808</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>78</v>
@@ -6111,13 +6090,13 @@
         <v>45809</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>78</v>
@@ -6127,7 +6106,7 @@
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="78" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J53" s="78"/>
       <c r="K53" s="78"/>
@@ -6138,13 +6117,13 @@
         <v>45809</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>78</v>
@@ -6154,7 +6133,7 @@
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="78" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J54" s="78"/>
       <c r="K54" s="78"/>
@@ -6165,10 +6144,10 @@
         <v>45809</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>86</v>
@@ -6181,7 +6160,7 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="78" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J55" s="78"/>
       <c r="K55" s="78"/>
@@ -6265,7 +6244,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>69</v>
@@ -6274,16 +6253,16 @@
         <v>70</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J61" s="88" t="s">
         <v>7</v>
@@ -6296,16 +6275,16 @@
         <v>45793</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G62" s="1">
         <v>610</v>
@@ -6313,7 +6292,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="78" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="K62" s="78"/>
       <c r="L62" s="78"/>
@@ -6323,16 +6302,16 @@
         <v>45794</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G63" s="1">
         <v>180</v>
@@ -6348,16 +6327,16 @@
         <v>45794</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G64" s="1">
         <v>180</v>
@@ -6373,16 +6352,16 @@
         <v>45795</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G65" s="1">
         <v>390</v>
@@ -6398,16 +6377,16 @@
         <v>45795</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G66" s="1">
         <v>390</v>
@@ -6423,13 +6402,13 @@
         <v>45796</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="40">
@@ -6440,7 +6419,7 @@
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="78" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="K67" s="78"/>
       <c r="L67" s="78"/>
@@ -6450,13 +6429,13 @@
         <v>45796</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="40">
@@ -6467,7 +6446,7 @@
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="78" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="K68" s="78"/>
       <c r="L68" s="78"/>
@@ -6477,13 +6456,13 @@
         <v>45797</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1">
@@ -6500,13 +6479,13 @@
         <v>45797</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1">
@@ -6523,13 +6502,13 @@
         <v>45797</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1">
@@ -6546,13 +6525,13 @@
         <v>45798</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1">
@@ -6569,13 +6548,13 @@
         <v>45798</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1">
@@ -6592,13 +6571,13 @@
         <v>45799</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1">
@@ -6615,7 +6594,7 @@
         <v>45799</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6632,13 +6611,13 @@
         <v>45800</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1">
@@ -6655,13 +6634,13 @@
         <v>45800</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1">
@@ -6678,7 +6657,7 @@
         <v>45800</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -6689,7 +6668,7 @@
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="78" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K78" s="78"/>
       <c r="L78" s="78"/>
@@ -6699,13 +6678,13 @@
         <v>45800</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1">
@@ -6722,13 +6701,13 @@
         <v>45800</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1">
@@ -6745,10 +6724,10 @@
         <v>45801</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>77</v>
@@ -6768,7 +6747,7 @@
         <v>45801</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>77</v>
@@ -6793,13 +6772,13 @@
         <v>45801</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1">
@@ -6816,13 +6795,13 @@
         <v>45801</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1">
@@ -6831,7 +6810,7 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="78" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="K84" s="78"/>
       <c r="L84" s="78"/>
@@ -6841,13 +6820,13 @@
         <v>45801</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="1">
@@ -6864,13 +6843,13 @@
         <v>45801</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1">
@@ -6887,13 +6866,13 @@
         <v>45802</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1">
@@ -6910,16 +6889,16 @@
         <v>45802</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G88" s="1">
         <v>230</v>
@@ -6935,16 +6914,16 @@
         <v>45802</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G89" s="1">
         <v>230</v>
@@ -6960,13 +6939,13 @@
         <v>45803</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1">
@@ -6983,13 +6962,13 @@
         <v>45803</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1">
@@ -7006,13 +6985,13 @@
         <v>45803</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1">
@@ -7029,13 +7008,13 @@
         <v>45803</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1">
@@ -7052,13 +7031,13 @@
         <v>45804</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1">
@@ -7067,7 +7046,7 @@
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="78" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="K94" s="78"/>
       <c r="L94" s="78"/>
@@ -7077,10 +7056,10 @@
         <v>45804</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>79</v>
@@ -7100,13 +7079,13 @@
         <v>45804</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1">
@@ -7123,13 +7102,13 @@
         <v>45805</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1">
@@ -7146,10 +7125,10 @@
         <v>45805</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>87</v>
@@ -7169,13 +7148,13 @@
         <v>45805</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1">
@@ -7192,10 +7171,10 @@
         <v>45805</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>95</v>
@@ -7215,13 +7194,13 @@
         <v>45805</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1">
@@ -7238,13 +7217,13 @@
         <v>45806</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1">
@@ -7261,13 +7240,13 @@
         <v>45806</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1">
@@ -7284,13 +7263,13 @@
         <v>45806</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1">
@@ -7306,10 +7285,10 @@
       <c r="B105" s="31"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1">
@@ -7326,13 +7305,13 @@
         <v>45807</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1">
@@ -7349,13 +7328,13 @@
         <v>45807</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1">
@@ -7372,7 +7351,7 @@
         <v>45808</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>78</v>
@@ -7387,7 +7366,7 @@
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
       <c r="J108" s="78" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="K108" s="78"/>
       <c r="L108" s="78"/>
@@ -7397,7 +7376,7 @@
         <v>45808</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>85</v>
@@ -7412,7 +7391,7 @@
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="78" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="K109" s="78"/>
       <c r="L109" s="78"/>
@@ -7422,13 +7401,13 @@
         <v>45810</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1">
@@ -7610,7 +7589,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5F645C-75EE-8D4F-9EC4-3C4B736D2C50}">
-  <dimension ref="B2:R124"/>
+  <dimension ref="B2:R122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -7651,7 +7630,7 @@
       <c r="O2" s="64"/>
       <c r="P2" s="65"/>
       <c r="R2" s="38" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="19" x14ac:dyDescent="0.25">
@@ -7668,16 +7647,16 @@
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="I3" s="82" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="J3" s="82"/>
       <c r="K3" s="82"/>
@@ -7694,7 +7673,7 @@
         <v>7</v>
       </c>
       <c r="R3" s="37">
-        <v>101.7</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="19" x14ac:dyDescent="0.25">
@@ -7705,10 +7684,10 @@
         <v>45877</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F4" s="3">
         <v>39.17</v>
@@ -7746,7 +7725,7 @@
         <v>175</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="F5" s="3">
         <v>26</v>
@@ -7784,7 +7763,7 @@
         <v>175</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="F6" s="3">
         <v>128</v>
@@ -7822,7 +7801,7 @@
         <v>176</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F7" s="3">
         <v>50.6</v>
@@ -7861,7 +7840,7 @@
         <v>177</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="F8" s="3">
         <v>121.47</v>
@@ -7874,7 +7853,7 @@
         <v>17.352857142857143</v>
       </c>
       <c r="I8" s="92" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="J8" s="92"/>
       <c r="K8" s="92"/>
@@ -7897,7 +7876,7 @@
         <v>178</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="F9" s="3">
         <v>25</v>
@@ -7931,7 +7910,7 @@
         <v>179</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="F10" s="3">
         <v>128</v>
@@ -7944,7 +7923,7 @@
         <v>18.285714285714285</v>
       </c>
       <c r="I10" s="92" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="J10" s="92"/>
       <c r="K10" s="92"/>
@@ -7976,7 +7955,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>53</v>
@@ -8011,14 +7990,12 @@
         <v>25</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O12" s="29">
         <v>75</v>
       </c>
-      <c r="P12" s="29" t="s">
-        <v>12</v>
-      </c>
+      <c r="P12" s="29"/>
       <c r="Q12" s="90" t="s">
         <v>175</v>
       </c>
@@ -8037,75 +8014,79 @@
       <c r="K13" s="83"/>
       <c r="L13" s="83"/>
       <c r="N13" s="28" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="O13" s="29">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="P13" s="29"/>
       <c r="Q13" s="90" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="R13" s="91"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="N14" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="O14" s="29">
-        <v>9</v>
-      </c>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="90" t="s">
-        <v>175</v>
-      </c>
-      <c r="R14" s="91"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="N14" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="O14" s="23">
+        <v>56</v>
+      </c>
+      <c r="P14" s="23">
+        <v>5695</v>
+      </c>
+      <c r="Q14" s="54" t="s">
+        <v>521</v>
+      </c>
+      <c r="R14" s="55"/>
     </row>
     <row r="15" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="C15" s="105" t="s">
+      <c r="C15" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="N15" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="O15" s="29">
-        <v>3</v>
-      </c>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="91"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="N15" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="O15" s="56">
+        <v>1.5</v>
+      </c>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="R15" s="119"/>
     </row>
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C16" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="111" t="s">
+      <c r="D16" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="111"/>
+      <c r="E16" s="107"/>
       <c r="F16" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>53</v>
@@ -8117,60 +8098,58 @@
       <c r="K16" s="80"/>
       <c r="L16" s="81"/>
       <c r="N16" s="22" t="s">
-        <v>529</v>
+        <v>229</v>
       </c>
       <c r="O16" s="23">
-        <v>56</v>
-      </c>
-      <c r="P16" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="Q16" s="54" t="s">
-        <v>531</v>
-      </c>
-      <c r="R16" s="55"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="R16" s="119"/>
     </row>
     <row r="17" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C17" s="48">
         <v>45875</v>
       </c>
-      <c r="D17" s="107" t="s">
-        <v>508</v>
-      </c>
-      <c r="E17" s="107"/>
+      <c r="D17" s="113" t="s">
+        <v>499</v>
+      </c>
+      <c r="E17" s="113"/>
       <c r="F17" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G17" s="47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H17" s="47"/>
       <c r="I17" s="108"/>
       <c r="J17" s="109"/>
       <c r="K17" s="109"/>
       <c r="L17" s="110"/>
-      <c r="N17" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="O17" s="56">
-        <v>1.5</v>
-      </c>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="R17" s="119"/>
+      <c r="N17" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="O17" s="26">
+        <v>10</v>
+      </c>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="R17" s="115"/>
     </row>
     <row r="18" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C18" s="48">
         <v>45875</v>
       </c>
-      <c r="D18" s="107" t="s">
-        <v>509</v>
-      </c>
-      <c r="E18" s="107"/>
+      <c r="D18" s="113" t="s">
+        <v>538</v>
+      </c>
+      <c r="E18" s="113"/>
       <c r="F18" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G18" s="47">
         <v>5</v>
@@ -8180,28 +8159,28 @@
       <c r="J18" s="109"/>
       <c r="K18" s="109"/>
       <c r="L18" s="110"/>
-      <c r="N18" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="O18" s="23">
-        <v>12</v>
-      </c>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="R18" s="119"/>
+      <c r="N18" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="O18" s="26">
+        <v>2</v>
+      </c>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="R18" s="115"/>
     </row>
     <row r="19" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C19" s="48">
         <v>45875</v>
       </c>
-      <c r="D19" s="107" t="s">
-        <v>510</v>
-      </c>
-      <c r="E19" s="107"/>
+      <c r="D19" s="113" t="s">
+        <v>500</v>
+      </c>
+      <c r="E19" s="113"/>
       <c r="F19" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G19" s="47">
         <v>0</v>
@@ -8211,28 +8190,28 @@
       <c r="J19" s="109"/>
       <c r="K19" s="109"/>
       <c r="L19" s="110"/>
-      <c r="N19" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="O19" s="26">
-        <v>10</v>
-      </c>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="114" t="s">
-        <v>177</v>
-      </c>
-      <c r="R19" s="115"/>
+      <c r="N19" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="O19" s="47">
+        <v>81</v>
+      </c>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="111" t="s">
+        <v>440</v>
+      </c>
+      <c r="R19" s="112"/>
     </row>
     <row r="20" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C20" s="48">
         <v>45876</v>
       </c>
-      <c r="D20" s="107" t="s">
-        <v>511</v>
-      </c>
-      <c r="E20" s="107"/>
+      <c r="D20" s="113" t="s">
+        <v>501</v>
+      </c>
+      <c r="E20" s="113"/>
       <c r="F20" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G20" s="47">
         <v>0</v>
@@ -8242,28 +8221,28 @@
       <c r="J20" s="109"/>
       <c r="K20" s="109"/>
       <c r="L20" s="110"/>
-      <c r="N20" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="O20" s="26">
-        <v>2</v>
-      </c>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="114" t="s">
-        <v>177</v>
-      </c>
-      <c r="R20" s="115"/>
+      <c r="N20" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="O20" s="4">
+        <v>10</v>
+      </c>
+      <c r="P20" s="4">
+        <v>1037.5999999999999</v>
+      </c>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="74"/>
     </row>
     <row r="21" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C21" s="48">
         <v>45876</v>
       </c>
-      <c r="D21" s="107" t="s">
-        <v>512</v>
-      </c>
-      <c r="E21" s="107"/>
+      <c r="D21" s="113" t="s">
+        <v>502</v>
+      </c>
+      <c r="E21" s="113"/>
       <c r="F21" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G21" s="47">
         <v>0</v>
@@ -8273,28 +8252,22 @@
       <c r="J21" s="109"/>
       <c r="K21" s="109"/>
       <c r="L21" s="110"/>
-      <c r="N21" s="46" t="s">
-        <v>507</v>
-      </c>
-      <c r="O21" s="47">
-        <v>81</v>
-      </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="112" t="s">
-        <v>449</v>
-      </c>
-      <c r="R21" s="113"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="74"/>
     </row>
     <row r="22" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C22" s="48">
         <v>45876</v>
       </c>
-      <c r="D22" s="107" t="s">
-        <v>513</v>
-      </c>
-      <c r="E22" s="107"/>
+      <c r="D22" s="113" t="s">
+        <v>503</v>
+      </c>
+      <c r="E22" s="113"/>
       <c r="F22" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G22" s="47">
         <v>0</v>
@@ -8304,15 +8277,9 @@
       <c r="J22" s="109"/>
       <c r="K22" s="109"/>
       <c r="L22" s="110"/>
-      <c r="N22" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="O22" s="4">
-        <v>10</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
       <c r="Q22" s="73"/>
       <c r="R22" s="74"/>
     </row>
@@ -8320,12 +8287,12 @@
       <c r="C23" s="48">
         <v>45876</v>
       </c>
-      <c r="D23" s="107" t="s">
-        <v>514</v>
-      </c>
-      <c r="E23" s="107"/>
+      <c r="D23" s="113" t="s">
+        <v>504</v>
+      </c>
+      <c r="E23" s="113"/>
       <c r="F23" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G23" s="47">
         <v>0</v>
@@ -8336,21 +8303,27 @@
       <c r="K23" s="109"/>
       <c r="L23" s="110"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="74"/>
+      <c r="O23" s="18">
+        <f>SUM(O12:O22)</f>
+        <v>312.5</v>
+      </c>
+      <c r="P23" s="5">
+        <f>SUM(P12:P20)</f>
+        <v>6732.6</v>
+      </c>
+      <c r="Q23" s="116"/>
+      <c r="R23" s="117"/>
     </row>
     <row r="24" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C24" s="48">
         <v>45876</v>
       </c>
-      <c r="D24" s="107" t="s">
-        <v>515</v>
-      </c>
-      <c r="E24" s="107"/>
+      <c r="D24" s="113" t="s">
+        <v>505</v>
+      </c>
+      <c r="E24" s="113"/>
       <c r="F24" s="46" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G24" s="47">
         <v>0</v>
@@ -8360,20 +8333,20 @@
       <c r="J24" s="109"/>
       <c r="K24" s="109"/>
       <c r="L24" s="110"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="74"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="49">
         <v>45877</v>
       </c>
-      <c r="D25" s="97" t="s">
-        <v>380</v>
-      </c>
-      <c r="E25" s="97"/>
+      <c r="D25" s="98" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" s="98"/>
       <c r="F25" s="28" t="s">
         <v>175</v>
       </c>
@@ -8381,32 +8354,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="29"/>
-      <c r="I25" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J25" s="100"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="101"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="18">
-        <f>SUM(O12:O24)</f>
-        <v>335.5</v>
-      </c>
-      <c r="P25" s="5">
-        <f>O25*$R$3</f>
-        <v>34120.35</v>
-      </c>
-      <c r="Q25" s="116"/>
-      <c r="R25" s="117"/>
+      <c r="I25" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="102"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="49">
         <v>45877</v>
       </c>
-      <c r="D26" s="97" t="s">
-        <v>379</v>
-      </c>
-      <c r="E26" s="97"/>
+      <c r="D26" s="98" t="s">
+        <v>370</v>
+      </c>
+      <c r="E26" s="98"/>
       <c r="F26" s="28" t="s">
         <v>175</v>
       </c>
@@ -8414,26 +8381,28 @@
         <v>0</v>
       </c>
       <c r="H26" s="29"/>
-      <c r="I26" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J26" s="100"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="101"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="83"/>
+      <c r="I26" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="102"/>
+      <c r="N26" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="64"/>
     </row>
     <row r="27" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C27" s="49">
         <v>45877</v>
       </c>
-      <c r="D27" s="97" t="s">
+      <c r="D27" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="97"/>
+      <c r="E27" s="98"/>
       <c r="F27" s="28" t="s">
         <v>175</v>
       </c>
@@ -8441,26 +8410,34 @@
         <v>0</v>
       </c>
       <c r="H27" s="29"/>
-      <c r="I27" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="101"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="84"/>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="84"/>
+      <c r="I27" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="102"/>
+      <c r="N27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="R27" s="80"/>
     </row>
     <row r="28" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C28" s="49">
         <v>45877</v>
       </c>
-      <c r="D28" s="97" t="s">
-        <v>378</v>
-      </c>
-      <c r="E28" s="97"/>
+      <c r="D28" s="98" t="s">
+        <v>369</v>
+      </c>
+      <c r="E28" s="98"/>
       <c r="F28" s="28" t="s">
         <v>175</v>
       </c>
@@ -8468,28 +8445,32 @@
         <v>0</v>
       </c>
       <c r="H28" s="29"/>
-      <c r="I28" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="101"/>
-      <c r="N28" s="63" t="s">
-        <v>38</v>
-      </c>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="64"/>
+      <c r="I28" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="102"/>
+      <c r="N28" s="13">
+        <v>45874</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="P28" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="74"/>
     </row>
     <row r="29" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C29" s="49">
         <v>45878</v>
       </c>
-      <c r="D29" s="97" t="s">
-        <v>429</v>
-      </c>
-      <c r="E29" s="97"/>
+      <c r="D29" s="98" t="s">
+        <v>420</v>
+      </c>
+      <c r="E29" s="98"/>
       <c r="F29" s="28" t="s">
         <v>175</v>
       </c>
@@ -8497,34 +8478,32 @@
         <v>0</v>
       </c>
       <c r="H29" s="29"/>
-      <c r="I29" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="101"/>
-      <c r="N29" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q29" s="79" t="s">
-        <v>7</v>
-      </c>
-      <c r="R29" s="80"/>
+      <c r="I29" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="N29" s="13">
+        <v>45900</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="P29" s="3">
+        <v>27979</v>
+      </c>
+      <c r="Q29" s="73"/>
+      <c r="R29" s="74"/>
     </row>
     <row r="30" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C30" s="49">
         <v>45878</v>
       </c>
-      <c r="D30" s="97" t="s">
-        <v>374</v>
-      </c>
-      <c r="E30" s="97"/>
+      <c r="D30" s="98" t="s">
+        <v>366</v>
+      </c>
+      <c r="E30" s="98"/>
       <c r="F30" s="28" t="s">
         <v>175</v>
       </c>
@@ -8532,20 +8511,17 @@
         <v>0</v>
       </c>
       <c r="H30" s="29"/>
-      <c r="I30" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="101"/>
-      <c r="N30" s="13">
-        <v>45874</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="P30" s="3">
-        <v>27000</v>
+      <c r="I30" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="102"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="5">
+        <f>P28+P29</f>
+        <v>54979</v>
       </c>
       <c r="Q30" s="73"/>
       <c r="R30" s="74"/>
@@ -8554,10 +8530,10 @@
       <c r="C31" s="49">
         <v>45878</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="100" t="s">
         <v>186</v>
       </c>
-      <c r="E31" s="101"/>
+      <c r="E31" s="102"/>
       <c r="F31" s="28" t="s">
         <v>175</v>
       </c>
@@ -8565,32 +8541,26 @@
         <v>0</v>
       </c>
       <c r="H31" s="29"/>
-      <c r="I31" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="101"/>
-      <c r="N31" s="13">
-        <v>45900</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="P31" s="3">
-        <v>27979</v>
-      </c>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="74"/>
+      <c r="I31" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="102"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="83"/>
+      <c r="R31" s="83"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="49">
         <v>45878</v>
       </c>
-      <c r="D32" s="97" t="s">
-        <v>377</v>
-      </c>
-      <c r="E32" s="97"/>
+      <c r="D32" s="98" t="s">
+        <v>368</v>
+      </c>
+      <c r="E32" s="98"/>
       <c r="F32" s="28" t="s">
         <v>175</v>
       </c>
@@ -8598,30 +8568,27 @@
         <v>0</v>
       </c>
       <c r="H32" s="29"/>
-      <c r="I32" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="101"/>
+      <c r="I32" s="100" t="s">
+        <v>535</v>
+      </c>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="102"/>
       <c r="M32" s="42"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="5">
-        <f>P30+P31</f>
-        <v>54979</v>
-      </c>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="74"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="84"/>
+      <c r="R32" s="84"/>
     </row>
     <row r="33" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C33" s="49">
         <v>45879</v>
       </c>
-      <c r="D33" s="97" t="s">
-        <v>375</v>
-      </c>
-      <c r="E33" s="97"/>
+      <c r="D33" s="98" t="s">
+        <v>367</v>
+      </c>
+      <c r="E33" s="98"/>
       <c r="F33" s="28" t="s">
         <v>175</v>
       </c>
@@ -8629,26 +8596,28 @@
         <v>0</v>
       </c>
       <c r="H33" s="29"/>
-      <c r="I33" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="101"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
+      <c r="I33" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="102"/>
+      <c r="N33" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
     </row>
     <row r="34" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C34" s="49">
         <v>45879</v>
       </c>
-      <c r="D34" s="97" t="s">
+      <c r="D34" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="E34" s="97"/>
+      <c r="E34" s="98"/>
       <c r="F34" s="28" t="s">
         <v>175</v>
       </c>
@@ -8656,90 +8625,89 @@
         <v>0</v>
       </c>
       <c r="H34" s="29"/>
-      <c r="I34" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="101"/>
-      <c r="N34" s="84"/>
-      <c r="O34" s="84"/>
-      <c r="P34" s="84"/>
-      <c r="Q34" s="84"/>
-      <c r="R34" s="84"/>
+      <c r="I34" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="102"/>
+      <c r="N34" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="35" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C35" s="49">
-        <v>45879</v>
-      </c>
-      <c r="D35" s="97" t="s">
-        <v>376</v>
-      </c>
-      <c r="E35" s="97"/>
+        <v>45880</v>
+      </c>
+      <c r="D35" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="98"/>
       <c r="F35" s="28" t="s">
         <v>175</v>
       </c>
       <c r="G35" s="29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H35" s="29"/>
-      <c r="I35" s="99" t="s">
-        <v>546</v>
-      </c>
-      <c r="J35" s="100"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="101"/>
-      <c r="N35" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="O35" s="61"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="101"/>
+      <c r="K35" s="101"/>
+      <c r="L35" s="102"/>
+      <c r="N35" s="3">
+        <v>300</v>
+      </c>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3">
+        <v>102.09</v>
+      </c>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5">
+        <v>30629</v>
+      </c>
     </row>
     <row r="36" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C36" s="49">
-        <v>45880</v>
-      </c>
-      <c r="D36" s="97" t="s">
-        <v>199</v>
-      </c>
-      <c r="E36" s="97"/>
+        <v>45881</v>
+      </c>
+      <c r="D36" s="98" t="s">
+        <v>517</v>
+      </c>
+      <c r="E36" s="98"/>
       <c r="F36" s="28" t="s">
         <v>175</v>
       </c>
       <c r="G36" s="29">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H36" s="29"/>
-      <c r="I36" s="99"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="101"/>
-      <c r="N36" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R36" s="6" t="s">
-        <v>446</v>
-      </c>
+      <c r="I36" s="100" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="102"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="49">
         <v>45881</v>
       </c>
-      <c r="D37" s="97" t="s">
-        <v>527</v>
-      </c>
-      <c r="E37" s="97"/>
+      <c r="D37" s="98" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="98"/>
       <c r="F37" s="28" t="s">
         <v>175</v>
       </c>
@@ -8747,26 +8715,21 @@
         <v>0</v>
       </c>
       <c r="H37" s="29"/>
-      <c r="I37" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="J37" s="100"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="101"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
+      <c r="I37" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="102"/>
     </row>
     <row r="38" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C38" s="49">
         <v>45881</v>
       </c>
-      <c r="D38" s="97" t="s">
-        <v>218</v>
-      </c>
-      <c r="E38" s="97"/>
+      <c r="D38" s="98" t="s">
+        <v>373</v>
+      </c>
+      <c r="E38" s="98"/>
       <c r="F38" s="28" t="s">
         <v>175</v>
       </c>
@@ -8774,21 +8737,25 @@
         <v>0</v>
       </c>
       <c r="H38" s="29"/>
-      <c r="I38" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="101"/>
+      <c r="I38" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J38" s="101"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="102"/>
+      <c r="N38" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="O38" s="65"/>
     </row>
     <row r="39" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C39" s="49">
         <v>45881</v>
       </c>
-      <c r="D39" s="97" t="s">
-        <v>382</v>
-      </c>
-      <c r="E39" s="97"/>
+      <c r="D39" s="98" t="s">
+        <v>372</v>
+      </c>
+      <c r="E39" s="98"/>
       <c r="F39" s="28" t="s">
         <v>175</v>
       </c>
@@ -8796,21 +8763,27 @@
         <v>0</v>
       </c>
       <c r="H39" s="29"/>
-      <c r="I39" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J39" s="100"/>
-      <c r="K39" s="100"/>
-      <c r="L39" s="101"/>
+      <c r="I39" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="102"/>
+      <c r="N39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="40" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C40" s="49">
-        <v>45881</v>
-      </c>
-      <c r="D40" s="97" t="s">
-        <v>381</v>
-      </c>
-      <c r="E40" s="97"/>
+        <v>45882</v>
+      </c>
+      <c r="D40" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="E40" s="98"/>
       <c r="F40" s="28" t="s">
         <v>175</v>
       </c>
@@ -8818,25 +8791,29 @@
         <v>0</v>
       </c>
       <c r="H40" s="29"/>
-      <c r="I40" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J40" s="100"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="101"/>
-      <c r="N40" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="O40" s="65"/>
+      <c r="I40" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J40" s="101"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="102"/>
+      <c r="N40" s="5">
+        <f>(F12+O23+G92+G121)*R3+O7+P30</f>
+        <v>210287.984</v>
+      </c>
+      <c r="O40" s="5">
+        <f>G12+O7+P30+P23+H92+H121</f>
+        <v>139359.57999999999</v>
+      </c>
     </row>
     <row r="41" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C41" s="49">
         <v>45882</v>
       </c>
-      <c r="D41" s="97" t="s">
-        <v>182</v>
-      </c>
-      <c r="E41" s="97"/>
+      <c r="D41" s="98" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="98"/>
       <c r="F41" s="28" t="s">
         <v>175</v>
       </c>
@@ -8844,27 +8821,21 @@
         <v>0</v>
       </c>
       <c r="H41" s="29"/>
-      <c r="I41" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J41" s="100"/>
-      <c r="K41" s="100"/>
-      <c r="L41" s="101"/>
-      <c r="N41" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="I41" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="102"/>
     </row>
     <row r="42" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C42" s="49">
         <v>45882</v>
       </c>
-      <c r="D42" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="E42" s="97"/>
+      <c r="D42" s="98" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="98"/>
       <c r="F42" s="28" t="s">
         <v>175</v>
       </c>
@@ -8872,95 +8843,87 @@
         <v>0</v>
       </c>
       <c r="H42" s="29"/>
-      <c r="I42" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J42" s="100"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="101"/>
-      <c r="N42" s="5">
-        <f>O7+G12+H93+P25+P32+R37+H123</f>
-        <v>215226.59600000002</v>
-      </c>
-      <c r="O42" s="5">
-        <f>G12+O7+P32</f>
-        <v>120291.68</v>
-      </c>
+      <c r="I42" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J42" s="101"/>
+      <c r="K42" s="101"/>
+      <c r="L42" s="102"/>
     </row>
     <row r="43" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C43" s="49">
-        <v>45882</v>
-      </c>
-      <c r="D43" s="97" t="s">
-        <v>224</v>
-      </c>
-      <c r="E43" s="97"/>
+        <v>45883</v>
+      </c>
+      <c r="D43" s="98" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="98"/>
       <c r="F43" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G43" s="29">
         <v>0</v>
       </c>
       <c r="H43" s="29"/>
-      <c r="I43" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J43" s="100"/>
-      <c r="K43" s="100"/>
-      <c r="L43" s="101"/>
+      <c r="I43" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="102"/>
     </row>
     <row r="44" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C44" s="49">
         <v>45883</v>
       </c>
-      <c r="D44" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="E44" s="97"/>
+      <c r="D44" s="98" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="98"/>
       <c r="F44" s="28" t="s">
         <v>176</v>
       </c>
       <c r="G44" s="29">
-        <v>0</v>
-      </c>
-      <c r="H44" s="29"/>
-      <c r="I44" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="101"/>
+        <v>18</v>
+      </c>
+      <c r="H44" s="29">
+        <v>1830.7</v>
+      </c>
+      <c r="I44" s="100"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="102"/>
     </row>
     <row r="45" spans="3:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="C45" s="49">
-        <v>45883</v>
-      </c>
-      <c r="D45" s="97" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" s="97"/>
+      <c r="C45" s="50">
+        <v>45884</v>
+      </c>
+      <c r="D45" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="E45" s="98"/>
       <c r="F45" s="28" t="s">
         <v>176</v>
       </c>
       <c r="G45" s="29">
-        <v>18</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" s="99"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="101"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="29"/>
+      <c r="I45" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="102"/>
     </row>
     <row r="46" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C46" s="50">
         <v>45884</v>
       </c>
-      <c r="D46" s="97" t="s">
-        <v>372</v>
-      </c>
-      <c r="E46" s="97"/>
+      <c r="D46" s="98" t="s">
+        <v>363</v>
+      </c>
+      <c r="E46" s="98"/>
       <c r="F46" s="28" t="s">
         <v>176</v>
       </c>
@@ -8968,21 +8931,21 @@
         <v>0</v>
       </c>
       <c r="H46" s="29"/>
-      <c r="I46" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J46" s="100"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="101"/>
+      <c r="I46" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J46" s="101"/>
+      <c r="K46" s="101"/>
+      <c r="L46" s="102"/>
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="50">
         <v>45884</v>
       </c>
-      <c r="D47" s="97" t="s">
-        <v>371</v>
-      </c>
-      <c r="E47" s="97"/>
+      <c r="D47" s="98" t="s">
+        <v>365</v>
+      </c>
+      <c r="E47" s="98"/>
       <c r="F47" s="28" t="s">
         <v>176</v>
       </c>
@@ -8990,21 +8953,21 @@
         <v>0</v>
       </c>
       <c r="H47" s="29"/>
-      <c r="I47" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J47" s="100"/>
-      <c r="K47" s="100"/>
-      <c r="L47" s="101"/>
+      <c r="I47" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J47" s="101"/>
+      <c r="K47" s="101"/>
+      <c r="L47" s="102"/>
     </row>
     <row r="48" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C48" s="50">
         <v>45884</v>
       </c>
-      <c r="D48" s="97" t="s">
-        <v>373</v>
-      </c>
-      <c r="E48" s="97"/>
+      <c r="D48" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="98"/>
       <c r="F48" s="28" t="s">
         <v>176</v>
       </c>
@@ -9012,21 +8975,21 @@
         <v>0</v>
       </c>
       <c r="H48" s="29"/>
-      <c r="I48" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="101"/>
+      <c r="I48" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J48" s="101"/>
+      <c r="K48" s="101"/>
+      <c r="L48" s="102"/>
     </row>
     <row r="49" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C49" s="50">
         <v>45884</v>
       </c>
-      <c r="D49" s="97" t="s">
-        <v>248</v>
-      </c>
-      <c r="E49" s="97"/>
+      <c r="D49" s="98" t="s">
+        <v>362</v>
+      </c>
+      <c r="E49" s="98"/>
       <c r="F49" s="28" t="s">
         <v>176</v>
       </c>
@@ -9034,289 +8997,293 @@
         <v>0</v>
       </c>
       <c r="H49" s="29"/>
-      <c r="I49" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J49" s="100"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="101"/>
+      <c r="I49" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="J49" s="101"/>
+      <c r="K49" s="101"/>
+      <c r="L49" s="102"/>
     </row>
     <row r="50" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C50" s="50">
-        <v>45884</v>
-      </c>
-      <c r="D50" s="97" t="s">
-        <v>370</v>
-      </c>
-      <c r="E50" s="97"/>
-      <c r="F50" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="G50" s="29">
-        <v>0</v>
-      </c>
-      <c r="H50" s="29"/>
-      <c r="I50" s="99" t="s">
-        <v>230</v>
-      </c>
-      <c r="J50" s="100"/>
-      <c r="K50" s="100"/>
-      <c r="L50" s="101"/>
+      <c r="C50" s="51">
+        <v>45885</v>
+      </c>
+      <c r="D50" s="99" t="s">
+        <v>196</v>
+      </c>
+      <c r="E50" s="99"/>
+      <c r="F50" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="G50" s="26">
+        <v>9</v>
+      </c>
+      <c r="H50" s="26"/>
+      <c r="I50" s="103" t="s">
+        <v>197</v>
+      </c>
+      <c r="J50" s="104"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="105"/>
     </row>
     <row r="51" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C51" s="51">
         <v>45885</v>
       </c>
-      <c r="D51" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="E51" s="98"/>
+      <c r="D51" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="E51" s="99"/>
       <c r="F51" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G51" s="26">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H51" s="26"/>
-      <c r="I51" s="102" t="s">
-        <v>198</v>
-      </c>
-      <c r="J51" s="103"/>
-      <c r="K51" s="103"/>
-      <c r="L51" s="104"/>
+      <c r="I51" s="103" t="s">
+        <v>541</v>
+      </c>
+      <c r="J51" s="104"/>
+      <c r="K51" s="104"/>
+      <c r="L51" s="105"/>
     </row>
     <row r="52" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C52" s="51">
-        <v>45885</v>
-      </c>
-      <c r="D52" s="98" t="s">
-        <v>364</v>
-      </c>
-      <c r="E52" s="98"/>
+        <v>45886</v>
+      </c>
+      <c r="D52" s="99" t="s">
+        <v>510</v>
+      </c>
+      <c r="E52" s="99"/>
       <c r="F52" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G52" s="26">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H52" s="26"/>
-      <c r="I52" s="102"/>
-      <c r="J52" s="103"/>
-      <c r="K52" s="103"/>
-      <c r="L52" s="104"/>
+      <c r="I52" s="103"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="105"/>
     </row>
     <row r="53" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C53" s="51">
         <v>45886</v>
       </c>
-      <c r="D53" s="98" t="s">
-        <v>520</v>
-      </c>
-      <c r="E53" s="98"/>
+      <c r="D53" s="99" t="s">
+        <v>511</v>
+      </c>
+      <c r="E53" s="99"/>
       <c r="F53" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G53" s="26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H53" s="26"/>
-      <c r="I53" s="102"/>
-      <c r="J53" s="103"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="104"/>
+      <c r="I53" s="103" t="s">
+        <v>540</v>
+      </c>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="105"/>
     </row>
     <row r="54" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C54" s="51">
         <v>45886</v>
       </c>
-      <c r="D54" s="98" t="s">
-        <v>521</v>
-      </c>
-      <c r="E54" s="98"/>
+      <c r="D54" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="99"/>
       <c r="F54" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G54" s="26">
-        <v>5</v>
-      </c>
-      <c r="H54" s="26"/>
-      <c r="I54" s="102"/>
-      <c r="J54" s="103"/>
-      <c r="K54" s="103"/>
-      <c r="L54" s="104"/>
+        <v>15.72</v>
+      </c>
+      <c r="H54" s="26">
+        <v>1598.8</v>
+      </c>
+      <c r="I54" s="103"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="105"/>
     </row>
     <row r="55" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C55" s="51">
-        <v>45886</v>
-      </c>
-      <c r="D55" s="98" t="s">
-        <v>219</v>
-      </c>
-      <c r="E55" s="98"/>
+        <v>45887</v>
+      </c>
+      <c r="D55" s="99" t="s">
+        <v>232</v>
+      </c>
+      <c r="E55" s="99"/>
       <c r="F55" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G55" s="26">
-        <v>15.72</v>
-      </c>
-      <c r="H55" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" s="102"/>
-      <c r="J55" s="103"/>
-      <c r="K55" s="103"/>
-      <c r="L55" s="104"/>
+        <v>6</v>
+      </c>
+      <c r="H55" s="26"/>
+      <c r="I55" s="103"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="105"/>
     </row>
     <row r="56" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C56" s="51">
         <v>45887</v>
       </c>
-      <c r="D56" s="98" t="s">
-        <v>239</v>
-      </c>
-      <c r="E56" s="98"/>
+      <c r="D56" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="E56" s="99"/>
       <c r="F56" s="25" t="s">
         <v>180</v>
       </c>
       <c r="G56" s="26">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H56" s="26"/>
-      <c r="I56" s="102"/>
-      <c r="J56" s="103"/>
-      <c r="K56" s="103"/>
-      <c r="L56" s="104"/>
+      <c r="I56" s="103"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="105"/>
     </row>
     <row r="57" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C57" s="51">
         <v>45887</v>
       </c>
-      <c r="D57" s="98" t="s">
-        <v>369</v>
-      </c>
-      <c r="E57" s="98"/>
+      <c r="D57" s="99" t="s">
+        <v>359</v>
+      </c>
+      <c r="E57" s="99"/>
       <c r="F57" s="25" t="s">
         <v>180</v>
       </c>
       <c r="G57" s="26">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="H57" s="26"/>
-      <c r="I57" s="102"/>
-      <c r="J57" s="103"/>
-      <c r="K57" s="103"/>
-      <c r="L57" s="104"/>
+      <c r="I57" s="103" t="s">
+        <v>419</v>
+      </c>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="105"/>
     </row>
     <row r="58" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C58" s="51">
         <v>45887</v>
       </c>
-      <c r="D58" s="98" t="s">
-        <v>367</v>
-      </c>
-      <c r="E58" s="98"/>
+      <c r="D58" s="99" t="s">
+        <v>360</v>
+      </c>
+      <c r="E58" s="99"/>
       <c r="F58" s="25" t="s">
         <v>180</v>
       </c>
       <c r="G58" s="26">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H58" s="26"/>
-      <c r="I58" s="102" t="s">
-        <v>428</v>
-      </c>
-      <c r="J58" s="103"/>
-      <c r="K58" s="103"/>
-      <c r="L58" s="104"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="105"/>
     </row>
     <row r="59" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C59" s="51">
-        <v>45887</v>
-      </c>
-      <c r="D59" s="98" t="s">
-        <v>368</v>
-      </c>
-      <c r="E59" s="98"/>
+        <v>45888</v>
+      </c>
+      <c r="D59" s="99" t="s">
+        <v>233</v>
+      </c>
+      <c r="E59" s="99"/>
       <c r="F59" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G59" s="26">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H59" s="26"/>
-      <c r="I59" s="102"/>
-      <c r="J59" s="103"/>
-      <c r="K59" s="103"/>
-      <c r="L59" s="104"/>
+      <c r="I59" s="103"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="104"/>
+      <c r="L59" s="105"/>
     </row>
     <row r="60" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C60" s="51">
         <v>45888</v>
       </c>
-      <c r="D60" s="98" t="s">
-        <v>240</v>
-      </c>
-      <c r="E60" s="98"/>
+      <c r="D60" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="99"/>
       <c r="F60" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G60" s="26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H60" s="26"/>
-      <c r="I60" s="102"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="103"/>
-      <c r="L60" s="104"/>
+      <c r="I60" s="103" t="s">
+        <v>541</v>
+      </c>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="105"/>
     </row>
     <row r="61" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C61" s="51">
-        <v>45888</v>
-      </c>
-      <c r="D61" s="98" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" s="98"/>
+        <v>45889</v>
+      </c>
+      <c r="D61" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="E61" s="99"/>
       <c r="F61" s="25" t="s">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="G61" s="26">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H61" s="26"/>
-      <c r="I61" s="102"/>
-      <c r="J61" s="103"/>
-      <c r="K61" s="103"/>
-      <c r="L61" s="104"/>
+      <c r="I61" s="103"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="105"/>
     </row>
     <row r="62" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C62" s="51">
-        <v>45889</v>
-      </c>
-      <c r="D62" s="98" t="s">
-        <v>365</v>
-      </c>
-      <c r="E62" s="98"/>
+        <v>45890</v>
+      </c>
+      <c r="D62" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="E62" s="99"/>
       <c r="F62" s="25" t="s">
-        <v>366</v>
+        <v>177</v>
       </c>
       <c r="G62" s="26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H62" s="26"/>
-      <c r="I62" s="102"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="103"/>
-      <c r="L62" s="104"/>
+      <c r="I62" s="103"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="104"/>
+      <c r="L62" s="105"/>
     </row>
     <row r="63" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C63" s="51">
         <v>45890</v>
       </c>
-      <c r="D63" s="98" t="s">
-        <v>220</v>
-      </c>
-      <c r="E63" s="98"/>
+      <c r="D63" s="99" t="s">
+        <v>512</v>
+      </c>
+      <c r="E63" s="99"/>
       <c r="F63" s="25" t="s">
         <v>177</v>
       </c>
@@ -9324,327 +9291,329 @@
         <v>8</v>
       </c>
       <c r="H63" s="26"/>
-      <c r="I63" s="102"/>
-      <c r="J63" s="103"/>
-      <c r="K63" s="103"/>
-      <c r="L63" s="104"/>
+      <c r="I63" s="103"/>
+      <c r="J63" s="104"/>
+      <c r="K63" s="104"/>
+      <c r="L63" s="105"/>
     </row>
     <row r="64" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C64" s="51">
-        <v>45890</v>
-      </c>
-      <c r="D64" s="98" t="s">
-        <v>522</v>
-      </c>
-      <c r="E64" s="98"/>
+        <v>45891</v>
+      </c>
+      <c r="D64" s="99" t="s">
+        <v>216</v>
+      </c>
+      <c r="E64" s="99"/>
       <c r="F64" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G64" s="26">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H64" s="26"/>
-      <c r="I64" s="102"/>
-      <c r="J64" s="103"/>
-      <c r="K64" s="103"/>
-      <c r="L64" s="104"/>
+      <c r="I64" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="J64" s="104"/>
+      <c r="K64" s="104"/>
+      <c r="L64" s="105"/>
     </row>
     <row r="65" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C65" s="51">
         <v>45891</v>
       </c>
-      <c r="D65" s="98" t="s">
-        <v>217</v>
-      </c>
-      <c r="E65" s="98"/>
+      <c r="D65" s="99" t="s">
+        <v>231</v>
+      </c>
+      <c r="E65" s="99"/>
       <c r="F65" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G65" s="26">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H65" s="26"/>
-      <c r="I65" s="102" t="s">
-        <v>234</v>
-      </c>
-      <c r="J65" s="103"/>
-      <c r="K65" s="103"/>
-      <c r="L65" s="104"/>
+      <c r="I65" s="103"/>
+      <c r="J65" s="104"/>
+      <c r="K65" s="104"/>
+      <c r="L65" s="105"/>
     </row>
     <row r="66" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C66" s="51">
         <v>45891</v>
       </c>
-      <c r="D66" s="98" t="s">
-        <v>235</v>
-      </c>
-      <c r="E66" s="98"/>
+      <c r="D66" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="E66" s="99"/>
       <c r="F66" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G66" s="26">
-        <v>5</v>
-      </c>
-      <c r="H66" s="26"/>
-      <c r="I66" s="102"/>
-      <c r="J66" s="103"/>
-      <c r="K66" s="103"/>
-      <c r="L66" s="104"/>
+        <v>15.72</v>
+      </c>
+      <c r="H66" s="26">
+        <v>1598.8</v>
+      </c>
+      <c r="I66" s="103"/>
+      <c r="J66" s="104"/>
+      <c r="K66" s="104"/>
+      <c r="L66" s="105"/>
     </row>
     <row r="67" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C67" s="51">
-        <v>45891</v>
-      </c>
-      <c r="D67" s="98" t="s">
-        <v>218</v>
-      </c>
-      <c r="E67" s="98"/>
-      <c r="F67" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="G67" s="26">
-        <v>15.72</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I67" s="102"/>
-      <c r="J67" s="103"/>
-      <c r="K67" s="103"/>
-      <c r="L67" s="104"/>
+      <c r="C67" s="52">
+        <v>45892</v>
+      </c>
+      <c r="D67" s="96" t="s">
+        <v>522</v>
+      </c>
+      <c r="E67" s="96"/>
+      <c r="F67" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="G67" s="23">
+        <v>8</v>
+      </c>
+      <c r="H67" s="23"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="33"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="34"/>
     </row>
     <row r="68" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C68" s="52">
-        <v>45892</v>
-      </c>
-      <c r="D68" s="93" t="s">
-        <v>532</v>
-      </c>
-      <c r="E68" s="93"/>
+        <v>45894</v>
+      </c>
+      <c r="D68" s="96" t="s">
+        <v>514</v>
+      </c>
+      <c r="E68" s="96"/>
       <c r="F68" s="22" t="s">
-        <v>533</v>
+        <v>179</v>
       </c>
       <c r="G68" s="23">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H68" s="23"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="34"/>
+      <c r="I68" s="94" t="s">
+        <v>414</v>
+      </c>
+      <c r="J68" s="97"/>
+      <c r="K68" s="97"/>
+      <c r="L68" s="95"/>
     </row>
     <row r="69" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C69" s="52">
         <v>45894</v>
       </c>
-      <c r="D69" s="93" t="s">
-        <v>524</v>
-      </c>
-      <c r="E69" s="93"/>
+      <c r="D69" s="96" t="s">
+        <v>513</v>
+      </c>
+      <c r="E69" s="96"/>
       <c r="F69" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G69" s="23">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H69" s="23"/>
-      <c r="I69" s="94" t="s">
-        <v>423</v>
-      </c>
-      <c r="J69" s="96"/>
-      <c r="K69" s="96"/>
+      <c r="I69" s="94"/>
+      <c r="J69" s="97"/>
+      <c r="K69" s="97"/>
       <c r="L69" s="95"/>
     </row>
     <row r="70" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C70" s="52">
         <v>45894</v>
       </c>
-      <c r="D70" s="93" t="s">
-        <v>523</v>
-      </c>
-      <c r="E70" s="93"/>
+      <c r="D70" s="96" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="96"/>
       <c r="F70" s="22" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G70" s="23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H70" s="23"/>
       <c r="I70" s="94"/>
-      <c r="J70" s="96"/>
-      <c r="K70" s="96"/>
+      <c r="J70" s="97"/>
+      <c r="K70" s="97"/>
       <c r="L70" s="95"/>
     </row>
     <row r="71" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C71" s="52">
-        <v>45894</v>
-      </c>
-      <c r="D71" s="93" t="s">
-        <v>191</v>
-      </c>
-      <c r="E71" s="93"/>
+        <v>45895</v>
+      </c>
+      <c r="D71" s="96" t="s">
+        <v>352</v>
+      </c>
+      <c r="E71" s="96"/>
       <c r="F71" s="22" t="s">
         <v>189</v>
       </c>
       <c r="G71" s="23">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H71" s="23"/>
       <c r="I71" s="94"/>
-      <c r="J71" s="96"/>
-      <c r="K71" s="96"/>
+      <c r="J71" s="97"/>
+      <c r="K71" s="97"/>
       <c r="L71" s="95"/>
     </row>
     <row r="72" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C72" s="52">
         <v>45895</v>
       </c>
-      <c r="D72" s="93" t="s">
-        <v>360</v>
-      </c>
-      <c r="E72" s="93"/>
+      <c r="D72" s="96" t="s">
+        <v>518</v>
+      </c>
+      <c r="E72" s="96"/>
       <c r="F72" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G72" s="23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H72" s="23"/>
       <c r="I72" s="94"/>
-      <c r="J72" s="96"/>
-      <c r="K72" s="96"/>
+      <c r="J72" s="97"/>
+      <c r="K72" s="97"/>
       <c r="L72" s="95"/>
     </row>
     <row r="73" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C73" s="52">
         <v>45895</v>
       </c>
-      <c r="D73" s="93" t="s">
-        <v>528</v>
-      </c>
-      <c r="E73" s="93"/>
+      <c r="D73" s="96" t="s">
+        <v>353</v>
+      </c>
+      <c r="E73" s="96"/>
       <c r="F73" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G73" s="23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73" s="23"/>
       <c r="I73" s="94"/>
-      <c r="J73" s="96"/>
-      <c r="K73" s="96"/>
+      <c r="J73" s="97"/>
+      <c r="K73" s="97"/>
       <c r="L73" s="95"/>
     </row>
     <row r="74" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C74" s="52">
         <v>45895</v>
       </c>
-      <c r="D74" s="93" t="s">
-        <v>361</v>
-      </c>
-      <c r="E74" s="93"/>
+      <c r="D74" s="96" t="s">
+        <v>354</v>
+      </c>
+      <c r="E74" s="96"/>
       <c r="F74" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G74" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H74" s="23"/>
       <c r="I74" s="94"/>
-      <c r="J74" s="96"/>
-      <c r="K74" s="96"/>
+      <c r="J74" s="97"/>
+      <c r="K74" s="97"/>
       <c r="L74" s="95"/>
     </row>
     <row r="75" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C75" s="52">
-        <v>45895</v>
-      </c>
-      <c r="D75" s="93" t="s">
-        <v>362</v>
-      </c>
-      <c r="E75" s="93"/>
+        <v>45896</v>
+      </c>
+      <c r="D75" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="E75" s="96"/>
       <c r="F75" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G75" s="23">
         <v>10</v>
       </c>
       <c r="H75" s="23"/>
       <c r="I75" s="94"/>
-      <c r="J75" s="96"/>
-      <c r="K75" s="96"/>
+      <c r="J75" s="97"/>
+      <c r="K75" s="97"/>
       <c r="L75" s="95"/>
     </row>
     <row r="76" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C76" s="52">
         <v>45896</v>
       </c>
-      <c r="D76" s="93" t="s">
-        <v>214</v>
-      </c>
-      <c r="E76" s="93"/>
+      <c r="D76" s="96" t="s">
+        <v>355</v>
+      </c>
+      <c r="E76" s="96"/>
       <c r="F76" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G76" s="23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H76" s="23"/>
       <c r="I76" s="94"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
+      <c r="J76" s="97"/>
+      <c r="K76" s="97"/>
       <c r="L76" s="95"/>
     </row>
     <row r="77" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C77" s="52">
         <v>45896</v>
       </c>
-      <c r="D77" s="93" t="s">
-        <v>363</v>
-      </c>
-      <c r="E77" s="93"/>
+      <c r="D77" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="96"/>
       <c r="F77" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G77" s="23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H77" s="23"/>
-      <c r="I77" s="94"/>
-      <c r="J77" s="96"/>
-      <c r="K77" s="96"/>
+      <c r="I77" s="94" t="s">
+        <v>237</v>
+      </c>
+      <c r="J77" s="97"/>
+      <c r="K77" s="97"/>
       <c r="L77" s="95"/>
     </row>
     <row r="78" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C78" s="52">
-        <v>45896</v>
-      </c>
-      <c r="D78" s="93" t="s">
-        <v>243</v>
-      </c>
-      <c r="E78" s="93"/>
+        <v>45897</v>
+      </c>
+      <c r="D78" s="96" t="s">
+        <v>351</v>
+      </c>
+      <c r="E78" s="96"/>
       <c r="F78" s="22" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G78" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H78" s="23"/>
       <c r="I78" s="94" t="s">
-        <v>245</v>
-      </c>
-      <c r="J78" s="96"/>
-      <c r="K78" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J78" s="97"/>
+      <c r="K78" s="97"/>
       <c r="L78" s="95"/>
     </row>
     <row r="79" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C79" s="52">
         <v>45897</v>
       </c>
-      <c r="D79" s="93" t="s">
-        <v>359</v>
-      </c>
-      <c r="E79" s="93"/>
+      <c r="D79" s="96" t="s">
+        <v>418</v>
+      </c>
+      <c r="E79" s="96"/>
       <c r="F79" s="22" t="s">
         <v>179</v>
       </c>
@@ -9653,20 +9622,20 @@
       </c>
       <c r="H79" s="23"/>
       <c r="I79" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J79" s="96"/>
-      <c r="K79" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J79" s="97"/>
+      <c r="K79" s="97"/>
       <c r="L79" s="95"/>
     </row>
     <row r="80" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C80" s="52">
         <v>45897</v>
       </c>
-      <c r="D80" s="93" t="s">
-        <v>427</v>
-      </c>
-      <c r="E80" s="93"/>
+      <c r="D80" s="96" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" s="96"/>
       <c r="F80" s="22" t="s">
         <v>179</v>
       </c>
@@ -9675,108 +9644,108 @@
       </c>
       <c r="H80" s="23"/>
       <c r="I80" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J80" s="96"/>
-      <c r="K80" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J80" s="97"/>
+      <c r="K80" s="97"/>
       <c r="L80" s="95"/>
     </row>
     <row r="81" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C81" s="52">
         <v>45897</v>
       </c>
-      <c r="D81" s="93" t="s">
+      <c r="D81" s="96" t="s">
         <v>211</v>
       </c>
-      <c r="E81" s="93"/>
+      <c r="E81" s="96"/>
       <c r="F81" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G81" s="23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H81" s="23"/>
       <c r="I81" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J81" s="96"/>
-      <c r="K81" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J81" s="97"/>
+      <c r="K81" s="97"/>
       <c r="L81" s="95"/>
     </row>
     <row r="82" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C82" s="52">
         <v>45897</v>
       </c>
-      <c r="D82" s="93" t="s">
-        <v>212</v>
-      </c>
-      <c r="E82" s="93"/>
+      <c r="D82" s="96" t="s">
+        <v>416</v>
+      </c>
+      <c r="E82" s="96"/>
       <c r="F82" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G82" s="23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H82" s="23"/>
       <c r="I82" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J82" s="96"/>
-      <c r="K82" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J82" s="97"/>
+      <c r="K82" s="97"/>
       <c r="L82" s="95"/>
     </row>
     <row r="83" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C83" s="52">
-        <v>45897</v>
-      </c>
-      <c r="D83" s="93" t="s">
-        <v>425</v>
-      </c>
-      <c r="E83" s="93"/>
+        <v>45898</v>
+      </c>
+      <c r="D83" s="96" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" s="96"/>
       <c r="F83" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G83" s="23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H83" s="23"/>
       <c r="I83" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J83" s="96"/>
-      <c r="K83" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J83" s="97"/>
+      <c r="K83" s="97"/>
       <c r="L83" s="95"/>
     </row>
     <row r="84" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C84" s="52">
         <v>45898</v>
       </c>
-      <c r="D84" s="93" t="s">
-        <v>205</v>
-      </c>
-      <c r="E84" s="93"/>
+      <c r="D84" s="96" t="s">
+        <v>516</v>
+      </c>
+      <c r="E84" s="96"/>
       <c r="F84" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G84" s="23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H84" s="23"/>
       <c r="I84" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J84" s="96"/>
-      <c r="K84" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J84" s="97"/>
+      <c r="K84" s="97"/>
       <c r="L84" s="95"/>
     </row>
     <row r="85" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C85" s="52">
         <v>45898</v>
       </c>
-      <c r="D85" s="93" t="s">
-        <v>526</v>
-      </c>
-      <c r="E85" s="93"/>
+      <c r="D85" s="96" t="s">
+        <v>417</v>
+      </c>
+      <c r="E85" s="96"/>
       <c r="F85" s="22" t="s">
         <v>179</v>
       </c>
@@ -9785,20 +9754,20 @@
       </c>
       <c r="H85" s="23"/>
       <c r="I85" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J85" s="96"/>
-      <c r="K85" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J85" s="97"/>
+      <c r="K85" s="97"/>
       <c r="L85" s="95"/>
     </row>
     <row r="86" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C86" s="52">
         <v>45898</v>
       </c>
-      <c r="D86" s="93" t="s">
-        <v>426</v>
-      </c>
-      <c r="E86" s="93"/>
+      <c r="D86" s="96" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="96"/>
       <c r="F86" s="22" t="s">
         <v>179</v>
       </c>
@@ -9807,20 +9776,20 @@
       </c>
       <c r="H86" s="23"/>
       <c r="I86" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J86" s="96"/>
-      <c r="K86" s="96"/>
+        <v>537</v>
+      </c>
+      <c r="J86" s="97"/>
+      <c r="K86" s="97"/>
       <c r="L86" s="95"/>
     </row>
     <row r="87" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C87" s="52">
         <v>45898</v>
       </c>
-      <c r="D87" s="93" t="s">
-        <v>207</v>
-      </c>
-      <c r="E87" s="93"/>
+      <c r="D87" s="94" t="s">
+        <v>515</v>
+      </c>
+      <c r="E87" s="95"/>
       <c r="F87" s="22" t="s">
         <v>179</v>
       </c>
@@ -9829,18 +9798,18 @@
       </c>
       <c r="H87" s="23"/>
       <c r="I87" s="94" t="s">
-        <v>548</v>
-      </c>
-      <c r="J87" s="96"/>
-      <c r="K87" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J87" s="97"/>
+      <c r="K87" s="97"/>
       <c r="L87" s="95"/>
     </row>
     <row r="88" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C88" s="52">
-        <v>45898</v>
+        <v>45899</v>
       </c>
       <c r="D88" s="94" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E88" s="95"/>
       <c r="F88" s="22" t="s">
@@ -9850,492 +9819,478 @@
         <v>0</v>
       </c>
       <c r="H88" s="23"/>
-      <c r="I88" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J88" s="96"/>
-      <c r="K88" s="96"/>
-      <c r="L88" s="95"/>
+      <c r="I88" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="J88" s="33"/>
+      <c r="K88" s="33"/>
+      <c r="L88" s="34"/>
     </row>
     <row r="89" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C89" s="52">
         <v>45899</v>
       </c>
-      <c r="D89" s="94" t="s">
-        <v>534</v>
-      </c>
-      <c r="E89" s="95"/>
+      <c r="D89" s="96" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="96"/>
       <c r="F89" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G89" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H89" s="23"/>
-      <c r="I89" s="32" t="s">
-        <v>547</v>
-      </c>
-      <c r="J89" s="33"/>
-      <c r="K89" s="33"/>
-      <c r="L89" s="34"/>
+      <c r="I89" s="94" t="s">
+        <v>536</v>
+      </c>
+      <c r="J89" s="97"/>
+      <c r="K89" s="97"/>
+      <c r="L89" s="95"/>
     </row>
     <row r="90" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C90" s="52">
         <v>45899</v>
       </c>
-      <c r="D90" s="93" t="s">
-        <v>244</v>
-      </c>
-      <c r="E90" s="93"/>
+      <c r="D90" s="96" t="s">
+        <v>415</v>
+      </c>
+      <c r="E90" s="96"/>
       <c r="F90" s="22" t="s">
         <v>179</v>
       </c>
       <c r="G90" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H90" s="23"/>
       <c r="I90" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J90" s="96"/>
-      <c r="K90" s="96"/>
+        <v>536</v>
+      </c>
+      <c r="J90" s="97"/>
+      <c r="K90" s="97"/>
       <c r="L90" s="95"/>
     </row>
     <row r="91" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C91" s="52">
-        <v>45899</v>
-      </c>
-      <c r="D91" s="93" t="s">
-        <v>424</v>
-      </c>
-      <c r="E91" s="93"/>
-      <c r="F91" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="G91" s="23">
-        <v>0</v>
-      </c>
-      <c r="H91" s="23"/>
-      <c r="I91" s="94" t="s">
-        <v>547</v>
-      </c>
-      <c r="J91" s="96"/>
-      <c r="K91" s="96"/>
-      <c r="L91" s="95"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="78"/>
+      <c r="E91" s="78"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="85"/>
+      <c r="J91" s="86"/>
+      <c r="K91" s="86"/>
+      <c r="L91" s="87"/>
     </row>
     <row r="92" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C92" s="1"/>
       <c r="D92" s="78"/>
       <c r="E92" s="78"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="85"/>
-      <c r="J92" s="86"/>
-      <c r="K92" s="86"/>
-      <c r="L92" s="87"/>
-    </row>
-    <row r="93" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C93" s="1"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="78"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="4">
-        <f>SUM(G17:G91)</f>
-        <v>412.94000000000005</v>
-      </c>
-      <c r="H93" s="5">
-        <f>G93*$R$3</f>
-        <v>41995.998000000007</v>
-      </c>
-      <c r="I93" s="67"/>
-      <c r="J93" s="68"/>
-      <c r="K93" s="68"/>
-      <c r="L93" s="69"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="4">
+        <f>SUM(G17:G90)</f>
+        <v>403.94000000000005</v>
+      </c>
+      <c r="H92" s="5">
+        <f>SUM(H17:H90)</f>
+        <v>5028.3</v>
+      </c>
+      <c r="I92" s="67"/>
+      <c r="J92" s="68"/>
+      <c r="K92" s="68"/>
+      <c r="L92" s="69"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C93" s="83"/>
+      <c r="D93" s="83"/>
+      <c r="E93" s="83"/>
+      <c r="F93" s="83"/>
+      <c r="G93" s="83"/>
+      <c r="H93" s="83"/>
+      <c r="I93" s="83"/>
+      <c r="J93" s="83"/>
+      <c r="K93" s="83"/>
+      <c r="L93" s="83"/>
     </row>
     <row r="94" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C94" s="83"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="83"/>
-      <c r="F94" s="83"/>
-      <c r="G94" s="83"/>
-      <c r="H94" s="83"/>
-      <c r="I94" s="83"/>
-      <c r="J94" s="83"/>
-      <c r="K94" s="83"/>
-      <c r="L94" s="83"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C95" s="84"/>
-      <c r="D95" s="84"/>
-      <c r="E95" s="84"/>
-      <c r="F95" s="84"/>
-      <c r="G95" s="84"/>
-      <c r="H95" s="84"/>
-      <c r="I95" s="84"/>
-      <c r="J95" s="84"/>
-      <c r="K95" s="84"/>
-      <c r="L95" s="84"/>
+      <c r="C94" s="84"/>
+      <c r="D94" s="84"/>
+      <c r="E94" s="84"/>
+      <c r="F94" s="84"/>
+      <c r="G94" s="84"/>
+      <c r="H94" s="84"/>
+      <c r="I94" s="84"/>
+      <c r="J94" s="84"/>
+      <c r="K94" s="84"/>
+      <c r="L94" s="84"/>
+    </row>
+    <row r="95" spans="3:12" ht="19" x14ac:dyDescent="0.25">
+      <c r="C95" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="64"/>
+      <c r="E95" s="64"/>
+      <c r="F95" s="64"/>
+      <c r="G95" s="64"/>
+      <c r="H95" s="64"/>
+      <c r="I95" s="64"/>
+      <c r="J95" s="64"/>
+      <c r="K95" s="64"/>
+      <c r="L95" s="65"/>
     </row>
     <row r="96" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C96" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D96" s="64"/>
-      <c r="E96" s="64"/>
-      <c r="F96" s="64"/>
-      <c r="G96" s="64"/>
-      <c r="H96" s="64"/>
-      <c r="I96" s="64"/>
-      <c r="J96" s="64"/>
-      <c r="K96" s="64"/>
-      <c r="L96" s="65"/>
+      <c r="C96" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="J96" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="K96" s="62"/>
+      <c r="L96" s="62"/>
     </row>
     <row r="97" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C97" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J97" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="K97" s="62"/>
-      <c r="L97" s="62"/>
+      <c r="C97" s="45">
+        <v>45877</v>
+      </c>
+      <c r="D97" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E97" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F97" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="G97" s="46">
+        <v>30</v>
+      </c>
+      <c r="H97" s="46">
+        <v>3065</v>
+      </c>
+      <c r="I97" s="46" t="s">
+        <v>509</v>
+      </c>
+      <c r="J97" s="113" t="s">
+        <v>526</v>
+      </c>
+      <c r="K97" s="113"/>
+      <c r="L97" s="113"/>
     </row>
     <row r="98" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C98" s="45">
-        <v>45877</v>
-      </c>
-      <c r="D98" s="46" t="s">
-        <v>449</v>
+      <c r="C98" s="27">
+        <v>45883</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>175</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F98" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G98" s="46">
-        <v>30</v>
-      </c>
-      <c r="H98" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="F98" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="G98" s="28">
         <v>12</v>
       </c>
-      <c r="I98" s="46" t="s">
-        <v>519</v>
-      </c>
-      <c r="J98" s="107" t="s">
-        <v>536</v>
-      </c>
-      <c r="K98" s="107"/>
-      <c r="L98" s="107"/>
+      <c r="H98" s="28">
+        <v>1220</v>
+      </c>
+      <c r="I98" s="28"/>
+      <c r="J98" s="98"/>
+      <c r="K98" s="98"/>
+      <c r="L98" s="98"/>
     </row>
     <row r="99" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C99" s="27">
-        <v>45883</v>
+        <v>45885</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E99" s="28" t="s">
         <v>176</v>
       </c>
+      <c r="E99" s="25" t="s">
+        <v>177</v>
+      </c>
       <c r="F99" s="28" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="G99" s="28">
-        <v>12</v>
-      </c>
-      <c r="H99" s="28" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="H99" s="28">
+        <v>1914</v>
       </c>
       <c r="I99" s="28"/>
-      <c r="J99" s="97"/>
-      <c r="K99" s="97"/>
-      <c r="L99" s="97"/>
+      <c r="J99" s="98" t="s">
+        <v>525</v>
+      </c>
+      <c r="K99" s="98"/>
+      <c r="L99" s="98"/>
     </row>
     <row r="100" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C100" s="27">
-        <v>45885</v>
-      </c>
-      <c r="D100" s="28" t="s">
-        <v>176</v>
+      <c r="C100" s="24">
+        <v>45887</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>177</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="F100" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="G100" s="28">
-        <v>19</v>
-      </c>
-      <c r="H100" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="I100" s="28"/>
-      <c r="J100" s="97" t="s">
-        <v>535</v>
-      </c>
-      <c r="K100" s="97"/>
-      <c r="L100" s="97"/>
+        <v>180</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G100" s="25">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H100" s="25"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="99"/>
+      <c r="K100" s="99"/>
+      <c r="L100" s="99"/>
     </row>
     <row r="101" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C101" s="24">
         <v>45887</v>
       </c>
       <c r="D101" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E101" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="E101" s="25" t="s">
-        <v>180</v>
-      </c>
       <c r="F101" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G101" s="25">
         <v>2.4500000000000002</v>
       </c>
       <c r="H101" s="25"/>
-      <c r="I101" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="J101" s="98"/>
-      <c r="K101" s="98"/>
-      <c r="L101" s="98"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="99"/>
+      <c r="K101" s="99"/>
+      <c r="L101" s="99"/>
     </row>
     <row r="102" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C102" s="24">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G102" s="25">
-        <v>2.4500000000000002</v>
+        <v>4.32</v>
       </c>
       <c r="H102" s="25"/>
-      <c r="I102" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="J102" s="98"/>
-      <c r="K102" s="98"/>
-      <c r="L102" s="98"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="99"/>
+      <c r="K102" s="99"/>
+      <c r="L102" s="99"/>
     </row>
     <row r="103" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C103" s="24">
         <v>45888</v>
       </c>
       <c r="D103" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E103" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="E103" s="25" t="s">
-        <v>181</v>
-      </c>
       <c r="F103" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G103" s="25">
         <v>4.32</v>
       </c>
       <c r="H103" s="25"/>
-      <c r="I103" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="J103" s="98"/>
-      <c r="K103" s="98"/>
-      <c r="L103" s="98"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="99"/>
+      <c r="K103" s="99"/>
+      <c r="L103" s="99"/>
     </row>
     <row r="104" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C104" s="24">
-        <v>45888</v>
+      <c r="C104" s="53">
+        <v>45889</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="G104" s="25">
-        <v>4.32</v>
+        <v>8</v>
       </c>
       <c r="H104" s="25"/>
-      <c r="I104" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="J104" s="98"/>
-      <c r="K104" s="98"/>
-      <c r="L104" s="98"/>
+      <c r="I104" s="25"/>
+      <c r="J104" s="99"/>
+      <c r="K104" s="99"/>
+      <c r="L104" s="99"/>
     </row>
     <row r="105" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C105" s="53">
         <v>45889</v>
       </c>
       <c r="D105" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="E105" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="E105" s="25" t="s">
-        <v>366</v>
-      </c>
       <c r="F105" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G105" s="25">
         <v>8</v>
       </c>
       <c r="H105" s="25"/>
       <c r="I105" s="25"/>
-      <c r="J105" s="98"/>
-      <c r="K105" s="98"/>
-      <c r="L105" s="98"/>
+      <c r="J105" s="99"/>
+      <c r="K105" s="99"/>
+      <c r="L105" s="99"/>
     </row>
     <row r="106" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C106" s="53">
-        <v>45889</v>
+      <c r="C106" s="21">
+        <v>45892</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="E106" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="F106" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="G106" s="25">
-        <v>8</v>
-      </c>
-      <c r="H106" s="25"/>
-      <c r="I106" s="25"/>
-      <c r="J106" s="98"/>
-      <c r="K106" s="98"/>
-      <c r="L106" s="98"/>
+      <c r="E106" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="F106" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G106" s="22">
+        <v>11</v>
+      </c>
+      <c r="H106" s="22">
+        <v>1108</v>
+      </c>
+      <c r="I106" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J106" s="96" t="s">
+        <v>525</v>
+      </c>
+      <c r="K106" s="96"/>
+      <c r="L106" s="96"/>
     </row>
     <row r="107" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C107" s="21">
         <v>45892</v>
       </c>
-      <c r="D107" s="25" t="s">
-        <v>177</v>
+      <c r="D107" s="22" t="s">
+        <v>178</v>
       </c>
       <c r="E107" s="22" t="s">
-        <v>178</v>
+        <v>523</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G107" s="22">
-        <v>11</v>
-      </c>
-      <c r="H107" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="I107" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="J107" s="93" t="s">
-        <v>535</v>
-      </c>
-      <c r="K107" s="93"/>
-      <c r="L107" s="93"/>
+        <v>3</v>
+      </c>
+      <c r="H107" s="22"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="96"/>
+      <c r="K107" s="96"/>
+      <c r="L107" s="96"/>
     </row>
     <row r="108" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C108" s="21">
         <v>45892</v>
       </c>
       <c r="D108" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="E108" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="E108" s="22" t="s">
-        <v>533</v>
-      </c>
       <c r="F108" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G108" s="22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H108" s="22"/>
-      <c r="I108" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="J108" s="93"/>
-      <c r="K108" s="93"/>
-      <c r="L108" s="93"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="96"/>
+      <c r="K108" s="96"/>
+      <c r="L108" s="96"/>
     </row>
     <row r="109" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C109" s="21">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>533</v>
+        <v>178</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F109" s="22" t="s">
         <v>195</v>
       </c>
       <c r="G109" s="22">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="H109" s="22"/>
-      <c r="I109" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="J109" s="93"/>
-      <c r="K109" s="93"/>
-      <c r="L109" s="93"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="96"/>
+      <c r="K109" s="96"/>
+      <c r="L109" s="96"/>
     </row>
     <row r="110" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C110" s="21">
         <v>45893</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E110" s="22" t="s">
         <v>192</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G110" s="22">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="H110" s="22"/>
-      <c r="I110" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="J110" s="93"/>
-      <c r="K110" s="93"/>
-      <c r="L110" s="93"/>
+      <c r="I110" s="22"/>
+      <c r="J110" s="96"/>
+      <c r="K110" s="96"/>
+      <c r="L110" s="96"/>
     </row>
     <row r="111" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C111" s="21">
@@ -10345,139 +10300,135 @@
         <v>192</v>
       </c>
       <c r="E111" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F111" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" s="22">
+        <v>15</v>
+      </c>
+      <c r="H111" s="22"/>
+      <c r="I111" s="22"/>
+      <c r="J111" s="94" t="s">
         <v>193</v>
       </c>
-      <c r="F111" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="G111" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="H111" s="22"/>
-      <c r="I111" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="J111" s="93"/>
-      <c r="K111" s="93"/>
-      <c r="L111" s="93"/>
+      <c r="K111" s="97"/>
+      <c r="L111" s="95"/>
     </row>
     <row r="112" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C112" s="21">
         <v>45893</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E112" s="22" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="G112" s="22">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="22"/>
-      <c r="J112" s="94" t="s">
-        <v>194</v>
-      </c>
+      <c r="J112" s="96"/>
       <c r="K112" s="96"/>
-      <c r="L112" s="95"/>
+      <c r="L112" s="96"/>
     </row>
     <row r="113" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C113" s="21">
         <v>45893</v>
       </c>
       <c r="D113" s="22" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="E113" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G113" s="22">
-        <v>1.5</v>
+        <v>25</v>
       </c>
       <c r="H113" s="22"/>
       <c r="I113" s="22"/>
-      <c r="J113" s="93"/>
-      <c r="K113" s="93"/>
-      <c r="L113" s="93"/>
+      <c r="J113" s="96"/>
+      <c r="K113" s="96"/>
+      <c r="L113" s="96"/>
     </row>
     <row r="114" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C114" s="21">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E114" s="22" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G114" s="22">
-        <v>25</v>
+        <v>2.6</v>
       </c>
       <c r="H114" s="22"/>
-      <c r="I114" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="J114" s="93"/>
-      <c r="K114" s="93"/>
-      <c r="L114" s="93"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="96"/>
+      <c r="K114" s="96"/>
+      <c r="L114" s="96"/>
     </row>
     <row r="115" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C115" s="21">
         <v>45894</v>
       </c>
       <c r="D115" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E115" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="E115" s="22" t="s">
-        <v>189</v>
-      </c>
       <c r="F115" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G115" s="22">
         <v>2.6</v>
       </c>
       <c r="H115" s="22"/>
       <c r="I115" s="22"/>
-      <c r="J115" s="93"/>
-      <c r="K115" s="93"/>
-      <c r="L115" s="93"/>
+      <c r="J115" s="96"/>
+      <c r="K115" s="96"/>
+      <c r="L115" s="96"/>
     </row>
     <row r="116" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C116" s="21">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="D116" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="E116" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="E116" s="22" t="s">
-        <v>179</v>
-      </c>
       <c r="F116" s="22" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="G116" s="22">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H116" s="22"/>
       <c r="I116" s="22"/>
-      <c r="J116" s="93"/>
-      <c r="K116" s="93"/>
-      <c r="L116" s="93"/>
+      <c r="J116" s="96"/>
+      <c r="K116" s="96"/>
+      <c r="L116" s="96"/>
     </row>
     <row r="117" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C117" s="21">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="D117" s="22" t="s">
         <v>189</v>
@@ -10486,357 +10437,308 @@
         <v>179</v>
       </c>
       <c r="F117" s="22" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="G117" s="22">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H117" s="22"/>
       <c r="I117" s="22"/>
-      <c r="J117" s="93"/>
-      <c r="K117" s="93"/>
-      <c r="L117" s="93"/>
+      <c r="J117" s="96"/>
+      <c r="K117" s="96"/>
+      <c r="L117" s="96"/>
     </row>
     <row r="118" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C118" s="21">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="D118" s="22" t="s">
         <v>179</v>
       </c>
       <c r="E118" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F118" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G118" s="22">
         <v>5.2</v>
       </c>
       <c r="H118" s="22"/>
       <c r="I118" s="22"/>
-      <c r="J118" s="93"/>
-      <c r="K118" s="93"/>
-      <c r="L118" s="93"/>
+      <c r="J118" s="96"/>
+      <c r="K118" s="96"/>
+      <c r="L118" s="96"/>
     </row>
     <row r="119" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C119" s="21">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="D119" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E119" s="22" t="s">
         <v>179</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G119" s="22">
         <v>5.2</v>
       </c>
       <c r="H119" s="22"/>
       <c r="I119" s="22"/>
-      <c r="J119" s="93"/>
-      <c r="K119" s="93"/>
-      <c r="L119" s="93"/>
-    </row>
-    <row r="120" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C120" s="21">
-        <v>45896</v>
-      </c>
-      <c r="D120" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="E120" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="F120" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="G120" s="22">
-        <v>5.2</v>
-      </c>
-      <c r="H120" s="22"/>
-      <c r="I120" s="22"/>
-      <c r="J120" s="93"/>
-      <c r="K120" s="93"/>
-      <c r="L120" s="93"/>
+      <c r="J119" s="96"/>
+      <c r="K119" s="96"/>
+      <c r="L119" s="96"/>
+    </row>
+    <row r="120" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="78"/>
+      <c r="K120" s="78"/>
+      <c r="L120" s="78"/>
     </row>
     <row r="121" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C121" s="21">
-        <v>45896</v>
-      </c>
-      <c r="D121" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="E121" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="F121" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="G121" s="22">
-        <v>5.2</v>
-      </c>
-      <c r="H121" s="22"/>
-      <c r="I121" s="22"/>
-      <c r="J121" s="93"/>
-      <c r="K121" s="93"/>
-      <c r="L121" s="93"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="30">
+        <f>SUM(G97:G119)</f>
+        <v>182.43999999999994</v>
+      </c>
+      <c r="H121" s="5">
+        <f>SUM(H97:H119)</f>
+        <v>7307</v>
+      </c>
+      <c r="I121" s="3"/>
+      <c r="J121" s="66"/>
+      <c r="K121" s="66"/>
+      <c r="L121" s="66"/>
     </row>
     <row r="122" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="78"/>
-      <c r="K122" s="78"/>
-      <c r="L122" s="78"/>
-    </row>
-    <row r="123" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C123" s="13"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="30">
-        <f>SUM(G98:G121)</f>
-        <v>185.03999999999994</v>
-      </c>
-      <c r="H123" s="5">
-        <f>G123*$R$3</f>
-        <v>18818.567999999996</v>
-      </c>
-      <c r="I123" s="3"/>
-      <c r="J123" s="66"/>
-      <c r="K123" s="66"/>
-      <c r="L123" s="66"/>
-    </row>
-    <row r="124" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="D124" s="44"/>
-      <c r="E124" s="44"/>
-      <c r="F124" s="44"/>
-      <c r="G124" s="44"/>
-      <c r="H124" s="44"/>
-      <c r="I124" s="44"/>
-      <c r="J124" s="44"/>
-      <c r="K124" s="44"/>
-      <c r="L124" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="44"/>
+      <c r="J122" s="44"/>
+      <c r="K122" s="44"/>
+      <c r="L122" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="222">
-    <mergeCell ref="J122:L122"/>
-    <mergeCell ref="J123:L123"/>
-    <mergeCell ref="I93:L93"/>
-    <mergeCell ref="J116:L116"/>
-    <mergeCell ref="J117:L117"/>
+  <mergeCells count="217">
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="I92:L92"/>
+    <mergeCell ref="J115:L115"/>
     <mergeCell ref="N10:R10"/>
     <mergeCell ref="Q11:R11"/>
     <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q16:R16"/>
     <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="N28:R28"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N26:R26"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
     <mergeCell ref="Q29:R29"/>
     <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N35:R35"/>
-    <mergeCell ref="N33:R34"/>
-    <mergeCell ref="I92:L92"/>
-    <mergeCell ref="I60:L60"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="N33:R33"/>
+    <mergeCell ref="N31:R32"/>
+    <mergeCell ref="I91:L91"/>
+    <mergeCell ref="I59:L59"/>
+    <mergeCell ref="I61:L61"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J98:L98"/>
     <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J103:L103"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="J117:L117"/>
     <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I65:L65"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="I90:L90"/>
+    <mergeCell ref="I86:L86"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="J114:L114"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="N8:P9"/>
-    <mergeCell ref="D50:E50"/>
     <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="J104:L104"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J103:L103"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D60:E60"/>
     <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D54:E54"/>
     <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="N26:R27"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="N24:R25"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D89:E89"/>
     <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D78:E78"/>
     <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D61:E61"/>
     <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D71:E71"/>
     <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I69:L69"/>
+    <mergeCell ref="I68:L68"/>
+    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="I83:L83"/>
+    <mergeCell ref="I84:L84"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="I50:L50"/>
     <mergeCell ref="D72:E72"/>
     <mergeCell ref="D73:E73"/>
     <mergeCell ref="D74:E74"/>
     <mergeCell ref="D75:E75"/>
     <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D80:E80"/>
     <mergeCell ref="D81:E81"/>
     <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D92:E92"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="I71:L71"/>
     <mergeCell ref="I72:L72"/>
     <mergeCell ref="I73:L73"/>
     <mergeCell ref="I74:L74"/>
     <mergeCell ref="I75:L75"/>
     <mergeCell ref="I76:L76"/>
     <mergeCell ref="I77:L77"/>
-    <mergeCell ref="I78:L78"/>
-    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="I70:L70"/>
+    <mergeCell ref="I80:L80"/>
     <mergeCell ref="I81:L81"/>
     <mergeCell ref="I82:L82"/>
-    <mergeCell ref="I83:L83"/>
-    <mergeCell ref="I86:L86"/>
-    <mergeCell ref="I80:L80"/>
-    <mergeCell ref="I88:L88"/>
-    <mergeCell ref="I65:L65"/>
+    <mergeCell ref="I85:L85"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="I64:L64"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="J98:L98"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I90:L90"/>
-    <mergeCell ref="I70:L70"/>
-    <mergeCell ref="I69:L69"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="I91:L91"/>
-    <mergeCell ref="I84:L84"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="I85:L85"/>
-    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="I49:L49"/>
     <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I45:L45"/>
     <mergeCell ref="I55:L55"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I46:L46"/>
     <mergeCell ref="I56:L56"/>
     <mergeCell ref="I57:L57"/>
     <mergeCell ref="I58:L58"/>
-    <mergeCell ref="I59:L59"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="I67:L67"/>
-    <mergeCell ref="I61:L61"/>
-    <mergeCell ref="I51:L51"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I42:L42"/>
     <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I36:L36"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="I27:L27"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I39:L39"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D42:E42"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="J110:L110"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="J111:L111"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J107:L107"/>
     <mergeCell ref="J108:L108"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="C94:L95"/>
-    <mergeCell ref="C96:L96"/>
-    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J116:L116"/>
+    <mergeCell ref="C93:L94"/>
+    <mergeCell ref="C95:L95"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J104:L104"/>
     <mergeCell ref="J105:L105"/>
     <mergeCell ref="J106:L106"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J110:L110"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="J109:L109"/>
     <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I40:L40"/>
     <mergeCell ref="I31:L31"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="D91:E91"/>
     <mergeCell ref="I47:L47"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="I3:K3"/>
@@ -10899,7 +10801,7 @@
       <c r="O2" s="64"/>
       <c r="P2" s="65"/>
       <c r="R2" s="38" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="19" x14ac:dyDescent="0.25">
@@ -10916,7 +10818,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>53</v>
@@ -10951,10 +10853,10 @@
         <v>45883</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F4" s="3">
         <v>2001</v>
@@ -10980,10 +10882,10 @@
         <v>45884</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="F5" s="3">
         <v>400</v>
@@ -11009,10 +10911,10 @@
         <v>45888</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="F6" s="3">
         <v>746</v>
@@ -11040,10 +10942,10 @@
         <v>45889</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F7" s="3">
         <v>625</v>
@@ -11138,7 +11040,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>53</v>
@@ -11163,7 +11065,7 @@
       <c r="K12" s="76"/>
       <c r="L12" s="77"/>
       <c r="N12" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="O12" s="4">
         <v>1299</v>
@@ -11177,7 +11079,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -11189,7 +11091,7 @@
         <v>21</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>53</v>
@@ -11201,7 +11103,7 @@
       <c r="K13" s="16"/>
       <c r="L13" s="17"/>
       <c r="N13" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="O13" s="4">
         <v>499</v>
@@ -11215,10 +11117,10 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G14" s="1">
         <v>69</v>
@@ -11229,7 +11131,7 @@
       <c r="K14" s="78"/>
       <c r="L14" s="78"/>
       <c r="N14" s="3" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="O14" s="4">
         <v>70</v>
@@ -11243,23 +11145,23 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J15" s="78"/>
       <c r="K15" s="78"/>
       <c r="L15" s="78"/>
       <c r="N15" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="O15" s="18">
         <v>175</v>
@@ -11273,17 +11175,17 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J16" s="78"/>
       <c r="K16" s="78"/>
@@ -11299,17 +11201,17 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J17" s="78"/>
       <c r="K17" s="78"/>
@@ -11325,17 +11227,17 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J18" s="78"/>
       <c r="K18" s="78"/>
@@ -11351,17 +11253,17 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J19" s="78"/>
       <c r="K19" s="78"/>
@@ -11377,17 +11279,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J20" s="78"/>
       <c r="K20" s="78"/>
@@ -11409,17 +11311,17 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J21" s="78"/>
       <c r="K21" s="78"/>
@@ -11435,10 +11337,10 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G22" s="1">
         <v>169</v>
@@ -11459,17 +11361,17 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J23" s="78"/>
       <c r="K23" s="78"/>
@@ -11488,10 +11390,10 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G24" s="1">
         <v>50</v>
@@ -11521,17 +11423,17 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J25" s="78"/>
       <c r="K25" s="78"/>
@@ -11548,17 +11450,17 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J26" s="78"/>
       <c r="K26" s="78"/>
@@ -11575,17 +11477,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J27" s="78"/>
       <c r="K27" s="78"/>
@@ -11604,10 +11506,10 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G28" s="1">
         <v>155</v>
@@ -11628,17 +11530,17 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="120" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J29" s="121"/>
       <c r="K29" s="121"/>
@@ -11654,10 +11556,10 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G30" s="1">
         <v>155</v>
@@ -11682,17 +11584,17 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="120" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J31" s="121"/>
       <c r="K31" s="121"/>
@@ -11724,17 +11626,17 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J32" s="78"/>
       <c r="K32" s="78"/>
@@ -11752,17 +11654,17 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J33" s="78"/>
       <c r="K33" s="78"/>
@@ -11773,10 +11675,10 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G34" s="1">
         <v>60</v>
@@ -11792,17 +11694,17 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J35" s="78"/>
       <c r="K35" s="78"/>
@@ -11817,17 +11719,17 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J36" s="78"/>
       <c r="K36" s="78"/>
@@ -11844,17 +11746,17 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J37" s="78"/>
       <c r="K37" s="78"/>
@@ -11870,10 +11772,10 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G38" s="1">
         <v>20</v>
@@ -11889,10 +11791,10 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G39" s="1">
         <v>20</v>
@@ -11908,10 +11810,10 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G40" s="1">
         <v>20</v>
@@ -11927,10 +11829,10 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="G41" s="1">
         <v>25</v>
@@ -11946,10 +11848,10 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="G42" s="1">
         <v>145</v>
@@ -11965,17 +11867,17 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="G43" s="1">
         <v>103</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="78" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="J43" s="78"/>
       <c r="K43" s="78"/>
@@ -11986,10 +11888,10 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="G44" s="1">
         <v>75</v>
@@ -12005,10 +11907,10 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="G45" s="1">
         <v>190</v>
@@ -12024,10 +11926,10 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="G46" s="1">
         <v>180</v>
@@ -12043,10 +11945,10 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="G47" s="1">
         <v>100</v>
@@ -12062,10 +11964,10 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="G48" s="1">
         <v>200</v>
@@ -12167,7 +12069,7 @@
         <v>20</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>69</v>
@@ -12176,16 +12078,16 @@
         <v>70</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J55" s="88" t="s">
         <v>7</v>
@@ -12197,10 +12099,10 @@
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1">
@@ -12216,10 +12118,10 @@
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1">
@@ -12228,7 +12130,7 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K57" s="78"/>
       <c r="L57" s="78"/>
@@ -12237,10 +12139,10 @@
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1">
@@ -12249,7 +12151,7 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K58" s="78"/>
       <c r="L58" s="78"/>
@@ -12258,10 +12160,10 @@
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1">
@@ -12270,7 +12172,7 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K59" s="78"/>
       <c r="L59" s="78"/>
@@ -12279,10 +12181,10 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1">
@@ -12291,7 +12193,7 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K60" s="78"/>
       <c r="L60" s="78"/>
@@ -12300,10 +12202,10 @@
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1">
@@ -12312,7 +12214,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K61" s="78"/>
       <c r="L61" s="78"/>
@@ -12321,13 +12223,13 @@
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G62" s="1">
         <v>45</v>
@@ -12342,13 +12244,13 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G63" s="1">
         <v>45</v>
@@ -12363,10 +12265,10 @@
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1">
@@ -12375,7 +12277,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="78" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K64" s="78"/>
       <c r="L64" s="78"/>
@@ -12384,10 +12286,10 @@
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1">
@@ -12395,7 +12297,7 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="J65" s="78"/>
       <c r="K65" s="78"/>
@@ -12405,10 +12307,10 @@
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1">
@@ -12424,10 +12326,10 @@
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1">
@@ -12443,10 +12345,10 @@
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1">
@@ -12454,7 +12356,7 @@
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="J68" s="78"/>
       <c r="K68" s="78"/>
@@ -12464,10 +12366,10 @@
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1">
@@ -12475,7 +12377,7 @@
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="J69" s="78"/>
       <c r="K69" s="78"/>
@@ -12485,10 +12387,10 @@
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1">
@@ -12496,7 +12398,7 @@
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="J70" s="78"/>
       <c r="K70" s="78"/>
@@ -12506,10 +12408,10 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1">
@@ -12517,7 +12419,7 @@
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="J71" s="78"/>
       <c r="K71" s="78"/>
@@ -12527,10 +12429,10 @@
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1">
@@ -12538,7 +12440,7 @@
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="J72" s="78"/>
       <c r="K72" s="78"/>
@@ -12548,10 +12450,10 @@
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1">
@@ -12559,7 +12461,7 @@
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="J73" s="78"/>
       <c r="K73" s="78"/>
@@ -12569,10 +12471,10 @@
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1">
@@ -12580,7 +12482,7 @@
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="J74" s="78"/>
       <c r="K74" s="78"/>
@@ -12590,10 +12492,10 @@
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1">
@@ -12601,7 +12503,7 @@
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="J75" s="78"/>
       <c r="K75" s="78"/>
@@ -12807,7 +12709,7 @@
       <c r="O2" s="64"/>
       <c r="P2" s="65"/>
       <c r="R2" s="38" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="19" x14ac:dyDescent="0.25">
@@ -12824,7 +12726,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>53</v>
@@ -12859,10 +12761,10 @@
         <v>45893</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="F4" s="3">
         <v>1640</v>
@@ -12890,10 +12792,10 @@
         <v>45900</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F5" s="3">
         <v>2730</v>
@@ -13016,7 +12918,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -13028,7 +12930,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>53</v>
@@ -13043,7 +12945,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>53</v>
@@ -13058,10 +12960,10 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G12" s="1">
         <v>150</v>
@@ -13072,7 +12974,7 @@
       <c r="K12" s="78"/>
       <c r="L12" s="78"/>
       <c r="N12" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="O12" s="4">
         <v>499</v>
@@ -13086,23 +12988,23 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G13" s="1">
         <v>140</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
       <c r="L13" s="78"/>
       <c r="N13" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="O13" s="4">
         <v>240</v>
@@ -13116,10 +13018,10 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G14" s="1">
         <v>200</v>
@@ -13140,17 +13042,17 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G15" s="1">
         <v>160</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J15" s="78"/>
       <c r="K15" s="78"/>
@@ -13166,10 +13068,10 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G16" s="1">
         <v>1955</v>
@@ -13190,17 +13092,17 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G17" s="1">
         <v>250</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J17" s="78"/>
       <c r="K17" s="78"/>
@@ -13216,10 +13118,10 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G18" s="1">
         <v>150</v>
@@ -13240,10 +13142,10 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G19" s="1">
         <v>100</v>
@@ -13264,17 +13166,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G20" s="1">
         <v>230</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J20" s="78"/>
       <c r="K20" s="78"/>
@@ -13296,17 +13198,17 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G21" s="1">
         <v>180</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J21" s="78"/>
       <c r="K21" s="78"/>
@@ -13322,17 +13224,17 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G22" s="1">
         <v>285</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="78" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J22" s="78"/>
       <c r="K22" s="78"/>
@@ -13348,10 +13250,10 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G23" s="1">
         <v>220</v>
@@ -13375,10 +13277,10 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G24" s="1">
         <v>60</v>
@@ -13408,10 +13310,10 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="G25" s="1">
         <v>150</v>
@@ -13425,7 +13327,7 @@
         <v>45885</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="11"/>
@@ -13437,10 +13339,10 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G26" s="1">
         <v>219</v>
@@ -13629,7 +13531,7 @@
         <v>20</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>69</v>
@@ -13638,16 +13540,16 @@
         <v>70</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J35" s="88" t="s">
         <v>7</v>
@@ -13664,16 +13566,16 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G36" s="1">
         <v>195</v>

--- a/content/notes/travel/travel.xlsx
+++ b/content/notes/travel/travel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ravi/programs/rk1165.github.io/content/notes/travel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B253A696-D8E9-E840-AB78-EEC0E217D109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2863D0-9D8A-8B49-B0AA-BB447A91F134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="3" xr2:uid="{FBDD8960-5B88-4843-A147-F58767FB427D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="535">
   <si>
     <t>Check In</t>
   </si>
@@ -1636,9 +1636,6 @@
   </si>
   <si>
     <t>Summer Guided Tour</t>
-  </si>
-  <si>
-    <t>TB</t>
   </si>
   <si>
     <t>Turaida</t>
@@ -1979,9 +1976,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1993,45 +2017,38 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2041,26 +2058,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4463,12 +4460,12 @@
       <c r="G3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="81"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
       <c r="L3" s="6" t="s">
         <v>5</v>
       </c>
@@ -4653,9 +4650,9 @@
         <f>C8-B8</f>
         <v>3</v>
       </c>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
     </row>
     <row r="9" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
@@ -4670,17 +4667,17 @@
         <f>SUM(G4:G8)</f>
         <v>36113</v>
       </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="87"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="81"/>
       <c r="L9" s="3">
         <f>SUM(L4:L8)</f>
         <v>17</v>
       </c>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
     </row>
     <row r="10" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B10" s="58"/>
@@ -4726,28 +4723,28 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="79" t="s">
+      <c r="Q11" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="81"/>
+      <c r="R11" s="78"/>
       <c r="T11">
         <v>295.75</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="19" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="88"/>
       <c r="N12" s="3" t="s">
         <v>81</v>
       </c>
@@ -4757,8 +4754,8 @@
       <c r="P12" s="4">
         <v>1462</v>
       </c>
-      <c r="Q12" s="73"/>
-      <c r="R12" s="74"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="85"/>
       <c r="T12">
         <v>399.85</v>
       </c>
@@ -4785,12 +4782,12 @@
       <c r="H13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="79" t="s">
+      <c r="I13" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
       <c r="N13" s="3" t="s">
         <v>296</v>
       </c>
@@ -4800,8 +4797,8 @@
       <c r="P13" s="4">
         <v>974</v>
       </c>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="74"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="85"/>
       <c r="T13">
         <v>851.75</v>
       </c>
@@ -4814,10 +4811,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
       <c r="N14" s="3" t="s">
         <v>286</v>
       </c>
@@ -4827,8 +4824,8 @@
       <c r="P14" s="4">
         <v>1781</v>
       </c>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="85"/>
       <c r="T14">
         <v>1182.99</v>
       </c>
@@ -4855,10 +4852,10 @@
       <c r="H15" s="1">
         <v>602.32000000000005</v>
       </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
       <c r="N15" s="3" t="s">
         <v>298</v>
       </c>
@@ -4868,8 +4865,8 @@
       <c r="P15" s="4">
         <v>1761</v>
       </c>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="74"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="85"/>
       <c r="T15">
         <v>556.01</v>
       </c>
@@ -4894,10 +4891,10 @@
         <v>400</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="75"/>
       <c r="N16" s="3" t="s">
         <v>312</v>
       </c>
@@ -4907,8 +4904,8 @@
       <c r="P16" s="4">
         <v>10088</v>
       </c>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="74"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="85"/>
       <c r="T16">
         <v>296.06</v>
       </c>
@@ -4933,10 +4930,10 @@
         <v>300</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="72"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="75"/>
       <c r="N17" s="3" t="s">
         <v>432</v>
       </c>
@@ -4944,8 +4941,8 @@
       <c r="P17" s="4">
         <v>29477</v>
       </c>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="74"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="85"/>
       <c r="T17">
         <v>355.27</v>
       </c>
@@ -4970,10 +4967,10 @@
       <c r="H18" s="1">
         <v>653.15</v>
       </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="75"/>
       <c r="N18" s="3"/>
       <c r="O18" s="4">
         <f>SUM(O12:O17)</f>
@@ -4983,8 +4980,8 @@
         <f>SUM(P12:P17)</f>
         <v>45543</v>
       </c>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
       <c r="T18">
         <v>1014.4</v>
       </c>
@@ -5009,15 +5006,15 @@
         <v>400</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="72"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="75"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
       <c r="T19">
         <v>83.84</v>
       </c>
@@ -5042,15 +5039,15 @@
         <v>300</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="84"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="84"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="75"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
       <c r="T20">
         <v>1177.33</v>
       </c>
@@ -5077,10 +5074,10 @@
       <c r="H21" s="1">
         <v>914.32</v>
       </c>
-      <c r="I21" s="70"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="75"/>
       <c r="N21" s="61" t="s">
         <v>38</v>
       </c>
@@ -5112,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
       <c r="N22" s="6" t="s">
         <v>20</v>
       </c>
@@ -5125,10 +5122,10 @@
       <c r="P22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="82" t="s">
+      <c r="Q22" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="R22" s="82"/>
+      <c r="R22" s="89"/>
       <c r="T22">
         <v>254.84</v>
       </c>
@@ -5153,10 +5150,10 @@
         <v>500</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
       <c r="N23" s="2"/>
       <c r="O23" s="3" t="s">
         <v>92</v>
@@ -5190,12 +5187,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="78" t="s">
+      <c r="I24" s="70" t="s">
         <v>246</v>
       </c>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
       <c r="N24" s="2"/>
       <c r="O24" s="3" t="s">
         <v>93</v>
@@ -5231,10 +5228,10 @@
       <c r="H25" s="1">
         <v>2000.76</v>
       </c>
-      <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="72"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="75"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="5">
@@ -5269,10 +5266,10 @@
       <c r="H26" s="1">
         <v>2848.38</v>
       </c>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
       <c r="N26" s="19"/>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
@@ -5304,10 +5301,10 @@
       <c r="H27" s="1">
         <v>2848.38</v>
       </c>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
       <c r="N27" s="42"/>
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
@@ -5336,12 +5333,12 @@
         <v>500</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="78" t="s">
+      <c r="I28" s="70" t="s">
         <v>253</v>
       </c>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
       <c r="N28" s="61" t="s">
         <v>55</v>
       </c>
@@ -5373,10 +5370,10 @@
       <c r="H29" s="1">
         <v>542</v>
       </c>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
       <c r="N29" s="6" t="s">
         <v>239</v>
       </c>
@@ -5416,10 +5413,10 @@
         <v>500</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
       <c r="N30" s="3">
         <v>600</v>
       </c>
@@ -5459,10 +5456,10 @@
         <v>500</v>
       </c>
       <c r="H31" s="1"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
       <c r="T31">
         <v>507.56</v>
       </c>
@@ -5487,10 +5484,10 @@
         <v>800</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
       <c r="T32">
         <v>302.12</v>
       </c>
@@ -5515,10 +5512,10 @@
         <v>500</v>
       </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
       <c r="N33" s="63" t="s">
         <v>61</v>
       </c>
@@ -5545,10 +5542,10 @@
         <v>800</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="72"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="75"/>
       <c r="N34" s="6" t="s">
         <v>67</v>
       </c>
@@ -5577,10 +5574,10 @@
         <v>1300</v>
       </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="72"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="74"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="75"/>
       <c r="N35" s="5">
         <f>G9+O7+P18+P25+H57+R30+H112</f>
         <v>187497.72</v>
@@ -5613,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="1"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
       <c r="T36">
         <v>259.82</v>
       </c>
@@ -5641,10 +5638,10 @@
         <v>500</v>
       </c>
       <c r="H37" s="1"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
       <c r="T37">
         <v>797.59</v>
       </c>
@@ -5667,10 +5664,10 @@
         <v>500</v>
       </c>
       <c r="H38" s="1"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
       <c r="T38">
         <v>1027.2</v>
       </c>
@@ -5695,10 +5692,10 @@
         <v>500</v>
       </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
       <c r="T39">
         <v>483.39</v>
       </c>
@@ -5723,12 +5720,12 @@
         <v>700</v>
       </c>
       <c r="H40" s="1"/>
-      <c r="I40" s="78" t="s">
+      <c r="I40" s="70" t="s">
         <v>277</v>
       </c>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
       <c r="T40">
         <v>71.3</v>
       </c>
@@ -5755,12 +5752,12 @@
       <c r="H41" s="1">
         <v>623.46</v>
       </c>
-      <c r="I41" s="78" t="s">
+      <c r="I41" s="70" t="s">
         <v>297</v>
       </c>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
       <c r="T41">
         <v>744.74</v>
       </c>
@@ -5783,10 +5780,10 @@
         <v>1700</v>
       </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
       <c r="T42">
         <v>472.77</v>
       </c>
@@ -5811,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="1"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
       <c r="T43">
         <v>1192.3599999999999</v>
       </c>
@@ -5839,12 +5836,12 @@
         <v>500</v>
       </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="78" t="s">
+      <c r="I44" s="70" t="s">
         <v>289</v>
       </c>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
       <c r="T44">
         <v>327.9</v>
       </c>
@@ -5869,12 +5866,12 @@
         <v>2000</v>
       </c>
       <c r="H45" s="1"/>
-      <c r="I45" s="78" t="s">
+      <c r="I45" s="70" t="s">
         <v>292</v>
       </c>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="70"/>
       <c r="T45">
         <v>1475.55</v>
       </c>
@@ -5901,10 +5898,10 @@
       <c r="H46" s="1">
         <v>117.69</v>
       </c>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
       <c r="T46">
         <v>807.23</v>
       </c>
@@ -5929,10 +5926,10 @@
         <v>800</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
       <c r="T47">
         <v>821.53</v>
       </c>
@@ -5957,10 +5954,10 @@
         <v>700</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="78"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="78"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="70"/>
       <c r="T48">
         <v>537.64</v>
       </c>
@@ -5985,12 +5982,12 @@
         <v>0</v>
       </c>
       <c r="H49" s="1"/>
-      <c r="I49" s="78" t="s">
+      <c r="I49" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="70"/>
       <c r="T49">
         <v>3982.12</v>
       </c>
@@ -6016,12 +6013,12 @@
         <v>0</v>
       </c>
       <c r="H50" s="1"/>
-      <c r="I50" s="78" t="s">
+      <c r="I50" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="78"/>
+      <c r="J50" s="70"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="70"/>
       <c r="T50">
         <v>649.95000000000005</v>
       </c>
@@ -6046,10 +6043,10 @@
         <v>900</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="70"/>
       <c r="T51">
         <v>896.07</v>
       </c>
@@ -6062,10 +6059,10 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="78"/>
-      <c r="J52" s="78"/>
-      <c r="K52" s="78"/>
-      <c r="L52" s="78"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="70"/>
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B53" s="31">
@@ -6087,12 +6084,12 @@
         <v>0</v>
       </c>
       <c r="H53" s="1"/>
-      <c r="I53" s="78" t="s">
+      <c r="I53" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="J53" s="78"/>
-      <c r="K53" s="78"/>
-      <c r="L53" s="78"/>
+      <c r="J53" s="70"/>
+      <c r="K53" s="70"/>
+      <c r="L53" s="70"/>
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B54" s="31">
@@ -6114,12 +6111,12 @@
         <v>0</v>
       </c>
       <c r="H54" s="1"/>
-      <c r="I54" s="78" t="s">
+      <c r="I54" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="J54" s="78"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="78"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B55" s="31">
@@ -6141,12 +6138,12 @@
         <v>0</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="78" t="s">
+      <c r="I55" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="J55" s="78"/>
-      <c r="K55" s="78"/>
-      <c r="L55" s="78"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="70"/>
     </row>
     <row r="56" spans="2:21" ht="19" x14ac:dyDescent="0.25">
       <c r="B56" s="13"/>
@@ -6246,11 +6243,11 @@
       <c r="I61" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="J61" s="88" t="s">
+      <c r="J61" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="K61" s="89"/>
-      <c r="L61" s="89"/>
+      <c r="K61" s="72"/>
+      <c r="L61" s="72"/>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B62" s="31">
@@ -6273,11 +6270,11 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="78" t="s">
+      <c r="J62" s="70" t="s">
         <v>300</v>
       </c>
-      <c r="K62" s="78"/>
-      <c r="L62" s="78"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B63" s="31">
@@ -6300,9 +6297,9 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-      <c r="J63" s="78"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="78"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="70"/>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B64" s="31">
@@ -6325,9 +6322,9 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="78"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="78"/>
+      <c r="J64" s="70"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="70"/>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="31">
@@ -6350,9 +6347,9 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-      <c r="J65" s="78"/>
-      <c r="K65" s="78"/>
-      <c r="L65" s="78"/>
+      <c r="J65" s="70"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="70"/>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="31">
@@ -6375,9 +6372,9 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="78"/>
-      <c r="K66" s="78"/>
-      <c r="L66" s="78"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="70"/>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="31">
@@ -6400,11 +6397,11 @@
         <v>993.13</v>
       </c>
       <c r="I67" s="1"/>
-      <c r="J67" s="78" t="s">
+      <c r="J67" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="K67" s="78"/>
-      <c r="L67" s="78"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="31">
@@ -6427,11 +6424,11 @@
         <v>993.13</v>
       </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="78" t="s">
+      <c r="J68" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="K68" s="78"/>
-      <c r="L68" s="78"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69" s="31">
@@ -6452,9 +6449,9 @@
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="78"/>
-      <c r="L69" s="78"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="70"/>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70" s="31">
@@ -6475,9 +6472,9 @@
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="78"/>
-      <c r="K70" s="78"/>
-      <c r="L70" s="78"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71" s="35">
@@ -6498,9 +6495,9 @@
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-      <c r="J71" s="78"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72" s="31">
@@ -6521,9 +6518,9 @@
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
-      <c r="J72" s="78"/>
-      <c r="K72" s="78"/>
-      <c r="L72" s="78"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="70"/>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73" s="31">
@@ -6544,9 +6541,9 @@
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
-      <c r="L73" s="78"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="70"/>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74" s="31">
@@ -6567,9 +6564,9 @@
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="78"/>
-      <c r="K74" s="78"/>
-      <c r="L74" s="78"/>
+      <c r="J74" s="70"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="70"/>
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75" s="31">
@@ -6584,9 +6581,9 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
+      <c r="J75" s="70"/>
+      <c r="K75" s="70"/>
+      <c r="L75" s="70"/>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B76" s="31">
@@ -6607,9 +6604,9 @@
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="78"/>
-      <c r="K76" s="78"/>
-      <c r="L76" s="78"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="70"/>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B77" s="31">
@@ -6630,9 +6627,9 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
     </row>
     <row r="78" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B78" s="31">
@@ -6649,11 +6646,11 @@
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="78" t="s">
+      <c r="J78" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="K78" s="78"/>
-      <c r="L78" s="78"/>
+      <c r="K78" s="70"/>
+      <c r="L78" s="70"/>
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="35">
@@ -6674,9 +6671,9 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-      <c r="J79" s="78"/>
-      <c r="K79" s="78"/>
-      <c r="L79" s="78"/>
+      <c r="J79" s="70"/>
+      <c r="K79" s="70"/>
+      <c r="L79" s="70"/>
     </row>
     <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B80" s="35">
@@ -6697,9 +6694,9 @@
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-      <c r="J80" s="78"/>
-      <c r="K80" s="78"/>
-      <c r="L80" s="78"/>
+      <c r="J80" s="70"/>
+      <c r="K80" s="70"/>
+      <c r="L80" s="70"/>
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B81" s="35">
@@ -6720,9 +6717,9 @@
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-      <c r="J81" s="78"/>
-      <c r="K81" s="78"/>
-      <c r="L81" s="78"/>
+      <c r="J81" s="70"/>
+      <c r="K81" s="70"/>
+      <c r="L81" s="70"/>
     </row>
     <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="31">
@@ -6745,9 +6742,9 @@
         <v>7223</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="78"/>
-      <c r="K82" s="78"/>
-      <c r="L82" s="78"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B83" s="31">
@@ -6768,9 +6765,9 @@
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="78"/>
-      <c r="K83" s="78"/>
-      <c r="L83" s="78"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B84" s="31">
@@ -6791,11 +6788,11 @@
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
-      <c r="J84" s="78" t="s">
+      <c r="J84" s="70" t="s">
         <v>418</v>
       </c>
-      <c r="K84" s="78"/>
-      <c r="L84" s="78"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B85" s="31">
@@ -6816,9 +6813,9 @@
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
-      <c r="J85" s="78"/>
-      <c r="K85" s="78"/>
-      <c r="L85" s="78"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="70"/>
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B86" s="31">
@@ -6839,9 +6836,9 @@
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="78"/>
-      <c r="K86" s="78"/>
-      <c r="L86" s="78"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="70"/>
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B87" s="31">
@@ -6862,9 +6859,9 @@
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="78"/>
-      <c r="K87" s="78"/>
-      <c r="L87" s="78"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="31">
@@ -6887,9 +6884,9 @@
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="78"/>
-      <c r="K88" s="78"/>
-      <c r="L88" s="78"/>
+      <c r="J88" s="70"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="70"/>
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B89" s="31">
@@ -6912,9 +6909,9 @@
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-      <c r="J89" s="78"/>
-      <c r="K89" s="78"/>
-      <c r="L89" s="78"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="70"/>
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B90" s="31">
@@ -6935,9 +6932,9 @@
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="78"/>
-      <c r="K90" s="78"/>
-      <c r="L90" s="78"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="70"/>
     </row>
     <row r="91" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B91" s="31">
@@ -6958,9 +6955,9 @@
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
-      <c r="J91" s="78"/>
-      <c r="K91" s="78"/>
-      <c r="L91" s="78"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="70"/>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B92" s="31">
@@ -6981,9 +6978,9 @@
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-      <c r="J92" s="78"/>
-      <c r="K92" s="78"/>
-      <c r="L92" s="78"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="31">
@@ -7004,9 +7001,9 @@
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
-      <c r="J93" s="78"/>
-      <c r="K93" s="78"/>
-      <c r="L93" s="78"/>
+      <c r="J93" s="70"/>
+      <c r="K93" s="70"/>
+      <c r="L93" s="70"/>
     </row>
     <row r="94" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B94" s="31">
@@ -7027,11 +7024,11 @@
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="78" t="s">
+      <c r="J94" s="70" t="s">
         <v>320</v>
       </c>
-      <c r="K94" s="78"/>
-      <c r="L94" s="78"/>
+      <c r="K94" s="70"/>
+      <c r="L94" s="70"/>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B95" s="31">
@@ -7052,9 +7049,9 @@
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
-      <c r="J95" s="78"/>
-      <c r="K95" s="78"/>
-      <c r="L95" s="78"/>
+      <c r="J95" s="70"/>
+      <c r="K95" s="70"/>
+      <c r="L95" s="70"/>
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B96" s="31">
@@ -7075,9 +7072,9 @@
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
-      <c r="J96" s="78"/>
-      <c r="K96" s="78"/>
-      <c r="L96" s="78"/>
+      <c r="J96" s="70"/>
+      <c r="K96" s="70"/>
+      <c r="L96" s="70"/>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B97" s="31">
@@ -7098,9 +7095,9 @@
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
-      <c r="J97" s="78"/>
-      <c r="K97" s="78"/>
-      <c r="L97" s="78"/>
+      <c r="J97" s="70"/>
+      <c r="K97" s="70"/>
+      <c r="L97" s="70"/>
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B98" s="31">
@@ -7121,9 +7118,9 @@
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="78"/>
-      <c r="K98" s="78"/>
-      <c r="L98" s="78"/>
+      <c r="J98" s="70"/>
+      <c r="K98" s="70"/>
+      <c r="L98" s="70"/>
     </row>
     <row r="99" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B99" s="31">
@@ -7144,9 +7141,9 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
-      <c r="J99" s="78"/>
-      <c r="K99" s="78"/>
-      <c r="L99" s="78"/>
+      <c r="J99" s="70"/>
+      <c r="K99" s="70"/>
+      <c r="L99" s="70"/>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B100" s="31">
@@ -7167,9 +7164,9 @@
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
-      <c r="J100" s="78"/>
-      <c r="K100" s="78"/>
-      <c r="L100" s="78"/>
+      <c r="J100" s="70"/>
+      <c r="K100" s="70"/>
+      <c r="L100" s="70"/>
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B101" s="31">
@@ -7190,9 +7187,9 @@
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
-      <c r="J101" s="78"/>
-      <c r="K101" s="78"/>
-      <c r="L101" s="78"/>
+      <c r="J101" s="70"/>
+      <c r="K101" s="70"/>
+      <c r="L101" s="70"/>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B102" s="31">
@@ -7213,9 +7210,9 @@
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="78"/>
-      <c r="K102" s="78"/>
-      <c r="L102" s="78"/>
+      <c r="J102" s="70"/>
+      <c r="K102" s="70"/>
+      <c r="L102" s="70"/>
     </row>
     <row r="103" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B103" s="31">
@@ -7236,9 +7233,9 @@
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
-      <c r="J103" s="78"/>
-      <c r="K103" s="78"/>
-      <c r="L103" s="78"/>
+      <c r="J103" s="70"/>
+      <c r="K103" s="70"/>
+      <c r="L103" s="70"/>
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B104" s="31">
@@ -7259,9 +7256,9 @@
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
-      <c r="J104" s="78"/>
-      <c r="K104" s="78"/>
-      <c r="L104" s="78"/>
+      <c r="J104" s="70"/>
+      <c r="K104" s="70"/>
+      <c r="L104" s="70"/>
     </row>
     <row r="105" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B105" s="31"/>
@@ -7278,9 +7275,9 @@
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
-      <c r="J105" s="78"/>
-      <c r="K105" s="78"/>
-      <c r="L105" s="78"/>
+      <c r="J105" s="70"/>
+      <c r="K105" s="70"/>
+      <c r="L105" s="70"/>
     </row>
     <row r="106" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B106" s="31">
@@ -7301,9 +7298,9 @@
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
-      <c r="J106" s="78"/>
-      <c r="K106" s="78"/>
-      <c r="L106" s="78"/>
+      <c r="J106" s="70"/>
+      <c r="K106" s="70"/>
+      <c r="L106" s="70"/>
     </row>
     <row r="107" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B107" s="31">
@@ -7324,9 +7321,9 @@
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
-      <c r="J107" s="78"/>
-      <c r="K107" s="78"/>
-      <c r="L107" s="78"/>
+      <c r="J107" s="70"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="70"/>
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B108" s="31">
@@ -7347,11 +7344,11 @@
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
-      <c r="J108" s="78" t="s">
+      <c r="J108" s="70" t="s">
         <v>414</v>
       </c>
-      <c r="K108" s="78"/>
-      <c r="L108" s="78"/>
+      <c r="K108" s="70"/>
+      <c r="L108" s="70"/>
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B109" s="31">
@@ -7372,11 +7369,11 @@
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="78" t="s">
+      <c r="J109" s="70" t="s">
         <v>414</v>
       </c>
-      <c r="K109" s="78"/>
-      <c r="L109" s="78"/>
+      <c r="K109" s="70"/>
+      <c r="L109" s="70"/>
     </row>
     <row r="110" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B110" s="31">
@@ -7397,9 +7394,9 @@
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
-      <c r="J110" s="78"/>
-      <c r="K110" s="78"/>
-      <c r="L110" s="78"/>
+      <c r="J110" s="70"/>
+      <c r="K110" s="70"/>
+      <c r="L110" s="70"/>
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B111" s="31"/>
@@ -7410,9 +7407,9 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="78"/>
-      <c r="K111" s="78"/>
-      <c r="L111" s="78"/>
+      <c r="J111" s="70"/>
+      <c r="K111" s="70"/>
+      <c r="L111" s="70"/>
     </row>
     <row r="112" spans="2:12" ht="19" x14ac:dyDescent="0.25">
       <c r="B112" s="13"/>
@@ -7429,12 +7426,116 @@
         <v>9209.26</v>
       </c>
       <c r="I112" s="3"/>
-      <c r="J112" s="78"/>
-      <c r="K112" s="78"/>
-      <c r="L112" s="78"/>
+      <c r="J112" s="70"/>
+      <c r="K112" s="70"/>
+      <c r="L112" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="128">
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="N19:R20"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="B10:L11"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="N8:P9"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:L74"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J80:L80"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="J111:L111"/>
+    <mergeCell ref="J73:L73"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="J98:L98"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J86:L86"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="J105:L105"/>
+    <mergeCell ref="J103:L103"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="J92:L92"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="I57:L57"/>
+    <mergeCell ref="B58:L59"/>
+    <mergeCell ref="N28:R28"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="J104:L104"/>
     <mergeCell ref="J108:L108"/>
     <mergeCell ref="J109:L109"/>
     <mergeCell ref="J110:L110"/>
@@ -7459,110 +7560,6 @@
     <mergeCell ref="I54:L54"/>
     <mergeCell ref="J67:L67"/>
     <mergeCell ref="J68:L68"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="I57:L57"/>
-    <mergeCell ref="B58:L59"/>
-    <mergeCell ref="N28:R28"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="J104:L104"/>
-    <mergeCell ref="J105:L105"/>
-    <mergeCell ref="J103:L103"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="J92:L92"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J66:L66"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:L74"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J80:L80"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="J111:L111"/>
-    <mergeCell ref="J73:L73"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="J98:L98"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J86:L86"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="B10:L11"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="N8:P9"/>
-    <mergeCell ref="N10:R10"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="N19:R20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7637,11 +7634,11 @@
       <c r="H3" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="89" t="s">
         <v>523</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
       <c r="L3" s="6" t="s">
         <v>5</v>
       </c>
@@ -7681,9 +7678,9 @@
         <f>F4/L4</f>
         <v>19.585000000000001</v>
       </c>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="3">
         <f t="shared" ref="L4:L10" si="0">C4-B4</f>
         <v>2</v>
@@ -7719,9 +7716,9 @@
         <f t="shared" ref="H5:H10" si="1">F5/L5</f>
         <v>26</v>
       </c>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -7757,9 +7754,9 @@
         <f t="shared" si="1"/>
         <v>25.6</v>
       </c>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
       <c r="L6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7795,9 +7792,9 @@
         <f t="shared" si="1"/>
         <v>25.3</v>
       </c>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
       <c r="L7" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -7834,18 +7831,18 @@
         <f>F8/L8</f>
         <v>17.352857142857143</v>
       </c>
-      <c r="I8" s="99" t="s">
+      <c r="I8" s="117" t="s">
         <v>524</v>
       </c>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
     </row>
     <row r="9" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B9" s="13">
@@ -7870,16 +7867,16 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
       <c r="L9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
     </row>
     <row r="10" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B10" s="13">
@@ -7904,11 +7901,11 @@
         <f t="shared" si="1"/>
         <v>18.285714285714285</v>
       </c>
-      <c r="I10" s="99" t="s">
+      <c r="I10" s="117" t="s">
         <v>525</v>
       </c>
-      <c r="J10" s="99"/>
-      <c r="K10" s="99"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
       <c r="L10" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -7929,9 +7926,9 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
       <c r="L11" s="3"/>
       <c r="N11" s="6" t="s">
         <v>45</v>
@@ -7942,10 +7939,10 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="79" t="s">
+      <c r="Q11" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="81"/>
+      <c r="R11" s="78"/>
     </row>
     <row r="12" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
@@ -7964,9 +7961,9 @@
         <f>F12/L12</f>
         <v>20.729600000000001</v>
       </c>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
       <c r="L12" s="3">
         <f>SUM(L4:L11)</f>
         <v>25</v>
@@ -7980,23 +7977,23 @@
       <c r="P12" s="29">
         <v>7626.65</v>
       </c>
-      <c r="Q12" s="97" t="s">
+      <c r="Q12" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="R12" s="98"/>
+      <c r="R12" s="92"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
       <c r="N13" s="28" t="s">
         <v>519</v>
       </c>
@@ -8006,21 +8003,21 @@
       <c r="P13" s="29">
         <v>6406</v>
       </c>
-      <c r="Q13" s="97" t="s">
+      <c r="Q13" s="91" t="s">
         <v>530</v>
       </c>
-      <c r="R13" s="98"/>
+      <c r="R13" s="92"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
       <c r="N14" s="22" t="s">
         <v>510</v>
       </c>
@@ -8036,18 +8033,18 @@
       <c r="R14" s="55"/>
     </row>
     <row r="15" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="101"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
       <c r="N15" s="22" t="s">
         <v>235</v>
       </c>
@@ -8055,19 +8052,19 @@
         <v>1.5</v>
       </c>
       <c r="P15" s="23"/>
-      <c r="Q15" s="118" t="s">
+      <c r="Q15" s="93" t="s">
         <v>179</v>
       </c>
-      <c r="R15" s="119"/>
+      <c r="R15" s="94"/>
     </row>
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C16" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="107" t="s">
+      <c r="D16" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="107"/>
+      <c r="E16" s="113"/>
       <c r="F16" s="12" t="s">
         <v>21</v>
       </c>
@@ -8077,12 +8074,12 @@
       <c r="H16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="79" t="s">
+      <c r="I16" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="81"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
       <c r="N16" s="22" t="s">
         <v>228</v>
       </c>
@@ -8090,19 +8087,19 @@
         <v>12</v>
       </c>
       <c r="P16" s="23"/>
-      <c r="Q16" s="118" t="s">
+      <c r="Q16" s="93" t="s">
         <v>179</v>
       </c>
-      <c r="R16" s="119"/>
+      <c r="R16" s="94"/>
     </row>
     <row r="17" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C17" s="48">
         <v>45875</v>
       </c>
-      <c r="D17" s="110" t="s">
+      <c r="D17" s="100" t="s">
         <v>492</v>
       </c>
-      <c r="E17" s="110"/>
+      <c r="E17" s="100"/>
       <c r="F17" s="46" t="s">
         <v>433</v>
       </c>
@@ -8110,10 +8107,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="47"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="113"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="116"/>
       <c r="N17" s="25" t="s">
         <v>228</v>
       </c>
@@ -8121,19 +8118,19 @@
         <v>10</v>
       </c>
       <c r="P17" s="26"/>
-      <c r="Q17" s="114" t="s">
+      <c r="Q17" s="104" t="s">
         <v>177</v>
       </c>
-      <c r="R17" s="115"/>
+      <c r="R17" s="105"/>
     </row>
     <row r="18" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C18" s="48">
         <v>45875</v>
       </c>
-      <c r="D18" s="110" t="s">
+      <c r="D18" s="100" t="s">
         <v>529</v>
       </c>
-      <c r="E18" s="110"/>
+      <c r="E18" s="100"/>
       <c r="F18" s="46" t="s">
         <v>433</v>
       </c>
@@ -8143,10 +8140,10 @@
       <c r="H18" s="47">
         <v>508.44</v>
       </c>
-      <c r="I18" s="111"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="113"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="116"/>
       <c r="N18" s="25" t="s">
         <v>236</v>
       </c>
@@ -8154,19 +8151,19 @@
         <v>2</v>
       </c>
       <c r="P18" s="26"/>
-      <c r="Q18" s="114" t="s">
+      <c r="Q18" s="104" t="s">
         <v>177</v>
       </c>
-      <c r="R18" s="115"/>
+      <c r="R18" s="105"/>
     </row>
     <row r="19" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C19" s="48">
         <v>45875</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="100" t="s">
         <v>493</v>
       </c>
-      <c r="E19" s="110"/>
+      <c r="E19" s="100"/>
       <c r="F19" s="46" t="s">
         <v>433</v>
       </c>
@@ -8174,10 +8171,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="47"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="113"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="116"/>
       <c r="N19" s="46" t="s">
         <v>491</v>
       </c>
@@ -8185,19 +8182,19 @@
         <v>81</v>
       </c>
       <c r="P19" s="47"/>
-      <c r="Q19" s="108" t="s">
+      <c r="Q19" s="111" t="s">
         <v>433</v>
       </c>
-      <c r="R19" s="109"/>
+      <c r="R19" s="112"/>
     </row>
     <row r="20" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C20" s="48">
         <v>45876</v>
       </c>
-      <c r="D20" s="110" t="s">
+      <c r="D20" s="100" t="s">
         <v>494</v>
       </c>
-      <c r="E20" s="110"/>
+      <c r="E20" s="100"/>
       <c r="F20" s="46" t="s">
         <v>433</v>
       </c>
@@ -8205,10 +8202,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="47"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="113"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="116"/>
       <c r="N20" s="3" t="s">
         <v>520</v>
       </c>
@@ -8218,17 +8215,17 @@
       <c r="P20" s="4">
         <v>1037.5999999999999</v>
       </c>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="74"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C21" s="48">
         <v>45876</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D21" s="100" t="s">
         <v>495</v>
       </c>
-      <c r="E21" s="110"/>
+      <c r="E21" s="100"/>
       <c r="F21" s="46" t="s">
         <v>433</v>
       </c>
@@ -8236,24 +8233,24 @@
         <v>0</v>
       </c>
       <c r="H21" s="47"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="113"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="115"/>
+      <c r="L21" s="116"/>
       <c r="N21" s="3"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
-      <c r="Q21" s="73"/>
-      <c r="R21" s="74"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="85"/>
     </row>
     <row r="22" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C22" s="48">
         <v>45876</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D22" s="100" t="s">
         <v>496</v>
       </c>
-      <c r="E22" s="110"/>
+      <c r="E22" s="100"/>
       <c r="F22" s="46" t="s">
         <v>433</v>
       </c>
@@ -8261,24 +8258,24 @@
         <v>0</v>
       </c>
       <c r="H22" s="47"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="112"/>
-      <c r="L22" s="113"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="116"/>
       <c r="N22" s="3"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="74"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="85"/>
     </row>
     <row r="23" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C23" s="48">
         <v>45876</v>
       </c>
-      <c r="D23" s="110" t="s">
+      <c r="D23" s="100" t="s">
         <v>497</v>
       </c>
-      <c r="E23" s="110"/>
+      <c r="E23" s="100"/>
       <c r="F23" s="46" t="s">
         <v>433</v>
       </c>
@@ -8286,10 +8283,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="47"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="113"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="115"/>
+      <c r="L23" s="116"/>
       <c r="N23" s="3"/>
       <c r="O23" s="18">
         <f>SUM(O12:O22)</f>
@@ -8299,17 +8296,17 @@
         <f>SUM(P12:P20)</f>
         <v>20765.25</v>
       </c>
-      <c r="Q23" s="116"/>
-      <c r="R23" s="117"/>
+      <c r="Q23" s="106"/>
+      <c r="R23" s="107"/>
     </row>
     <row r="24" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C24" s="48">
         <v>45876</v>
       </c>
-      <c r="D24" s="110" t="s">
+      <c r="D24" s="100" t="s">
         <v>498</v>
       </c>
-      <c r="E24" s="110"/>
+      <c r="E24" s="100"/>
       <c r="F24" s="46" t="s">
         <v>433</v>
       </c>
@@ -8317,24 +8314,24 @@
         <v>0</v>
       </c>
       <c r="H24" s="47"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="113"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
+      <c r="L24" s="116"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="49">
         <v>45877</v>
       </c>
-      <c r="D25" s="102" t="s">
+      <c r="D25" s="99" t="s">
         <v>365</v>
       </c>
-      <c r="E25" s="102"/>
+      <c r="E25" s="99"/>
       <c r="F25" s="28" t="s">
         <v>175</v>
       </c>
@@ -8342,26 +8339,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="29"/>
-      <c r="I25" s="90" t="s">
+      <c r="I25" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="92"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="110"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="83"/>
     </row>
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="49">
         <v>45877</v>
       </c>
-      <c r="D26" s="102" t="s">
+      <c r="D26" s="99" t="s">
         <v>364</v>
       </c>
-      <c r="E26" s="102"/>
+      <c r="E26" s="99"/>
       <c r="F26" s="28" t="s">
         <v>175</v>
       </c>
@@ -8369,12 +8366,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="29"/>
-      <c r="I26" s="90" t="s">
+      <c r="I26" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="92"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="110"/>
       <c r="N26" s="63" t="s">
         <v>38</v>
       </c>
@@ -8387,10 +8384,10 @@
       <c r="C27" s="49">
         <v>45877</v>
       </c>
-      <c r="D27" s="102" t="s">
+      <c r="D27" s="99" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="102"/>
+      <c r="E27" s="99"/>
       <c r="F27" s="28" t="s">
         <v>175</v>
       </c>
@@ -8398,12 +8395,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="29"/>
-      <c r="I27" s="90" t="s">
+      <c r="I27" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="92"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="110"/>
       <c r="N27" s="6" t="s">
         <v>20</v>
       </c>
@@ -8413,19 +8410,19 @@
       <c r="P27" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q27" s="79" t="s">
+      <c r="Q27" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R27" s="80"/>
+      <c r="R27" s="77"/>
     </row>
     <row r="28" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C28" s="49">
         <v>45877</v>
       </c>
-      <c r="D28" s="102" t="s">
+      <c r="D28" s="99" t="s">
         <v>363</v>
       </c>
-      <c r="E28" s="102"/>
+      <c r="E28" s="99"/>
       <c r="F28" s="28" t="s">
         <v>175</v>
       </c>
@@ -8433,12 +8430,12 @@
         <v>0</v>
       </c>
       <c r="H28" s="29"/>
-      <c r="I28" s="90" t="s">
+      <c r="I28" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="92"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="109"/>
+      <c r="L28" s="110"/>
       <c r="N28" s="13">
         <v>45874</v>
       </c>
@@ -8448,17 +8445,17 @@
       <c r="P28" s="3">
         <v>27000</v>
       </c>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="74"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="85"/>
     </row>
     <row r="29" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C29" s="49">
         <v>45878</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D29" s="99" t="s">
         <v>413</v>
       </c>
-      <c r="E29" s="102"/>
+      <c r="E29" s="99"/>
       <c r="F29" s="28" t="s">
         <v>175</v>
       </c>
@@ -8466,12 +8463,12 @@
         <v>0</v>
       </c>
       <c r="H29" s="29"/>
-      <c r="I29" s="90" t="s">
+      <c r="I29" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="92"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="110"/>
       <c r="N29" s="13">
         <v>45900</v>
       </c>
@@ -8481,17 +8478,17 @@
       <c r="P29" s="3">
         <v>27979</v>
       </c>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="74"/>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="85"/>
     </row>
     <row r="30" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C30" s="49">
         <v>45878</v>
       </c>
-      <c r="D30" s="102" t="s">
+      <c r="D30" s="99" t="s">
         <v>360</v>
       </c>
-      <c r="E30" s="102"/>
+      <c r="E30" s="99"/>
       <c r="F30" s="28" t="s">
         <v>175</v>
       </c>
@@ -8499,29 +8496,29 @@
         <v>0</v>
       </c>
       <c r="H30" s="29"/>
-      <c r="I30" s="90" t="s">
+      <c r="I30" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="92"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="110"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="5">
         <f>P28+P29</f>
         <v>54979</v>
       </c>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="74"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="85"/>
     </row>
     <row r="31" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C31" s="49">
         <v>45878</v>
       </c>
-      <c r="D31" s="90" t="s">
+      <c r="D31" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="E31" s="92"/>
+      <c r="E31" s="110"/>
       <c r="F31" s="28" t="s">
         <v>175</v>
       </c>
@@ -8529,26 +8526,26 @@
         <v>0</v>
       </c>
       <c r="H31" s="29"/>
-      <c r="I31" s="90" t="s">
+      <c r="I31" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="92"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="83"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="110"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="49">
         <v>45878</v>
       </c>
-      <c r="D32" s="102" t="s">
+      <c r="D32" s="99" t="s">
         <v>362</v>
       </c>
-      <c r="E32" s="102"/>
+      <c r="E32" s="99"/>
       <c r="F32" s="28" t="s">
         <v>175</v>
       </c>
@@ -8556,27 +8553,27 @@
         <v>0</v>
       </c>
       <c r="H32" s="29"/>
-      <c r="I32" s="90" t="s">
+      <c r="I32" s="108" t="s">
         <v>526</v>
       </c>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="110"/>
       <c r="M32" s="42"/>
-      <c r="N32" s="84"/>
-      <c r="O32" s="84"/>
-      <c r="P32" s="84"/>
-      <c r="Q32" s="84"/>
-      <c r="R32" s="84"/>
+      <c r="N32" s="83"/>
+      <c r="O32" s="83"/>
+      <c r="P32" s="83"/>
+      <c r="Q32" s="83"/>
+      <c r="R32" s="83"/>
     </row>
     <row r="33" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C33" s="49">
         <v>45879</v>
       </c>
-      <c r="D33" s="102" t="s">
+      <c r="D33" s="99" t="s">
         <v>361</v>
       </c>
-      <c r="E33" s="102"/>
+      <c r="E33" s="99"/>
       <c r="F33" s="28" t="s">
         <v>175</v>
       </c>
@@ -8584,12 +8581,12 @@
         <v>0</v>
       </c>
       <c r="H33" s="29"/>
-      <c r="I33" s="90" t="s">
+      <c r="I33" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="92"/>
+      <c r="J33" s="109"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="110"/>
       <c r="N33" s="61" t="s">
         <v>55</v>
       </c>
@@ -8602,10 +8599,10 @@
       <c r="C34" s="49">
         <v>45879</v>
       </c>
-      <c r="D34" s="102" t="s">
+      <c r="D34" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="E34" s="102"/>
+      <c r="E34" s="99"/>
       <c r="F34" s="28" t="s">
         <v>175</v>
       </c>
@@ -8613,12 +8610,12 @@
         <v>0</v>
       </c>
       <c r="H34" s="29"/>
-      <c r="I34" s="90" t="s">
+      <c r="I34" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="109"/>
+      <c r="L34" s="110"/>
       <c r="N34" s="6" t="s">
         <v>94</v>
       </c>
@@ -8639,10 +8636,10 @@
       <c r="C35" s="49">
         <v>45880</v>
       </c>
-      <c r="D35" s="102" t="s">
+      <c r="D35" s="99" t="s">
         <v>198</v>
       </c>
-      <c r="E35" s="102"/>
+      <c r="E35" s="99"/>
       <c r="F35" s="28" t="s">
         <v>175</v>
       </c>
@@ -8652,10 +8649,10 @@
       <c r="H35" s="29">
         <v>9660.4</v>
       </c>
-      <c r="I35" s="90"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="91"/>
-      <c r="L35" s="92"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="110"/>
       <c r="N35" s="3">
         <v>300</v>
       </c>
@@ -8672,10 +8669,10 @@
       <c r="C36" s="49">
         <v>45881</v>
       </c>
-      <c r="D36" s="102" t="s">
+      <c r="D36" s="99" t="s">
         <v>216</v>
       </c>
-      <c r="E36" s="102"/>
+      <c r="E36" s="99"/>
       <c r="F36" s="28" t="s">
         <v>175</v>
       </c>
@@ -8683,21 +8680,21 @@
         <v>0</v>
       </c>
       <c r="H36" s="29"/>
-      <c r="I36" s="90" t="s">
+      <c r="I36" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J36" s="91"/>
-      <c r="K36" s="91"/>
-      <c r="L36" s="92"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="110"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="49">
         <v>45881</v>
       </c>
-      <c r="D37" s="102" t="s">
+      <c r="D37" s="99" t="s">
         <v>367</v>
       </c>
-      <c r="E37" s="102"/>
+      <c r="E37" s="99"/>
       <c r="F37" s="28" t="s">
         <v>175</v>
       </c>
@@ -8705,21 +8702,21 @@
         <v>0</v>
       </c>
       <c r="H37" s="29"/>
-      <c r="I37" s="90" t="s">
+      <c r="I37" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="92"/>
+      <c r="J37" s="109"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="110"/>
     </row>
     <row r="38" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C38" s="49">
         <v>45881</v>
       </c>
-      <c r="D38" s="102" t="s">
+      <c r="D38" s="99" t="s">
         <v>366</v>
       </c>
-      <c r="E38" s="102"/>
+      <c r="E38" s="99"/>
       <c r="F38" s="28" t="s">
         <v>175</v>
       </c>
@@ -8727,12 +8724,12 @@
         <v>0</v>
       </c>
       <c r="H38" s="29"/>
-      <c r="I38" s="90" t="s">
+      <c r="I38" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J38" s="91"/>
-      <c r="K38" s="91"/>
-      <c r="L38" s="92"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="110"/>
       <c r="N38" s="63" t="s">
         <v>61</v>
       </c>
@@ -8742,10 +8739,10 @@
       <c r="C39" s="49">
         <v>45882</v>
       </c>
-      <c r="D39" s="102" t="s">
+      <c r="D39" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="102"/>
+      <c r="E39" s="99"/>
       <c r="F39" s="28" t="s">
         <v>175</v>
       </c>
@@ -8753,12 +8750,12 @@
         <v>0</v>
       </c>
       <c r="H39" s="29"/>
-      <c r="I39" s="90" t="s">
+      <c r="I39" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="92"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109"/>
+      <c r="L39" s="110"/>
       <c r="N39" s="6" t="s">
         <v>67</v>
       </c>
@@ -8770,10 +8767,10 @@
       <c r="C40" s="49">
         <v>45882</v>
       </c>
-      <c r="D40" s="102" t="s">
+      <c r="D40" s="99" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="102"/>
+      <c r="E40" s="99"/>
       <c r="F40" s="28" t="s">
         <v>175</v>
       </c>
@@ -8781,29 +8778,29 @@
         <v>0</v>
       </c>
       <c r="H40" s="29"/>
-      <c r="I40" s="90" t="s">
+      <c r="I40" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="92"/>
+      <c r="J40" s="109"/>
+      <c r="K40" s="109"/>
+      <c r="L40" s="110"/>
       <c r="N40" s="5">
         <f>(F12+O23+G87+G114)*R3+O7+P30</f>
         <v>205845.1</v>
       </c>
       <c r="O40" s="5">
         <f>G12+O7+P30+P23+H87+H114</f>
-        <v>169471</v>
+        <v>170692.33</v>
       </c>
     </row>
     <row r="41" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C41" s="49">
         <v>45882</v>
       </c>
-      <c r="D41" s="102" t="s">
+      <c r="D41" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="E41" s="102"/>
+      <c r="E41" s="99"/>
       <c r="F41" s="28" t="s">
         <v>175</v>
       </c>
@@ -8811,21 +8808,21 @@
         <v>0</v>
       </c>
       <c r="H41" s="29"/>
-      <c r="I41" s="90" t="s">
+      <c r="I41" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="92"/>
+      <c r="J41" s="109"/>
+      <c r="K41" s="109"/>
+      <c r="L41" s="110"/>
     </row>
     <row r="42" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C42" s="49">
         <v>45883</v>
       </c>
-      <c r="D42" s="102" t="s">
+      <c r="D42" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="E42" s="102"/>
+      <c r="E42" s="99"/>
       <c r="F42" s="28" t="s">
         <v>176</v>
       </c>
@@ -8833,21 +8830,21 @@
         <v>0</v>
       </c>
       <c r="H42" s="29"/>
-      <c r="I42" s="90" t="s">
+      <c r="I42" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J42" s="91"/>
-      <c r="K42" s="91"/>
-      <c r="L42" s="92"/>
+      <c r="J42" s="109"/>
+      <c r="K42" s="109"/>
+      <c r="L42" s="110"/>
     </row>
     <row r="43" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C43" s="49">
         <v>45883</v>
       </c>
-      <c r="D43" s="102" t="s">
+      <c r="D43" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="E43" s="102"/>
+      <c r="E43" s="99"/>
       <c r="F43" s="28" t="s">
         <v>176</v>
       </c>
@@ -8857,19 +8854,19 @@
       <c r="H43" s="29">
         <v>1830.7</v>
       </c>
-      <c r="I43" s="90"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="91"/>
-      <c r="L43" s="92"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="109"/>
+      <c r="K43" s="109"/>
+      <c r="L43" s="110"/>
     </row>
     <row r="44" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C44" s="50">
         <v>45884</v>
       </c>
-      <c r="D44" s="102" t="s">
+      <c r="D44" s="99" t="s">
         <v>358</v>
       </c>
-      <c r="E44" s="102"/>
+      <c r="E44" s="99"/>
       <c r="F44" s="28" t="s">
         <v>176</v>
       </c>
@@ -8877,21 +8874,21 @@
         <v>0</v>
       </c>
       <c r="H44" s="29"/>
-      <c r="I44" s="90" t="s">
+      <c r="I44" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J44" s="91"/>
-      <c r="K44" s="91"/>
-      <c r="L44" s="92"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="109"/>
+      <c r="L44" s="110"/>
     </row>
     <row r="45" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C45" s="50">
         <v>45884</v>
       </c>
-      <c r="D45" s="102" t="s">
+      <c r="D45" s="99" t="s">
         <v>357</v>
       </c>
-      <c r="E45" s="102"/>
+      <c r="E45" s="99"/>
       <c r="F45" s="28" t="s">
         <v>176</v>
       </c>
@@ -8899,21 +8896,21 @@
         <v>0</v>
       </c>
       <c r="H45" s="29"/>
-      <c r="I45" s="90" t="s">
+      <c r="I45" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J45" s="91"/>
-      <c r="K45" s="91"/>
-      <c r="L45" s="92"/>
+      <c r="J45" s="109"/>
+      <c r="K45" s="109"/>
+      <c r="L45" s="110"/>
     </row>
     <row r="46" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C46" s="50">
         <v>45884</v>
       </c>
-      <c r="D46" s="102" t="s">
+      <c r="D46" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="E46" s="102"/>
+      <c r="E46" s="99"/>
       <c r="F46" s="28" t="s">
         <v>176</v>
       </c>
@@ -8921,21 +8918,21 @@
         <v>0</v>
       </c>
       <c r="H46" s="29"/>
-      <c r="I46" s="90" t="s">
+      <c r="I46" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J46" s="91"/>
-      <c r="K46" s="91"/>
-      <c r="L46" s="92"/>
+      <c r="J46" s="109"/>
+      <c r="K46" s="109"/>
+      <c r="L46" s="110"/>
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="50">
         <v>45884</v>
       </c>
-      <c r="D47" s="102" t="s">
+      <c r="D47" s="99" t="s">
         <v>237</v>
       </c>
-      <c r="E47" s="102"/>
+      <c r="E47" s="99"/>
       <c r="F47" s="28" t="s">
         <v>176</v>
       </c>
@@ -8943,21 +8940,21 @@
         <v>0</v>
       </c>
       <c r="H47" s="29"/>
-      <c r="I47" s="90" t="s">
+      <c r="I47" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J47" s="91"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="92"/>
+      <c r="J47" s="109"/>
+      <c r="K47" s="109"/>
+      <c r="L47" s="110"/>
     </row>
     <row r="48" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C48" s="50">
         <v>45884</v>
       </c>
-      <c r="D48" s="102" t="s">
+      <c r="D48" s="99" t="s">
         <v>356</v>
       </c>
-      <c r="E48" s="102"/>
+      <c r="E48" s="99"/>
       <c r="F48" s="28" t="s">
         <v>176</v>
       </c>
@@ -8965,21 +8962,21 @@
         <v>0</v>
       </c>
       <c r="H48" s="29"/>
-      <c r="I48" s="90" t="s">
+      <c r="I48" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="J48" s="91"/>
-      <c r="K48" s="91"/>
-      <c r="L48" s="92"/>
+      <c r="J48" s="109"/>
+      <c r="K48" s="109"/>
+      <c r="L48" s="110"/>
     </row>
     <row r="49" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C49" s="51">
         <v>45885</v>
       </c>
-      <c r="D49" s="93" t="s">
+      <c r="D49" s="98" t="s">
         <v>196</v>
       </c>
-      <c r="E49" s="93"/>
+      <c r="E49" s="98"/>
       <c r="F49" s="25" t="s">
         <v>177</v>
       </c>
@@ -8987,21 +8984,21 @@
         <v>9</v>
       </c>
       <c r="H49" s="26"/>
-      <c r="I49" s="94" t="s">
+      <c r="I49" s="95" t="s">
         <v>197</v>
       </c>
-      <c r="J49" s="95"/>
-      <c r="K49" s="95"/>
-      <c r="L49" s="96"/>
+      <c r="J49" s="96"/>
+      <c r="K49" s="96"/>
+      <c r="L49" s="97"/>
     </row>
     <row r="50" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C50" s="51">
         <v>45885</v>
       </c>
-      <c r="D50" s="93" t="s">
+      <c r="D50" s="98" t="s">
         <v>350</v>
       </c>
-      <c r="E50" s="93"/>
+      <c r="E50" s="98"/>
       <c r="F50" s="25" t="s">
         <v>177</v>
       </c>
@@ -9011,19 +9008,19 @@
       <c r="H50" s="26">
         <v>2033.77</v>
       </c>
-      <c r="I50" s="94"/>
-      <c r="J50" s="95"/>
-      <c r="K50" s="95"/>
-      <c r="L50" s="96"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="96"/>
+      <c r="K50" s="96"/>
+      <c r="L50" s="97"/>
     </row>
     <row r="51" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C51" s="51">
         <v>45886</v>
       </c>
-      <c r="D51" s="93" t="s">
+      <c r="D51" s="98" t="s">
         <v>503</v>
       </c>
-      <c r="E51" s="93"/>
+      <c r="E51" s="98"/>
       <c r="F51" s="25" t="s">
         <v>177</v>
       </c>
@@ -9031,19 +9028,19 @@
         <v>8</v>
       </c>
       <c r="H51" s="26"/>
-      <c r="I51" s="94"/>
-      <c r="J51" s="95"/>
-      <c r="K51" s="95"/>
-      <c r="L51" s="96"/>
+      <c r="I51" s="95"/>
+      <c r="J51" s="96"/>
+      <c r="K51" s="96"/>
+      <c r="L51" s="97"/>
     </row>
     <row r="52" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C52" s="51">
         <v>45886</v>
       </c>
-      <c r="D52" s="93" t="s">
+      <c r="D52" s="98" t="s">
         <v>504</v>
       </c>
-      <c r="E52" s="93"/>
+      <c r="E52" s="98"/>
       <c r="F52" s="25" t="s">
         <v>177</v>
       </c>
@@ -9051,21 +9048,21 @@
         <v>5</v>
       </c>
       <c r="H52" s="26"/>
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="95" t="s">
         <v>531</v>
       </c>
-      <c r="J52" s="95"/>
-      <c r="K52" s="95"/>
-      <c r="L52" s="96"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="96"/>
+      <c r="L52" s="97"/>
     </row>
     <row r="53" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C53" s="51">
         <v>45886</v>
       </c>
-      <c r="D53" s="93" t="s">
+      <c r="D53" s="98" t="s">
         <v>217</v>
       </c>
-      <c r="E53" s="93"/>
+      <c r="E53" s="98"/>
       <c r="F53" s="25" t="s">
         <v>177</v>
       </c>
@@ -9075,19 +9072,19 @@
       <c r="H53" s="26">
         <v>1598.8</v>
       </c>
-      <c r="I53" s="94"/>
-      <c r="J53" s="95"/>
-      <c r="K53" s="95"/>
-      <c r="L53" s="96"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="96"/>
+      <c r="K53" s="96"/>
+      <c r="L53" s="97"/>
     </row>
     <row r="54" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C54" s="51">
         <v>45887</v>
       </c>
-      <c r="D54" s="93" t="s">
+      <c r="D54" s="98" t="s">
         <v>231</v>
       </c>
-      <c r="E54" s="93"/>
+      <c r="E54" s="98"/>
       <c r="F54" s="25" t="s">
         <v>180</v>
       </c>
@@ -9095,19 +9092,19 @@
         <v>6</v>
       </c>
       <c r="H54" s="26"/>
-      <c r="I54" s="94"/>
-      <c r="J54" s="95"/>
-      <c r="K54" s="95"/>
-      <c r="L54" s="96"/>
+      <c r="I54" s="95"/>
+      <c r="J54" s="96"/>
+      <c r="K54" s="96"/>
+      <c r="L54" s="97"/>
     </row>
     <row r="55" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C55" s="51">
         <v>45887</v>
       </c>
-      <c r="D55" s="93" t="s">
+      <c r="D55" s="98" t="s">
         <v>355</v>
       </c>
-      <c r="E55" s="93"/>
+      <c r="E55" s="98"/>
       <c r="F55" s="25" t="s">
         <v>180</v>
       </c>
@@ -9115,19 +9112,19 @@
         <v>4.5</v>
       </c>
       <c r="H55" s="26"/>
-      <c r="I55" s="94"/>
-      <c r="J55" s="95"/>
-      <c r="K55" s="95"/>
-      <c r="L55" s="96"/>
+      <c r="I55" s="95"/>
+      <c r="J55" s="96"/>
+      <c r="K55" s="96"/>
+      <c r="L55" s="97"/>
     </row>
     <row r="56" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C56" s="51">
         <v>45887</v>
       </c>
-      <c r="D56" s="93" t="s">
-        <v>534</v>
-      </c>
-      <c r="E56" s="93"/>
+      <c r="D56" s="98" t="s">
+        <v>533</v>
+      </c>
+      <c r="E56" s="98"/>
       <c r="F56" s="25" t="s">
         <v>180</v>
       </c>
@@ -9135,19 +9132,19 @@
         <v>5</v>
       </c>
       <c r="H56" s="26"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="96"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="96"/>
+      <c r="K56" s="96"/>
+      <c r="L56" s="97"/>
     </row>
     <row r="57" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C57" s="51">
         <v>45887</v>
       </c>
-      <c r="D57" s="93" t="s">
+      <c r="D57" s="98" t="s">
         <v>353</v>
       </c>
-      <c r="E57" s="93"/>
+      <c r="E57" s="98"/>
       <c r="F57" s="25" t="s">
         <v>180</v>
       </c>
@@ -9155,21 +9152,21 @@
         <v>14</v>
       </c>
       <c r="H57" s="26"/>
-      <c r="I57" s="94" t="s">
-        <v>535</v>
-      </c>
-      <c r="J57" s="95"/>
-      <c r="K57" s="95"/>
-      <c r="L57" s="96"/>
+      <c r="I57" s="95" t="s">
+        <v>534</v>
+      </c>
+      <c r="J57" s="96"/>
+      <c r="K57" s="96"/>
+      <c r="L57" s="97"/>
     </row>
     <row r="58" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C58" s="51">
         <v>45887</v>
       </c>
-      <c r="D58" s="93" t="s">
+      <c r="D58" s="98" t="s">
         <v>354</v>
       </c>
-      <c r="E58" s="93"/>
+      <c r="E58" s="98"/>
       <c r="F58" s="25" t="s">
         <v>180</v>
       </c>
@@ -9177,19 +9174,19 @@
         <v>4</v>
       </c>
       <c r="H58" s="26"/>
-      <c r="I58" s="94"/>
-      <c r="J58" s="95"/>
-      <c r="K58" s="95"/>
-      <c r="L58" s="96"/>
+      <c r="I58" s="95"/>
+      <c r="J58" s="96"/>
+      <c r="K58" s="96"/>
+      <c r="L58" s="97"/>
     </row>
     <row r="59" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C59" s="51">
         <v>45888</v>
       </c>
-      <c r="D59" s="93" t="s">
+      <c r="D59" s="98" t="s">
         <v>232</v>
       </c>
-      <c r="E59" s="93"/>
+      <c r="E59" s="98"/>
       <c r="F59" s="25" t="s">
         <v>181</v>
       </c>
@@ -9197,41 +9194,41 @@
         <v>12</v>
       </c>
       <c r="H59" s="26"/>
-      <c r="I59" s="94"/>
-      <c r="J59" s="95"/>
-      <c r="K59" s="95"/>
-      <c r="L59" s="96"/>
+      <c r="I59" s="95"/>
+      <c r="J59" s="96"/>
+      <c r="K59" s="96"/>
+      <c r="L59" s="97"/>
     </row>
     <row r="60" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C60" s="51">
         <v>45888</v>
       </c>
-      <c r="D60" s="93" t="s">
+      <c r="D60" s="98" t="s">
         <v>220</v>
       </c>
-      <c r="E60" s="93"/>
+      <c r="E60" s="98"/>
       <c r="F60" s="25" t="s">
         <v>177</v>
       </c>
       <c r="G60" s="26">
         <v>12</v>
       </c>
-      <c r="H60" s="26"/>
-      <c r="I60" s="94" t="s">
-        <v>532</v>
-      </c>
-      <c r="J60" s="95"/>
-      <c r="K60" s="95"/>
-      <c r="L60" s="96"/>
+      <c r="H60" s="26">
+        <v>1221.33</v>
+      </c>
+      <c r="I60" s="95"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="96"/>
+      <c r="L60" s="97"/>
     </row>
     <row r="61" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C61" s="51">
         <v>45889</v>
       </c>
-      <c r="D61" s="93" t="s">
+      <c r="D61" s="98" t="s">
         <v>351</v>
       </c>
-      <c r="E61" s="93"/>
+      <c r="E61" s="98"/>
       <c r="F61" s="25" t="s">
         <v>352</v>
       </c>
@@ -9239,19 +9236,19 @@
         <v>6</v>
       </c>
       <c r="H61" s="26"/>
-      <c r="I61" s="94"/>
-      <c r="J61" s="95"/>
-      <c r="K61" s="95"/>
-      <c r="L61" s="96"/>
+      <c r="I61" s="95"/>
+      <c r="J61" s="96"/>
+      <c r="K61" s="96"/>
+      <c r="L61" s="97"/>
     </row>
     <row r="62" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C62" s="51">
         <v>45890</v>
       </c>
-      <c r="D62" s="93" t="s">
+      <c r="D62" s="98" t="s">
         <v>218</v>
       </c>
-      <c r="E62" s="93"/>
+      <c r="E62" s="98"/>
       <c r="F62" s="25" t="s">
         <v>177</v>
       </c>
@@ -9259,19 +9256,19 @@
         <v>8</v>
       </c>
       <c r="H62" s="26"/>
-      <c r="I62" s="94"/>
-      <c r="J62" s="95"/>
-      <c r="K62" s="95"/>
-      <c r="L62" s="96"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="96"/>
+      <c r="K62" s="96"/>
+      <c r="L62" s="97"/>
     </row>
     <row r="63" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C63" s="51">
         <v>45890</v>
       </c>
-      <c r="D63" s="93" t="s">
+      <c r="D63" s="98" t="s">
         <v>505</v>
       </c>
-      <c r="E63" s="93"/>
+      <c r="E63" s="98"/>
       <c r="F63" s="25" t="s">
         <v>177</v>
       </c>
@@ -9279,19 +9276,19 @@
         <v>8</v>
       </c>
       <c r="H63" s="26"/>
-      <c r="I63" s="94"/>
-      <c r="J63" s="95"/>
-      <c r="K63" s="95"/>
-      <c r="L63" s="96"/>
+      <c r="I63" s="95"/>
+      <c r="J63" s="96"/>
+      <c r="K63" s="96"/>
+      <c r="L63" s="97"/>
     </row>
     <row r="64" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C64" s="51">
         <v>45891</v>
       </c>
-      <c r="D64" s="93" t="s">
+      <c r="D64" s="98" t="s">
         <v>215</v>
       </c>
-      <c r="E64" s="93"/>
+      <c r="E64" s="98"/>
       <c r="F64" s="25" t="s">
         <v>177</v>
       </c>
@@ -9299,21 +9296,21 @@
         <v>13</v>
       </c>
       <c r="H64" s="26"/>
-      <c r="I64" s="94" t="s">
+      <c r="I64" s="95" t="s">
         <v>229</v>
       </c>
-      <c r="J64" s="95"/>
-      <c r="K64" s="95"/>
-      <c r="L64" s="96"/>
+      <c r="J64" s="96"/>
+      <c r="K64" s="96"/>
+      <c r="L64" s="97"/>
     </row>
     <row r="65" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C65" s="51">
         <v>45891</v>
       </c>
-      <c r="D65" s="93" t="s">
+      <c r="D65" s="98" t="s">
         <v>230</v>
       </c>
-      <c r="E65" s="93"/>
+      <c r="E65" s="98"/>
       <c r="F65" s="25" t="s">
         <v>177</v>
       </c>
@@ -9321,19 +9318,19 @@
         <v>5</v>
       </c>
       <c r="H65" s="26"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="95"/>
-      <c r="K65" s="95"/>
-      <c r="L65" s="96"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="96"/>
+      <c r="K65" s="96"/>
+      <c r="L65" s="97"/>
     </row>
     <row r="66" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C66" s="51">
         <v>45891</v>
       </c>
-      <c r="D66" s="93" t="s">
+      <c r="D66" s="98" t="s">
         <v>216</v>
       </c>
-      <c r="E66" s="93"/>
+      <c r="E66" s="98"/>
       <c r="F66" s="25" t="s">
         <v>177</v>
       </c>
@@ -9343,19 +9340,19 @@
       <c r="H66" s="26">
         <v>1598.8</v>
       </c>
-      <c r="I66" s="94"/>
-      <c r="J66" s="95"/>
-      <c r="K66" s="95"/>
-      <c r="L66" s="96"/>
+      <c r="I66" s="95"/>
+      <c r="J66" s="96"/>
+      <c r="K66" s="96"/>
+      <c r="L66" s="97"/>
     </row>
     <row r="67" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C67" s="52">
         <v>45892</v>
       </c>
-      <c r="D67" s="105" t="s">
+      <c r="D67" s="90" t="s">
         <v>513</v>
       </c>
-      <c r="E67" s="105"/>
+      <c r="E67" s="90"/>
       <c r="F67" s="22" t="s">
         <v>514</v>
       </c>
@@ -9372,10 +9369,10 @@
       <c r="C68" s="52">
         <v>45894</v>
       </c>
-      <c r="D68" s="105" t="s">
+      <c r="D68" s="90" t="s">
         <v>507</v>
       </c>
-      <c r="E68" s="105"/>
+      <c r="E68" s="90"/>
       <c r="F68" s="22" t="s">
         <v>179</v>
       </c>
@@ -9383,21 +9380,21 @@
         <v>17</v>
       </c>
       <c r="H68" s="23"/>
-      <c r="I68" s="103" t="s">
+      <c r="I68" s="101" t="s">
         <v>408</v>
       </c>
-      <c r="J68" s="106"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="104"/>
+      <c r="J68" s="102"/>
+      <c r="K68" s="102"/>
+      <c r="L68" s="103"/>
     </row>
     <row r="69" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C69" s="52">
         <v>45894</v>
       </c>
-      <c r="D69" s="105" t="s">
+      <c r="D69" s="90" t="s">
         <v>506</v>
       </c>
-      <c r="E69" s="105"/>
+      <c r="E69" s="90"/>
       <c r="F69" s="22" t="s">
         <v>179</v>
       </c>
@@ -9405,19 +9402,19 @@
         <v>8</v>
       </c>
       <c r="H69" s="23"/>
-      <c r="I69" s="103"/>
-      <c r="J69" s="106"/>
-      <c r="K69" s="106"/>
-      <c r="L69" s="104"/>
+      <c r="I69" s="101"/>
+      <c r="J69" s="102"/>
+      <c r="K69" s="102"/>
+      <c r="L69" s="103"/>
     </row>
     <row r="70" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C70" s="52">
         <v>45894</v>
       </c>
-      <c r="D70" s="105" t="s">
+      <c r="D70" s="90" t="s">
         <v>190</v>
       </c>
-      <c r="E70" s="105"/>
+      <c r="E70" s="90"/>
       <c r="F70" s="22" t="s">
         <v>188</v>
       </c>
@@ -9425,19 +9422,19 @@
         <v>12</v>
       </c>
       <c r="H70" s="23"/>
-      <c r="I70" s="103"/>
-      <c r="J70" s="106"/>
-      <c r="K70" s="106"/>
-      <c r="L70" s="104"/>
+      <c r="I70" s="101"/>
+      <c r="J70" s="102"/>
+      <c r="K70" s="102"/>
+      <c r="L70" s="103"/>
     </row>
     <row r="71" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C71" s="52">
         <v>45895</v>
       </c>
-      <c r="D71" s="105" t="s">
+      <c r="D71" s="90" t="s">
         <v>348</v>
       </c>
-      <c r="E71" s="105"/>
+      <c r="E71" s="90"/>
       <c r="F71" s="22" t="s">
         <v>189</v>
       </c>
@@ -9445,19 +9442,19 @@
         <v>8</v>
       </c>
       <c r="H71" s="23"/>
-      <c r="I71" s="103"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="106"/>
-      <c r="L71" s="104"/>
+      <c r="I71" s="101"/>
+      <c r="J71" s="102"/>
+      <c r="K71" s="102"/>
+      <c r="L71" s="103"/>
     </row>
     <row r="72" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C72" s="52">
         <v>45895</v>
       </c>
-      <c r="D72" s="105" t="s">
+      <c r="D72" s="90" t="s">
         <v>349</v>
       </c>
-      <c r="E72" s="105"/>
+      <c r="E72" s="90"/>
       <c r="F72" s="22" t="s">
         <v>189</v>
       </c>
@@ -9465,19 +9462,19 @@
         <v>4</v>
       </c>
       <c r="H72" s="23"/>
-      <c r="I72" s="103"/>
-      <c r="J72" s="106"/>
-      <c r="K72" s="106"/>
-      <c r="L72" s="104"/>
+      <c r="I72" s="101"/>
+      <c r="J72" s="102"/>
+      <c r="K72" s="102"/>
+      <c r="L72" s="103"/>
     </row>
     <row r="73" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C73" s="52">
         <v>45897</v>
       </c>
-      <c r="D73" s="105" t="s">
+      <c r="D73" s="90" t="s">
         <v>347</v>
       </c>
-      <c r="E73" s="105"/>
+      <c r="E73" s="90"/>
       <c r="F73" s="22" t="s">
         <v>179</v>
       </c>
@@ -9485,21 +9482,21 @@
         <v>0</v>
       </c>
       <c r="H73" s="23"/>
-      <c r="I73" s="103" t="s">
+      <c r="I73" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J73" s="106"/>
-      <c r="K73" s="106"/>
-      <c r="L73" s="104"/>
+      <c r="J73" s="102"/>
+      <c r="K73" s="102"/>
+      <c r="L73" s="103"/>
     </row>
     <row r="74" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C74" s="52">
         <v>45897</v>
       </c>
-      <c r="D74" s="105" t="s">
+      <c r="D74" s="90" t="s">
         <v>412</v>
       </c>
-      <c r="E74" s="105"/>
+      <c r="E74" s="90"/>
       <c r="F74" s="22" t="s">
         <v>179</v>
       </c>
@@ -9507,21 +9504,21 @@
         <v>0</v>
       </c>
       <c r="H74" s="23"/>
-      <c r="I74" s="103" t="s">
+      <c r="I74" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J74" s="106"/>
-      <c r="K74" s="106"/>
-      <c r="L74" s="104"/>
+      <c r="J74" s="102"/>
+      <c r="K74" s="102"/>
+      <c r="L74" s="103"/>
     </row>
     <row r="75" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C75" s="52">
         <v>45897</v>
       </c>
-      <c r="D75" s="105" t="s">
+      <c r="D75" s="90" t="s">
         <v>210</v>
       </c>
-      <c r="E75" s="105"/>
+      <c r="E75" s="90"/>
       <c r="F75" s="22" t="s">
         <v>179</v>
       </c>
@@ -9529,21 +9526,21 @@
         <v>0</v>
       </c>
       <c r="H75" s="23"/>
-      <c r="I75" s="103" t="s">
+      <c r="I75" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J75" s="106"/>
-      <c r="K75" s="106"/>
-      <c r="L75" s="104"/>
+      <c r="J75" s="102"/>
+      <c r="K75" s="102"/>
+      <c r="L75" s="103"/>
     </row>
     <row r="76" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C76" s="52">
         <v>45897</v>
       </c>
-      <c r="D76" s="105" t="s">
+      <c r="D76" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="E76" s="105"/>
+      <c r="E76" s="90"/>
       <c r="F76" s="22" t="s">
         <v>179</v>
       </c>
@@ -9551,21 +9548,21 @@
         <v>10</v>
       </c>
       <c r="H76" s="23"/>
-      <c r="I76" s="103" t="s">
+      <c r="I76" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J76" s="106"/>
-      <c r="K76" s="106"/>
-      <c r="L76" s="104"/>
+      <c r="J76" s="102"/>
+      <c r="K76" s="102"/>
+      <c r="L76" s="103"/>
     </row>
     <row r="77" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C77" s="52">
         <v>45897</v>
       </c>
-      <c r="D77" s="105" t="s">
+      <c r="D77" s="90" t="s">
         <v>410</v>
       </c>
-      <c r="E77" s="105"/>
+      <c r="E77" s="90"/>
       <c r="F77" s="22" t="s">
         <v>179</v>
       </c>
@@ -9573,21 +9570,21 @@
         <v>0</v>
       </c>
       <c r="H77" s="23"/>
-      <c r="I77" s="103" t="s">
+      <c r="I77" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J77" s="106"/>
-      <c r="K77" s="106"/>
-      <c r="L77" s="104"/>
+      <c r="J77" s="102"/>
+      <c r="K77" s="102"/>
+      <c r="L77" s="103"/>
     </row>
     <row r="78" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C78" s="52">
         <v>45898</v>
       </c>
-      <c r="D78" s="105" t="s">
+      <c r="D78" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="E78" s="105"/>
+      <c r="E78" s="90"/>
       <c r="F78" s="22" t="s">
         <v>179</v>
       </c>
@@ -9595,21 +9592,21 @@
         <v>7</v>
       </c>
       <c r="H78" s="23"/>
-      <c r="I78" s="103" t="s">
+      <c r="I78" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J78" s="106"/>
-      <c r="K78" s="106"/>
-      <c r="L78" s="104"/>
+      <c r="J78" s="102"/>
+      <c r="K78" s="102"/>
+      <c r="L78" s="103"/>
     </row>
     <row r="79" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C79" s="52">
         <v>45898</v>
       </c>
-      <c r="D79" s="105" t="s">
+      <c r="D79" s="90" t="s">
         <v>509</v>
       </c>
-      <c r="E79" s="105"/>
+      <c r="E79" s="90"/>
       <c r="F79" s="22" t="s">
         <v>179</v>
       </c>
@@ -9617,21 +9614,21 @@
         <v>0</v>
       </c>
       <c r="H79" s="23"/>
-      <c r="I79" s="103" t="s">
+      <c r="I79" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J79" s="106"/>
-      <c r="K79" s="106"/>
-      <c r="L79" s="104"/>
+      <c r="J79" s="102"/>
+      <c r="K79" s="102"/>
+      <c r="L79" s="103"/>
     </row>
     <row r="80" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C80" s="52">
         <v>45898</v>
       </c>
-      <c r="D80" s="105" t="s">
+      <c r="D80" s="90" t="s">
         <v>411</v>
       </c>
-      <c r="E80" s="105"/>
+      <c r="E80" s="90"/>
       <c r="F80" s="22" t="s">
         <v>179</v>
       </c>
@@ -9639,21 +9636,21 @@
         <v>0</v>
       </c>
       <c r="H80" s="23"/>
-      <c r="I80" s="103" t="s">
+      <c r="I80" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J80" s="106"/>
-      <c r="K80" s="106"/>
-      <c r="L80" s="104"/>
+      <c r="J80" s="102"/>
+      <c r="K80" s="102"/>
+      <c r="L80" s="103"/>
     </row>
     <row r="81" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C81" s="52">
         <v>45898</v>
       </c>
-      <c r="D81" s="105" t="s">
+      <c r="D81" s="90" t="s">
         <v>206</v>
       </c>
-      <c r="E81" s="105"/>
+      <c r="E81" s="90"/>
       <c r="F81" s="22" t="s">
         <v>179</v>
       </c>
@@ -9661,21 +9658,21 @@
         <v>0</v>
       </c>
       <c r="H81" s="23"/>
-      <c r="I81" s="103" t="s">
+      <c r="I81" s="101" t="s">
         <v>528</v>
       </c>
-      <c r="J81" s="106"/>
-      <c r="K81" s="106"/>
-      <c r="L81" s="104"/>
+      <c r="J81" s="102"/>
+      <c r="K81" s="102"/>
+      <c r="L81" s="103"/>
     </row>
     <row r="82" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C82" s="52">
         <v>45898</v>
       </c>
-      <c r="D82" s="103" t="s">
+      <c r="D82" s="101" t="s">
         <v>508</v>
       </c>
-      <c r="E82" s="104"/>
+      <c r="E82" s="103"/>
       <c r="F82" s="22" t="s">
         <v>179</v>
       </c>
@@ -9683,21 +9680,21 @@
         <v>0</v>
       </c>
       <c r="H82" s="23"/>
-      <c r="I82" s="103" t="s">
+      <c r="I82" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J82" s="106"/>
-      <c r="K82" s="106"/>
-      <c r="L82" s="104"/>
+      <c r="J82" s="102"/>
+      <c r="K82" s="102"/>
+      <c r="L82" s="103"/>
     </row>
     <row r="83" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C83" s="52">
         <v>45899</v>
       </c>
-      <c r="D83" s="103" t="s">
+      <c r="D83" s="101" t="s">
         <v>515</v>
       </c>
-      <c r="E83" s="104"/>
+      <c r="E83" s="103"/>
       <c r="F83" s="22" t="s">
         <v>179</v>
       </c>
@@ -9716,10 +9713,10 @@
       <c r="C84" s="52">
         <v>45899</v>
       </c>
-      <c r="D84" s="105" t="s">
+      <c r="D84" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="E84" s="105"/>
+      <c r="E84" s="90"/>
       <c r="F84" s="22" t="s">
         <v>179</v>
       </c>
@@ -9727,21 +9724,21 @@
         <v>5</v>
       </c>
       <c r="H84" s="23"/>
-      <c r="I84" s="103" t="s">
+      <c r="I84" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J84" s="106"/>
-      <c r="K84" s="106"/>
-      <c r="L84" s="104"/>
+      <c r="J84" s="102"/>
+      <c r="K84" s="102"/>
+      <c r="L84" s="103"/>
     </row>
     <row r="85" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C85" s="52">
         <v>45899</v>
       </c>
-      <c r="D85" s="105" t="s">
+      <c r="D85" s="90" t="s">
         <v>409</v>
       </c>
-      <c r="E85" s="105"/>
+      <c r="E85" s="90"/>
       <c r="F85" s="22" t="s">
         <v>179</v>
       </c>
@@ -9749,29 +9746,29 @@
         <v>0</v>
       </c>
       <c r="H85" s="23"/>
-      <c r="I85" s="103" t="s">
+      <c r="I85" s="101" t="s">
         <v>527</v>
       </c>
-      <c r="J85" s="106"/>
-      <c r="K85" s="106"/>
-      <c r="L85" s="104"/>
+      <c r="J85" s="102"/>
+      <c r="K85" s="102"/>
+      <c r="L85" s="103"/>
     </row>
     <row r="86" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C86" s="1"/>
-      <c r="D86" s="78"/>
-      <c r="E86" s="78"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="70"/>
       <c r="F86" s="3"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
-      <c r="I86" s="85"/>
-      <c r="J86" s="86"/>
-      <c r="K86" s="86"/>
-      <c r="L86" s="87"/>
+      <c r="I86" s="79"/>
+      <c r="J86" s="80"/>
+      <c r="K86" s="80"/>
+      <c r="L86" s="81"/>
     </row>
     <row r="87" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C87" s="1"/>
-      <c r="D87" s="78"/>
-      <c r="E87" s="78"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
       <c r="F87" s="15"/>
       <c r="G87" s="4">
         <f>SUM(G17:G85)</f>
@@ -9779,7 +9776,7 @@
       </c>
       <c r="H87" s="5">
         <f>SUM(H17:H85)</f>
-        <v>17230.91</v>
+        <v>18452.240000000002</v>
       </c>
       <c r="I87" s="67"/>
       <c r="J87" s="68"/>
@@ -9787,28 +9784,28 @@
       <c r="L87" s="69"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C88" s="83"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="83"/>
-      <c r="F88" s="83"/>
-      <c r="G88" s="83"/>
-      <c r="H88" s="83"/>
-      <c r="I88" s="83"/>
-      <c r="J88" s="83"/>
-      <c r="K88" s="83"/>
-      <c r="L88" s="83"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
+      <c r="I88" s="82"/>
+      <c r="J88" s="82"/>
+      <c r="K88" s="82"/>
+      <c r="L88" s="82"/>
     </row>
     <row r="89" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C89" s="84"/>
-      <c r="D89" s="84"/>
-      <c r="E89" s="84"/>
-      <c r="F89" s="84"/>
-      <c r="G89" s="84"/>
-      <c r="H89" s="84"/>
-      <c r="I89" s="84"/>
-      <c r="J89" s="84"/>
-      <c r="K89" s="84"/>
-      <c r="L89" s="84"/>
+      <c r="C89" s="83"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="83"/>
+      <c r="H89" s="83"/>
+      <c r="I89" s="83"/>
+      <c r="J89" s="83"/>
+      <c r="K89" s="83"/>
+      <c r="L89" s="83"/>
     </row>
     <row r="90" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C90" s="63" t="s">
@@ -9874,11 +9871,11 @@
       <c r="I92" s="46" t="s">
         <v>502</v>
       </c>
-      <c r="J92" s="110" t="s">
+      <c r="J92" s="100" t="s">
         <v>517</v>
       </c>
-      <c r="K92" s="110"/>
-      <c r="L92" s="110"/>
+      <c r="K92" s="100"/>
+      <c r="L92" s="100"/>
     </row>
     <row r="93" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C93" s="27">
@@ -9900,9 +9897,9 @@
         <v>1220</v>
       </c>
       <c r="I93" s="28"/>
-      <c r="J93" s="102"/>
-      <c r="K93" s="102"/>
-      <c r="L93" s="102"/>
+      <c r="J93" s="99"/>
+      <c r="K93" s="99"/>
+      <c r="L93" s="99"/>
     </row>
     <row r="94" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C94" s="27">
@@ -9924,11 +9921,11 @@
         <v>1914</v>
       </c>
       <c r="I94" s="28"/>
-      <c r="J94" s="102" t="s">
+      <c r="J94" s="99" t="s">
         <v>516</v>
       </c>
-      <c r="K94" s="102"/>
-      <c r="L94" s="102"/>
+      <c r="K94" s="99"/>
+      <c r="L94" s="99"/>
     </row>
     <row r="95" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C95" s="24">
@@ -9938,7 +9935,7 @@
         <v>177</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F95" s="25" t="s">
         <v>194</v>
@@ -9948,9 +9945,9 @@
       </c>
       <c r="H95" s="25"/>
       <c r="I95" s="25"/>
-      <c r="J95" s="93"/>
-      <c r="K95" s="93"/>
-      <c r="L95" s="93"/>
+      <c r="J95" s="98"/>
+      <c r="K95" s="98"/>
+      <c r="L95" s="98"/>
     </row>
     <row r="96" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C96" s="24">
@@ -9970,9 +9967,9 @@
       </c>
       <c r="H96" s="25"/>
       <c r="I96" s="25"/>
-      <c r="J96" s="93"/>
-      <c r="K96" s="93"/>
-      <c r="L96" s="93"/>
+      <c r="J96" s="98"/>
+      <c r="K96" s="98"/>
+      <c r="L96" s="98"/>
     </row>
     <row r="97" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C97" s="24">
@@ -9992,9 +9989,9 @@
       </c>
       <c r="H97" s="25"/>
       <c r="I97" s="25"/>
-      <c r="J97" s="93"/>
-      <c r="K97" s="93"/>
-      <c r="L97" s="93"/>
+      <c r="J97" s="98"/>
+      <c r="K97" s="98"/>
+      <c r="L97" s="98"/>
     </row>
     <row r="98" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C98" s="24">
@@ -10014,9 +10011,9 @@
       </c>
       <c r="H98" s="25"/>
       <c r="I98" s="25"/>
-      <c r="J98" s="93"/>
-      <c r="K98" s="93"/>
-      <c r="L98" s="93"/>
+      <c r="J98" s="98"/>
+      <c r="K98" s="98"/>
+      <c r="L98" s="98"/>
     </row>
     <row r="99" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C99" s="53">
@@ -10036,9 +10033,9 @@
       </c>
       <c r="H99" s="25"/>
       <c r="I99" s="25"/>
-      <c r="J99" s="93"/>
-      <c r="K99" s="93"/>
-      <c r="L99" s="93"/>
+      <c r="J99" s="98"/>
+      <c r="K99" s="98"/>
+      <c r="L99" s="98"/>
     </row>
     <row r="100" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C100" s="53">
@@ -10058,9 +10055,9 @@
       </c>
       <c r="H100" s="25"/>
       <c r="I100" s="25"/>
-      <c r="J100" s="93"/>
-      <c r="K100" s="93"/>
-      <c r="L100" s="93"/>
+      <c r="J100" s="98"/>
+      <c r="K100" s="98"/>
+      <c r="L100" s="98"/>
     </row>
     <row r="101" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C101" s="21">
@@ -10084,11 +10081,11 @@
       <c r="I101" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="J101" s="105" t="s">
+      <c r="J101" s="90" t="s">
         <v>516</v>
       </c>
-      <c r="K101" s="105"/>
-      <c r="L101" s="105"/>
+      <c r="K101" s="90"/>
+      <c r="L101" s="90"/>
     </row>
     <row r="102" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C102" s="21">
@@ -10108,9 +10105,9 @@
       </c>
       <c r="H102" s="22"/>
       <c r="I102" s="22"/>
-      <c r="J102" s="105"/>
-      <c r="K102" s="105"/>
-      <c r="L102" s="105"/>
+      <c r="J102" s="90"/>
+      <c r="K102" s="90"/>
+      <c r="L102" s="90"/>
     </row>
     <row r="103" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C103" s="21">
@@ -10130,9 +10127,9 @@
       </c>
       <c r="H103" s="22"/>
       <c r="I103" s="22"/>
-      <c r="J103" s="105"/>
-      <c r="K103" s="105"/>
-      <c r="L103" s="105"/>
+      <c r="J103" s="90"/>
+      <c r="K103" s="90"/>
+      <c r="L103" s="90"/>
     </row>
     <row r="104" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C104" s="21">
@@ -10152,9 +10149,9 @@
       </c>
       <c r="H104" s="22"/>
       <c r="I104" s="22"/>
-      <c r="J104" s="105"/>
-      <c r="K104" s="105"/>
-      <c r="L104" s="105"/>
+      <c r="J104" s="90"/>
+      <c r="K104" s="90"/>
+      <c r="L104" s="90"/>
     </row>
     <row r="105" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C105" s="21">
@@ -10174,9 +10171,9 @@
       </c>
       <c r="H105" s="22"/>
       <c r="I105" s="22"/>
-      <c r="J105" s="105"/>
-      <c r="K105" s="105"/>
-      <c r="L105" s="105"/>
+      <c r="J105" s="90"/>
+      <c r="K105" s="90"/>
+      <c r="L105" s="90"/>
     </row>
     <row r="106" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C106" s="21">
@@ -10196,11 +10193,11 @@
       </c>
       <c r="H106" s="22"/>
       <c r="I106" s="22"/>
-      <c r="J106" s="103" t="s">
+      <c r="J106" s="101" t="s">
         <v>193</v>
       </c>
-      <c r="K106" s="106"/>
-      <c r="L106" s="104"/>
+      <c r="K106" s="102"/>
+      <c r="L106" s="103"/>
     </row>
     <row r="107" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C107" s="21">
@@ -10220,9 +10217,9 @@
       </c>
       <c r="H107" s="22"/>
       <c r="I107" s="22"/>
-      <c r="J107" s="105"/>
-      <c r="K107" s="105"/>
-      <c r="L107" s="105"/>
+      <c r="J107" s="90"/>
+      <c r="K107" s="90"/>
+      <c r="L107" s="90"/>
     </row>
     <row r="108" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C108" s="21">
@@ -10244,9 +10241,9 @@
         <v>2542</v>
       </c>
       <c r="I108" s="22"/>
-      <c r="J108" s="105"/>
-      <c r="K108" s="105"/>
-      <c r="L108" s="105"/>
+      <c r="J108" s="90"/>
+      <c r="K108" s="90"/>
+      <c r="L108" s="90"/>
     </row>
     <row r="109" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C109" s="21">
@@ -10266,9 +10263,9 @@
       </c>
       <c r="H109" s="22"/>
       <c r="I109" s="22"/>
-      <c r="J109" s="105"/>
-      <c r="K109" s="105"/>
-      <c r="L109" s="105"/>
+      <c r="J109" s="90"/>
+      <c r="K109" s="90"/>
+      <c r="L109" s="90"/>
     </row>
     <row r="110" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C110" s="21">
@@ -10288,9 +10285,9 @@
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="22"/>
-      <c r="J110" s="105"/>
-      <c r="K110" s="105"/>
-      <c r="L110" s="105"/>
+      <c r="J110" s="90"/>
+      <c r="K110" s="90"/>
+      <c r="L110" s="90"/>
     </row>
     <row r="111" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C111" s="21">
@@ -10312,9 +10309,9 @@
         <v>640.64</v>
       </c>
       <c r="I111" s="22"/>
-      <c r="J111" s="105"/>
-      <c r="K111" s="105"/>
-      <c r="L111" s="105"/>
+      <c r="J111" s="90"/>
+      <c r="K111" s="90"/>
+      <c r="L111" s="90"/>
     </row>
     <row r="112" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C112" s="21">
@@ -10336,9 +10333,9 @@
         <v>693.52</v>
       </c>
       <c r="I112" s="22"/>
-      <c r="J112" s="105"/>
-      <c r="K112" s="105"/>
-      <c r="L112" s="105"/>
+      <c r="J112" s="90"/>
+      <c r="K112" s="90"/>
+      <c r="L112" s="90"/>
     </row>
     <row r="113" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C113" s="1"/>
@@ -10348,9 +10345,9 @@
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="78"/>
-      <c r="K113" s="78"/>
-      <c r="L113" s="78"/>
+      <c r="J113" s="70"/>
+      <c r="K113" s="70"/>
+      <c r="L113" s="70"/>
     </row>
     <row r="114" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C114" s="13"/>
@@ -10370,7 +10367,7 @@
       <c r="K114" s="66"/>
       <c r="L114" s="66"/>
     </row>
-    <row r="115" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D115" s="44"/>
       <c r="E115" s="44"/>
       <c r="F115" s="44"/>
@@ -10383,6 +10380,187 @@
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="D13:L14"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="J105:L105"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J103:L103"/>
+    <mergeCell ref="C88:L89"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J104:L104"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="I69:L69"/>
+    <mergeCell ref="I68:L68"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="I72:L72"/>
+    <mergeCell ref="I70:L70"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="I73:L73"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="I57:L57"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="N8:P9"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J98:L98"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="N24:R25"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I65:L65"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="J92:L92"/>
+    <mergeCell ref="I84:L84"/>
+    <mergeCell ref="I85:L85"/>
+    <mergeCell ref="I81:L81"/>
+    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="I58:L58"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="J111:L111"/>
+    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="I75:L75"/>
+    <mergeCell ref="I76:L76"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="I80:L80"/>
+    <mergeCell ref="I74:L74"/>
     <mergeCell ref="J113:L113"/>
     <mergeCell ref="J114:L114"/>
     <mergeCell ref="I87:L87"/>
@@ -10407,187 +10585,6 @@
     <mergeCell ref="J95:L95"/>
     <mergeCell ref="J97:L97"/>
     <mergeCell ref="J93:L93"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I65:L65"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="J92:L92"/>
-    <mergeCell ref="I84:L84"/>
-    <mergeCell ref="I85:L85"/>
-    <mergeCell ref="I81:L81"/>
-    <mergeCell ref="I78:L78"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="I58:L58"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="J111:L111"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J98:L98"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="N24:R25"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="N8:P9"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="I73:L73"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="I66:L66"/>
-    <mergeCell ref="I60:L60"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="I55:L55"/>
-    <mergeCell ref="I57:L57"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="I82:L82"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="I69:L69"/>
-    <mergeCell ref="I68:L68"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="I71:L71"/>
-    <mergeCell ref="I72:L72"/>
-    <mergeCell ref="I70:L70"/>
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="I80:L80"/>
-    <mergeCell ref="I74:L74"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="J105:L105"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J103:L103"/>
-    <mergeCell ref="C88:L89"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J104:L104"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="D13:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="D26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -10659,12 +10656,12 @@
       <c r="G3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="81"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
       <c r="L3" s="6" t="s">
         <v>5</v>
       </c>
@@ -10698,10 +10695,10 @@
         <v>2001</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="87"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="81"/>
       <c r="L4" s="39">
         <f>C4-B4</f>
         <v>8</v>
@@ -10727,10 +10724,10 @@
         <v>400</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="87"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="81"/>
       <c r="L5" s="39">
         <f t="shared" ref="L5:L6" si="0">C5-B5</f>
         <v>1</v>
@@ -10756,12 +10753,12 @@
         <v>746</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="85">
+      <c r="H6" s="79">
         <v>680</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="87"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="81"/>
       <c r="L6" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10787,10 +10784,10 @@
         <v>625</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="87"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="81"/>
       <c r="L7" s="39">
         <f t="shared" ref="L7" si="1">C7-B7</f>
         <v>1</v>
@@ -10806,14 +10803,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="87"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="81"/>
       <c r="L8" s="39"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
     </row>
     <row r="9" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
@@ -10828,17 +10825,17 @@
         <f>F9*$R$3</f>
         <v>50167.600000000006</v>
       </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="87"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="81"/>
       <c r="L9" s="3">
         <f>SUM(L4:L8)</f>
         <v>14</v>
       </c>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
     </row>
     <row r="10" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B10" s="58"/>
@@ -10881,25 +10878,25 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="79" t="s">
+      <c r="Q11" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="81"/>
+      <c r="R11" s="78"/>
     </row>
     <row r="12" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="88"/>
       <c r="N12" s="3" t="s">
         <v>405</v>
       </c>
@@ -10907,8 +10904,8 @@
         <v>1299</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="73"/>
-      <c r="R12" s="74"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
@@ -10945,8 +10942,8 @@
         <v>499</v>
       </c>
       <c r="P13" s="4"/>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="74"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="85"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
@@ -10962,10 +10959,10 @@
         <v>69</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
       <c r="N14" s="3" t="s">
         <v>450</v>
       </c>
@@ -10973,8 +10970,8 @@
         <v>70</v>
       </c>
       <c r="P14" s="4"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
@@ -10990,12 +10987,12 @@
         <v>0</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="78" t="s">
+      <c r="I15" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
       <c r="N15" s="3" t="s">
         <v>464</v>
       </c>
@@ -11003,8 +11000,8 @@
         <v>175</v>
       </c>
       <c r="P15" s="4"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="74"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
@@ -11020,17 +11017,17 @@
         <v>0</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="78" t="s">
+      <c r="I16" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
       <c r="N16" s="3"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="74"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="85"/>
     </row>
     <row r="17" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
@@ -11046,17 +11043,17 @@
         <v>0</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="78" t="s">
+      <c r="I17" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
       <c r="N17" s="3"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="74"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="85"/>
     </row>
     <row r="18" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
@@ -11072,17 +11069,17 @@
         <v>0</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="78" t="s">
+      <c r="I18" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
       <c r="N18" s="3"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="74"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="85"/>
     </row>
     <row r="19" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
@@ -11098,17 +11095,17 @@
         <v>0</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="78" t="s">
+      <c r="I19" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
       <c r="N19" s="3"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="74"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="85"/>
     </row>
     <row r="20" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
@@ -11124,12 +11121,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="78" t="s">
+      <c r="I20" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
       <c r="N20" s="3"/>
       <c r="O20" s="18">
         <f>SUM(O12:O19)</f>
@@ -11139,8 +11136,8 @@
         <f>O20*$R$3</f>
         <v>27171.9</v>
       </c>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="74"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
@@ -11156,17 +11153,17 @@
         <v>0</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="78" t="s">
+      <c r="I21" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
@@ -11182,15 +11179,15 @@
         <v>169</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
     </row>
     <row r="23" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
@@ -11206,12 +11203,12 @@
         <v>0</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="78" t="s">
+      <c r="I23" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
       <c r="N23" s="63" t="s">
         <v>38</v>
       </c>
@@ -11235,10 +11232,10 @@
         <v>50</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
       <c r="N24" s="6" t="s">
         <v>20</v>
       </c>
@@ -11268,12 +11265,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="78" t="s">
+      <c r="I25" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
       <c r="N25" s="13"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -11295,12 +11292,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="78" t="s">
+      <c r="I26" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
       <c r="N26" s="13"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -11322,12 +11319,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="78" t="s">
+      <c r="I27" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="5">
@@ -11351,10 +11348,10 @@
         <v>155</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
       <c r="N28" s="19"/>
       <c r="O28" s="19"/>
       <c r="P28" s="19"/>
@@ -11471,12 +11468,12 @@
         <v>0</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="78" t="s">
+      <c r="I32" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
       <c r="N32" s="3"/>
       <c r="O32" s="4"/>
       <c r="P32" s="3"/>
@@ -11499,12 +11496,12 @@
         <v>0</v>
       </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="78" t="s">
+      <c r="I33" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
@@ -11520,10 +11517,10 @@
         <v>60</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
     </row>
     <row r="35" spans="2:15" ht="19" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
@@ -11539,12 +11536,12 @@
         <v>0</v>
       </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="78" t="s">
+      <c r="I35" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J35" s="78"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="78"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
       <c r="N35" s="63" t="s">
         <v>61</v>
       </c>
@@ -11564,12 +11561,12 @@
         <v>0</v>
       </c>
       <c r="H36" s="1"/>
-      <c r="I36" s="78" t="s">
+      <c r="I36" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
       <c r="N36" s="6" t="s">
         <v>67</v>
       </c>
@@ -11591,12 +11588,12 @@
         <v>0</v>
       </c>
       <c r="H37" s="1"/>
-      <c r="I37" s="78" t="s">
+      <c r="I37" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
       <c r="N37" s="5">
         <f>O7+G9+H51+P20+P27+T32+H77</f>
         <v>138449.00000000003</v>
@@ -11617,10 +11614,10 @@
         <v>20</v>
       </c>
       <c r="H38" s="1"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B39" s="1"/>
@@ -11636,10 +11633,10 @@
         <v>20</v>
       </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="1"/>
@@ -11655,10 +11652,10 @@
         <v>20</v>
       </c>
       <c r="H40" s="1"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
@@ -11674,10 +11671,10 @@
         <v>25</v>
       </c>
       <c r="H41" s="1"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B42" s="1"/>
@@ -11693,10 +11690,10 @@
         <v>145</v>
       </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B43" s="1"/>
@@ -11712,12 +11709,12 @@
         <v>103</v>
       </c>
       <c r="H43" s="1"/>
-      <c r="I43" s="78" t="s">
+      <c r="I43" s="70" t="s">
         <v>459</v>
       </c>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B44" s="1"/>
@@ -11733,10 +11730,10 @@
         <v>75</v>
       </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B45" s="1"/>
@@ -11752,10 +11749,10 @@
         <v>190</v>
       </c>
       <c r="H45" s="1"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="70"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B46" s="1"/>
@@ -11771,10 +11768,10 @@
         <v>180</v>
       </c>
       <c r="H46" s="1"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B47" s="1"/>
@@ -11790,10 +11787,10 @@
         <v>100</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B48" s="1"/>
@@ -11809,10 +11806,10 @@
         <v>200</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="78"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="78"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="70"/>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="1"/>
@@ -11822,10 +11819,10 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="70"/>
     </row>
     <row r="50" spans="2:12" ht="19" x14ac:dyDescent="0.25">
       <c r="B50" s="13"/>
@@ -11925,11 +11922,11 @@
       <c r="I55" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="J55" s="88" t="s">
+      <c r="J55" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="89"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="72"/>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" s="1"/>
@@ -11946,9 +11943,9 @@
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="78"/>
-      <c r="K56" s="78"/>
-      <c r="L56" s="78"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="70"/>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57" s="1"/>
@@ -11965,11 +11962,11 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="78" t="s">
+      <c r="J57" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="70"/>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="1"/>
@@ -11986,11 +11983,11 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-      <c r="J58" s="78" t="s">
+      <c r="J58" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K58" s="78"/>
-      <c r="L58" s="78"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="70"/>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="1"/>
@@ -12007,11 +12004,11 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="78" t="s">
+      <c r="J59" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K59" s="78"/>
-      <c r="L59" s="78"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="70"/>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="1"/>
@@ -12028,11 +12025,11 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="78" t="s">
+      <c r="J60" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K60" s="78"/>
-      <c r="L60" s="78"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="70"/>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="1"/>
@@ -12049,11 +12046,11 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="78" t="s">
+      <c r="J61" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K61" s="78"/>
-      <c r="L61" s="78"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="70"/>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62" s="1"/>
@@ -12072,9 +12069,9 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="78"/>
-      <c r="K62" s="78"/>
-      <c r="L62" s="78"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63" s="1"/>
@@ -12093,9 +12090,9 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-      <c r="J63" s="78"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="78"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="70"/>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" s="1"/>
@@ -12112,11 +12109,11 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="78" t="s">
+      <c r="J64" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="K64" s="78"/>
-      <c r="L64" s="78"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="70"/>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="1"/>
@@ -12135,9 +12132,9 @@
       <c r="I65" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="J65" s="78"/>
-      <c r="K65" s="78"/>
-      <c r="L65" s="78"/>
+      <c r="J65" s="70"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="70"/>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="1"/>
@@ -12154,9 +12151,9 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="78"/>
-      <c r="K66" s="78"/>
-      <c r="L66" s="78"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="70"/>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="1"/>
@@ -12173,9 +12170,9 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="78"/>
-      <c r="K67" s="78"/>
-      <c r="L67" s="78"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="1"/>
@@ -12194,9 +12191,9 @@
       <c r="I68" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="J68" s="78"/>
-      <c r="K68" s="78"/>
-      <c r="L68" s="78"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69" s="1"/>
@@ -12215,9 +12212,9 @@
       <c r="I69" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="J69" s="78"/>
-      <c r="K69" s="78"/>
-      <c r="L69" s="78"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="70"/>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70" s="1"/>
@@ -12236,9 +12233,9 @@
       <c r="I70" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="J70" s="78"/>
-      <c r="K70" s="78"/>
-      <c r="L70" s="78"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71" s="1"/>
@@ -12257,9 +12254,9 @@
       <c r="I71" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="J71" s="78"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72" s="1"/>
@@ -12278,9 +12275,9 @@
       <c r="I72" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="J72" s="78"/>
-      <c r="K72" s="78"/>
-      <c r="L72" s="78"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="70"/>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73" s="1"/>
@@ -12299,9 +12296,9 @@
       <c r="I73" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
-      <c r="L73" s="78"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="70"/>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74" s="1"/>
@@ -12320,9 +12317,9 @@
       <c r="I74" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="J74" s="78"/>
-      <c r="K74" s="78"/>
-      <c r="L74" s="78"/>
+      <c r="J74" s="70"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="70"/>
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75" s="1"/>
@@ -12341,9 +12338,9 @@
       <c r="I75" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
+      <c r="J75" s="70"/>
+      <c r="K75" s="70"/>
+      <c r="L75" s="70"/>
     </row>
     <row r="76" spans="2:12" ht="19" x14ac:dyDescent="0.25">
       <c r="B76" s="13"/>
@@ -12354,9 +12351,9 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
-      <c r="J76" s="78"/>
-      <c r="K76" s="78"/>
-      <c r="L76" s="78"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="70"/>
     </row>
     <row r="77" spans="2:12" ht="19" x14ac:dyDescent="0.25">
       <c r="B77" s="13"/>
@@ -12373,9 +12370,9 @@
         <v>13020.7</v>
       </c>
       <c r="I77" s="3"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
     </row>
     <row r="78" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B78" s="58"/>
@@ -12405,43 +12402,44 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J73:L73"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="J66:L66"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="B78:L79"/>
+    <mergeCell ref="B52:L53"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="J74:L74"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N21:R22"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="N30:T30"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="I27:L27"/>
@@ -12458,44 +12456,43 @@
     <mergeCell ref="B12:L12"/>
     <mergeCell ref="Q14:R14"/>
     <mergeCell ref="I14:L14"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N21:R22"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="N30:T30"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="B78:L79"/>
-    <mergeCell ref="B52:L53"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="J74:L74"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J73:L73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -12567,12 +12564,12 @@
       <c r="G3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="81"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
       <c r="L3" s="6" t="s">
         <v>5</v>
       </c>
@@ -12606,12 +12603,12 @@
         <v>1640</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="85">
+      <c r="H4" s="79">
         <v>1476</v>
       </c>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="87"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="81"/>
       <c r="L4" s="3">
         <f>C4-B4</f>
         <v>4</v>
@@ -12637,12 +12634,12 @@
         <v>2730</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="85">
+      <c r="H5" s="79">
         <v>2590</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="87"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="81"/>
       <c r="L5" s="3">
         <f>C5-B5</f>
         <v>7</v>
@@ -12658,10 +12655,10 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="87"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="81"/>
       <c r="L6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -12680,13 +12677,13 @@
         <f>F7*$R$3</f>
         <v>38980.400000000001</v>
       </c>
-      <c r="H7" s="85">
+      <c r="H7" s="79">
         <f>H4+H5</f>
         <v>4066</v>
       </c>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="87"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="81"/>
       <c r="L7" s="3">
         <f>SUM(L4:L6)</f>
         <v>11</v>
@@ -12707,9 +12704,9 @@
       <c r="J8" s="58"/>
       <c r="K8" s="58"/>
       <c r="L8" s="58"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B9" s="59"/>
@@ -12723,24 +12720,24 @@
       <c r="J9" s="59"/>
       <c r="K9" s="59"/>
       <c r="L9" s="59"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
     </row>
     <row r="10" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
-      <c r="L10" s="77"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="88"/>
       <c r="N10" s="63" t="s">
         <v>73</v>
       </c>
@@ -12786,10 +12783,10 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="79" t="s">
+      <c r="Q11" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="81"/>
+      <c r="R11" s="78"/>
     </row>
     <row r="12" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
@@ -12805,10 +12802,10 @@
         <v>150</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
       <c r="N12" s="3" t="s">
         <v>385</v>
       </c>
@@ -12816,8 +12813,8 @@
         <v>499</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="73"/>
-      <c r="R12" s="74"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
@@ -12833,12 +12830,12 @@
         <v>140</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="78" t="s">
+      <c r="I13" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
       <c r="N13" s="3" t="s">
         <v>470</v>
       </c>
@@ -12846,8 +12843,8 @@
         <v>240</v>
       </c>
       <c r="P13" s="4"/>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="74"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="85"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
@@ -12863,15 +12860,15 @@
         <v>200</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
       <c r="N14" s="3"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
@@ -12887,17 +12884,17 @@
         <v>160</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="78" t="s">
+      <c r="I15" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
       <c r="N15" s="3"/>
       <c r="O15" s="18"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="74"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
@@ -12913,15 +12910,15 @@
         <v>1955</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
       <c r="N16" s="3"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="74"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="85"/>
     </row>
     <row r="17" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
@@ -12937,17 +12934,17 @@
         <v>250</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="78" t="s">
+      <c r="I17" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
       <c r="N17" s="3"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="74"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="85"/>
     </row>
     <row r="18" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
@@ -12963,15 +12960,15 @@
         <v>150</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
       <c r="N18" s="3"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="74"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="85"/>
     </row>
     <row r="19" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
@@ -12987,15 +12984,15 @@
         <v>100</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
       <c r="N19" s="3"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="74"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="85"/>
     </row>
     <row r="20" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
@@ -13011,12 +13008,12 @@
         <v>230</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="78" t="s">
+      <c r="I20" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
       <c r="N20" s="3"/>
       <c r="O20" s="18">
         <f>SUM(O12:O19)</f>
@@ -13026,8 +13023,8 @@
         <f>O20*$R$3</f>
         <v>6591.88</v>
       </c>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="74"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
@@ -13043,17 +13040,17 @@
         <v>180</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="78" t="s">
+      <c r="I21" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
@@ -13069,17 +13066,17 @@
         <v>285</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="78" t="s">
+      <c r="I22" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
     </row>
     <row r="23" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
@@ -13095,10 +13092,10 @@
         <v>220</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
       <c r="N23" s="63" t="s">
         <v>38</v>
       </c>
@@ -13122,10 +13119,10 @@
         <v>60</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
       <c r="N24" s="6" t="s">
         <v>20</v>
       </c>
@@ -13155,10 +13152,10 @@
         <v>150</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
       <c r="N25" s="13">
         <v>45885</v>
       </c>
@@ -13184,10 +13181,10 @@
         <v>219</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
       <c r="N26" s="13"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -13203,10 +13200,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="5">
@@ -13224,10 +13221,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
       <c r="N28" s="19"/>
       <c r="O28" s="19"/>
       <c r="P28" s="19"/>
@@ -13242,10 +13239,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
       <c r="N29" s="20"/>
       <c r="O29" s="20"/>
       <c r="P29" s="20"/>
@@ -13387,11 +13384,11 @@
       <c r="I35" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="J35" s="88" t="s">
+      <c r="J35" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="72"/>
       <c r="N35" s="63" t="s">
         <v>61</v>
       </c>
@@ -13418,9 +13415,9 @@
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
       <c r="N36" s="6" t="s">
         <v>67</v>
       </c>
@@ -13439,9 +13436,9 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
       <c r="N37" s="5">
         <f>O7+G7+H31+P20+P27+T32+H46</f>
         <v>112496.76000000001</v>
@@ -13459,9 +13456,9 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B39" s="31">
@@ -13474,9 +13471,9 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="31">
@@ -13489,9 +13486,9 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
@@ -13502,9 +13499,9 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B42" s="1"/>
@@ -13515,9 +13512,9 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B43" s="1"/>
@@ -13528,9 +13525,9 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B44" s="1"/>
@@ -13541,9 +13538,9 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
     </row>
     <row r="45" spans="2:15" ht="19" x14ac:dyDescent="0.25">
       <c r="B45" s="13"/>
@@ -13605,24 +13602,33 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="N8:P9"/>
-    <mergeCell ref="N10:R10"/>
-    <mergeCell ref="B8:L9"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="B10:L10"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="B47:L48"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="B32:L33"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="N30:T30"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
     <mergeCell ref="Q16:R16"/>
     <mergeCell ref="Q17:R17"/>
     <mergeCell ref="I15:L15"/>
@@ -13638,33 +13644,24 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q19:R19"/>
     <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="N30:T30"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="B32:L33"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="B47:L48"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="N8:P9"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="B8:L9"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="I12:L12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
